--- a/landfall-list.xlsx
+++ b/landfall-list.xlsx
@@ -3461,31 +3461,31 @@
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>Vincent M Bruner</t>
+          <t>Family Trust Wilson</t>
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>239 YACHT CLUB DR NE</t>
+          <t>528 BAYVIEW ST</t>
         </is>
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>FORT WALTON BEACH</t>
+          <t>DESTIN</t>
         </is>
       </c>
       <c r="H39" s="5" t="inlineStr">
         <is>
-          <t>850-243-2222</t>
+          <t>850-269-1593</t>
         </is>
       </c>
       <c r="I39" s="5" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>low</t>
         </is>
       </c>
       <c r="J39" s="6" t="n">
-        <v>2349907</v>
+        <v>4191571</v>
       </c>
       <c r="K39" s="5" t="inlineStr">
         <is>
@@ -3494,22 +3494,22 @@
       </c>
       <c r="L39" s="5" t="inlineStr">
         <is>
-          <t>Hughes Estates - Choctawhatchee Bay</t>
+          <t>Joes Bayou waterfront</t>
         </is>
       </c>
       <c r="M39" s="5" t="inlineStr">
         <is>
-          <t>12-2S-24-1251-0002-0030</t>
+          <t>00-2S-22-1320-0040-0010</t>
         </is>
       </c>
       <c r="N39" s="5" t="inlineStr">
         <is>
-          <t>239 YACHT CLUB DR, FT WALTON BEACH, FL 32548</t>
+          <t>524 BAYVIEW ST, DESTIN, FL 32541</t>
         </is>
       </c>
       <c r="O39" s="5" t="inlineStr">
         <is>
-          <t>Ranked #19 of 69. Chosen from Okaloosa County Property Appraiser GIS (single-family use code 0100, assessed $2,349,907). Score 60 = $2M+ value (+20); bay/lagoon waterfront (+15); owner-occupied (+10); phone found via people-search (medium confidence) (+15). Hughes Estates - Choctawhatchee Bay. Owner-occupied (mailing address matches property). In direct Isaias landfall corridor per NHC 1pm Oct 7 advisory (AL/FL border, landfall Fri night). Phone from free people-search aggregators - dial to verify before counting as qualified.</t>
+          <t>Ranked #37 of 69. Chosen from Okaloosa County Property Appraiser GIS (single-family use code 0100, assessed $4,191,571). Score 50 = $3M+ value (+25); bayou waterfront (+15); owner-occupied (+10). Joes Bayou waterfront. Owner-occupied (mailing address matches property). In direct Isaias landfall corridor per NHC 1pm Oct 7 advisory (AL/FL border, landfall Fri night). No phone found in free sources. Phone via veripages.</t>
         </is>
       </c>
     </row>
@@ -3534,22 +3534,22 @@
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
-          <t>Ramak R Amjad</t>
+          <t>Vincent M Bruner</t>
         </is>
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>1315 Panferio Dr</t>
+          <t>239 YACHT CLUB DR NE</t>
         </is>
       </c>
       <c r="G40" s="5" t="inlineStr">
         <is>
-          <t>Pensacola Beach</t>
+          <t>FORT WALTON BEACH</t>
         </is>
       </c>
       <c r="H40" s="5" t="inlineStr">
         <is>
-          <t>573-268-0529</t>
+          <t>850-243-2222</t>
         </is>
       </c>
       <c r="I40" s="5" t="inlineStr">
@@ -3558,7 +3558,7 @@
         </is>
       </c>
       <c r="J40" s="6" t="n">
-        <v>2228593</v>
+        <v>2349907</v>
       </c>
       <c r="K40" s="5" t="inlineStr">
         <is>
@@ -3567,14 +3567,22 @@
       </c>
       <c r="L40" s="5" t="inlineStr">
         <is>
-          <t>Santa Rosa Sound</t>
-        </is>
-      </c>
-      <c r="M40" s="5" t="inlineStr"/>
-      <c r="N40" s="5" t="inlineStr"/>
+          <t>Hughes Estates - Choctawhatchee Bay</t>
+        </is>
+      </c>
+      <c r="M40" s="5" t="inlineStr">
+        <is>
+          <t>12-2S-24-1251-0002-0030</t>
+        </is>
+      </c>
+      <c r="N40" s="5" t="inlineStr">
+        <is>
+          <t>239 YACHT CLUB DR, FT WALTON BEACH, FL 32548</t>
+        </is>
+      </c>
       <c r="O40" s="5" t="inlineStr">
         <is>
-          <t>Score 80: direct Santa Rosa Sound frontage (+25), $2.23M assessed value (+30), owner-occupied homestead (+10), medium-confidence phone (+15). Built 2016, 5,887 sqft. In direct landfall corridor per NHC 1pm Oct 7 advisory — landfall expected near AL/FL border Friday night.</t>
+          <t>Ranked #19 of 69. Chosen from Okaloosa County Property Appraiser GIS (single-family use code 0100, assessed $2,349,907). Score 60 = $2M+ value (+20); bay/lagoon waterfront (+15); owner-occupied (+10); phone found via people-search (medium confidence) (+15). Hughes Estates - Choctawhatchee Bay. Owner-occupied (mailing address matches property). In direct Isaias landfall corridor per NHC 1pm Oct 7 advisory (AL/FL border, landfall Fri night). Phone from free people-search aggregators - dial to verify before counting as qualified.</t>
         </is>
       </c>
     </row>
@@ -3599,22 +3607,22 @@
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t>Samuel D &amp; Maricarmen Critides</t>
+          <t>Ramak R Amjad</t>
         </is>
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>265 COUNTRY CLUB RD</t>
+          <t>1315 Panferio Dr</t>
         </is>
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>SHALIMAR</t>
+          <t>Pensacola Beach</t>
         </is>
       </c>
       <c r="H41" s="5" t="inlineStr">
         <is>
-          <t>850-374-3125</t>
+          <t>573-268-0529</t>
         </is>
       </c>
       <c r="I41" s="5" t="inlineStr">
@@ -3623,7 +3631,7 @@
         </is>
       </c>
       <c r="J41" s="6" t="n">
-        <v>1818090</v>
+        <v>2228593</v>
       </c>
       <c r="K41" s="5" t="inlineStr">
         <is>
@@ -3632,22 +3640,14 @@
       </c>
       <c r="L41" s="5" t="inlineStr">
         <is>
-          <t>Bluffs at Shalimar Pointe</t>
-        </is>
-      </c>
-      <c r="M41" s="5" t="inlineStr">
-        <is>
-          <t>04-2S-23-4805-0000-0040</t>
-        </is>
-      </c>
-      <c r="N41" s="5" t="inlineStr">
-        <is>
-          <t>265 COUNTRY CLUB RD, SHALIMAR, FL 32579</t>
-        </is>
-      </c>
+          <t>Santa Rosa Sound</t>
+        </is>
+      </c>
+      <c r="M41" s="5" t="inlineStr"/>
+      <c r="N41" s="5" t="inlineStr"/>
       <c r="O41" s="5" t="inlineStr">
         <is>
-          <t>Ranked #24 of 69. Chosen from Okaloosa County Property Appraiser GIS (single-family use code 0100, assessed $1,818,090). Score 40 = $1.5M+ value (+15); owner-occupied (+10); phone found via people-search (medium confidence) (+15). Bluffs at Shalimar Pointe. Owner-occupied (mailing address matches property). In direct Isaias landfall corridor per NHC 1pm Oct 7 advisory (AL/FL border, landfall Fri night). Phone from free people-search aggregators - dial to verify before counting as qualified.</t>
+          <t>Score 80: direct Santa Rosa Sound frontage (+25), $2.23M assessed value (+30), owner-occupied homestead (+10), medium-confidence phone (+15). Built 2016, 5,887 sqft. In direct landfall corridor per NHC 1pm Oct 7 advisory — landfall expected near AL/FL border Friday night.</t>
         </is>
       </c>
     </row>
@@ -3672,22 +3672,22 @@
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
-          <t>Curtis C Rodgers And Laura C Rodgers</t>
+          <t>Samuel D &amp; Maricarmen Critides</t>
         </is>
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>26142 Marina Rd</t>
+          <t>265 COUNTRY CLUB RD</t>
         </is>
       </c>
       <c r="G42" s="5" t="inlineStr">
         <is>
-          <t>Orange Beach</t>
+          <t>SHALIMAR</t>
         </is>
       </c>
       <c r="H42" s="5" t="inlineStr">
         <is>
-          <t>2514760195</t>
+          <t>850-374-3125</t>
         </is>
       </c>
       <c r="I42" s="5" t="inlineStr">
@@ -3696,7 +3696,7 @@
         </is>
       </c>
       <c r="J42" s="6" t="n">
-        <v>1717400</v>
+        <v>1818090</v>
       </c>
       <c r="K42" s="5" t="inlineStr">
         <is>
@@ -3705,22 +3705,22 @@
       </c>
       <c r="L42" s="5" t="inlineStr">
         <is>
-          <t>Terry Cove</t>
+          <t>Bluffs at Shalimar Pointe</t>
         </is>
       </c>
       <c r="M42" s="5" t="inlineStr">
         <is>
-          <t>65-02-09-0-001-104.000</t>
+          <t>04-2S-23-4805-0000-0040</t>
         </is>
       </c>
       <c r="N42" s="5" t="inlineStr">
         <is>
-          <t>26142 MARINA RD, ORANGE BEACH, AL 36561-3540</t>
+          <t>265 COUNTRY CLUB RD, SHALIMAR, FL 32579</t>
         </is>
       </c>
       <c r="O42" s="5" t="inlineStr">
         <is>
-          <t>Score 70: $1.72M county assessed value (+30); Terry Cove frontage (+15); owner-occupied (+10); medium-confidence phone (+15). Owner-occupied Terry Cove waterfront; $1.7M assessed. In direct landfall corridor per NHC Oct 7 advisory - Tropical Storm Isaias landfall expected near AL/FL border Friday night.</t>
+          <t>Ranked #24 of 69. Chosen from Okaloosa County Property Appraiser GIS (single-family use code 0100, assessed $1,818,090). Score 40 = $1.5M+ value (+15); owner-occupied (+10); phone found via people-search (medium confidence) (+15). Bluffs at Shalimar Pointe. Owner-occupied (mailing address matches property). In direct Isaias landfall corridor per NHC 1pm Oct 7 advisory (AL/FL border, landfall Fri night). Phone from free people-search aggregators - dial to verify before counting as qualified.</t>
         </is>
       </c>
     </row>
@@ -3745,12 +3745,12 @@
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t>Michael R Boyd And Virginia M Boyd</t>
+          <t>Curtis C Rodgers And Laura C Rodgers</t>
         </is>
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>31691 Shoalwater Dr</t>
+          <t>26142 Marina Rd</t>
         </is>
       </c>
       <c r="G43" s="5" t="inlineStr">
@@ -3760,7 +3760,7 @@
       </c>
       <c r="H43" s="5" t="inlineStr">
         <is>
-          <t>2514145976</t>
+          <t>2514760195</t>
         </is>
       </c>
       <c r="I43" s="5" t="inlineStr">
@@ -3769,7 +3769,7 @@
         </is>
       </c>
       <c r="J43" s="6" t="n">
-        <v>1667300</v>
+        <v>1717400</v>
       </c>
       <c r="K43" s="5" t="inlineStr">
         <is>
@@ -3778,22 +3778,22 @@
       </c>
       <c r="L43" s="5" t="inlineStr">
         <is>
-          <t>Ole River (Ono Island)</t>
+          <t>Terry Cove</t>
         </is>
       </c>
       <c r="M43" s="5" t="inlineStr">
         <is>
-          <t>64-03-05-0-000-001.005</t>
+          <t>65-02-09-0-001-104.000</t>
         </is>
       </c>
       <c r="N43" s="5" t="inlineStr">
         <is>
-          <t>31691 SHOAL WATER DR, ORANGE BEACH, AL 36561-3768</t>
+          <t>26142 MARINA RD, ORANGE BEACH, AL 36561-3540</t>
         </is>
       </c>
       <c r="O43" s="5" t="inlineStr">
         <is>
-          <t>Score 70: $1.67M county assessed value (+30); Ole River (Ono Island) frontage (+15); owner-occupied (+10); medium-confidence phone (+15). Owner-occupied Ono Island waterfront; $1.67M assessed. In direct landfall corridor per NHC Oct 7 advisory - Tropical Storm Isaias landfall expected near AL/FL border Friday night.</t>
+          <t>Score 70: $1.72M county assessed value (+30); Terry Cove frontage (+15); owner-occupied (+10); medium-confidence phone (+15). Owner-occupied Terry Cove waterfront; $1.7M assessed. In direct landfall corridor per NHC Oct 7 advisory - Tropical Storm Isaias landfall expected near AL/FL border Friday night.</t>
         </is>
       </c>
     </row>
@@ -3818,22 +3818,22 @@
       </c>
       <c r="E44" s="5" t="inlineStr">
         <is>
-          <t>Living Trust Harageones</t>
+          <t>Michael R Boyd And Virginia M Boyd</t>
         </is>
       </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
-          <t>35 SENNER CT</t>
+          <t>31691 Shoalwater Dr</t>
         </is>
       </c>
       <c r="G44" s="5" t="inlineStr">
         <is>
-          <t>SHALIMAR</t>
+          <t>Orange Beach</t>
         </is>
       </c>
       <c r="H44" s="5" t="inlineStr">
         <is>
-          <t>607-217-5431</t>
+          <t>2514145976</t>
         </is>
       </c>
       <c r="I44" s="5" t="inlineStr">
@@ -3842,7 +3842,7 @@
         </is>
       </c>
       <c r="J44" s="6" t="n">
-        <v>1599521</v>
+        <v>1667300</v>
       </c>
       <c r="K44" s="5" t="inlineStr">
         <is>
@@ -3851,22 +3851,22 @@
       </c>
       <c r="L44" s="5" t="inlineStr">
         <is>
-          <t>Lake Lorraine Gardens</t>
+          <t>Ole River (Ono Island)</t>
         </is>
       </c>
       <c r="M44" s="5" t="inlineStr">
         <is>
-          <t>04-2S-23-1437-0000-0290</t>
+          <t>64-03-05-0-000-001.005</t>
         </is>
       </c>
       <c r="N44" s="5" t="inlineStr">
         <is>
-          <t>35 SENNER CT, SHALIMAR, FL 32579</t>
+          <t>31691 SHOAL WATER DR, ORANGE BEACH, AL 36561-3768</t>
         </is>
       </c>
       <c r="O44" s="5" t="inlineStr">
         <is>
-          <t>Ranked #26 of 69. Chosen from Okaloosa County Property Appraiser GIS (single-family use code 0100, assessed $1,599,521). Score 40 = $1.5M+ value (+15); owner-occupied (+10); phone found via people-search (medium confidence) (+15). Lake Lorraine Gardens. Owner-occupied (mailing address matches property). In direct Isaias landfall corridor per NHC 1pm Oct 7 advisory (AL/FL border, landfall Fri night). Phone from free people-search aggregators - dial to verify before counting as qualified.</t>
+          <t>Score 70: $1.67M county assessed value (+30); Ole River (Ono Island) frontage (+15); owner-occupied (+10); medium-confidence phone (+15). Owner-occupied Ono Island waterfront; $1.67M assessed. In direct landfall corridor per NHC Oct 7 advisory - Tropical Storm Isaias landfall expected near AL/FL border Friday night.</t>
         </is>
       </c>
     </row>
@@ -3891,22 +3891,22 @@
       </c>
       <c r="E45" s="5" t="inlineStr">
         <is>
-          <t>John D Stomps And Karan S Stomps</t>
+          <t>Living Trust Harageones</t>
         </is>
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
-          <t>32301 River Rd</t>
+          <t>35 SENNER CT</t>
         </is>
       </c>
       <c r="G45" s="5" t="inlineStr">
         <is>
-          <t>Orange Beach</t>
+          <t>SHALIMAR</t>
         </is>
       </c>
       <c r="H45" s="5" t="inlineStr">
         <is>
-          <t>6015352213</t>
+          <t>607-217-5431</t>
         </is>
       </c>
       <c r="I45" s="5" t="inlineStr">
@@ -3915,7 +3915,7 @@
         </is>
       </c>
       <c r="J45" s="6" t="n">
-        <v>1509200</v>
+        <v>1599521</v>
       </c>
       <c r="K45" s="5" t="inlineStr">
         <is>
@@ -3924,22 +3924,22 @@
       </c>
       <c r="L45" s="5" t="inlineStr">
         <is>
-          <t>Ole River (Ono Island)</t>
+          <t>Lake Lorraine Gardens</t>
         </is>
       </c>
       <c r="M45" s="5" t="inlineStr">
         <is>
-          <t>63-08-33-0-000-001.077</t>
+          <t>04-2S-23-1437-0000-0290</t>
         </is>
       </c>
       <c r="N45" s="5" t="inlineStr">
         <is>
-          <t>32301 RIVER RD, ORANGE BEACH, AL 36561-5737</t>
+          <t>35 SENNER CT, SHALIMAR, FL 32579</t>
         </is>
       </c>
       <c r="O45" s="5" t="inlineStr">
         <is>
-          <t>Score 70: $1.51M county assessed value (+30); Ole River (Ono Island) frontage (+15); owner-occupied (+10); medium-confidence phone (+15). Owner-occupied Ono Island riverfront; $1.5M assessed. In direct landfall corridor per NHC Oct 7 advisory - Tropical Storm Isaias landfall expected near AL/FL border Friday night.</t>
+          <t>Ranked #26 of 69. Chosen from Okaloosa County Property Appraiser GIS (single-family use code 0100, assessed $1,599,521). Score 40 = $1.5M+ value (+15); owner-occupied (+10); phone found via people-search (medium confidence) (+15). Lake Lorraine Gardens. Owner-occupied (mailing address matches property). In direct Isaias landfall corridor per NHC 1pm Oct 7 advisory (AL/FL border, landfall Fri night). Phone from free people-search aggregators - dial to verify before counting as qualified.</t>
         </is>
       </c>
     </row>
@@ -3964,22 +3964,22 @@
       </c>
       <c r="E46" s="5" t="inlineStr">
         <is>
-          <t>Timothy E Ray</t>
+          <t>John D Stomps And Karan S Stomps</t>
         </is>
       </c>
       <c r="F46" s="5" t="inlineStr">
         <is>
-          <t>225 Yacht Club Dr NE</t>
+          <t>32301 River Rd</t>
         </is>
       </c>
       <c r="G46" s="5" t="inlineStr">
         <is>
-          <t>Fort Walton Beach</t>
+          <t>Orange Beach</t>
         </is>
       </c>
       <c r="H46" s="5" t="inlineStr">
         <is>
-          <t>850-796-2843</t>
+          <t>6015352213</t>
         </is>
       </c>
       <c r="I46" s="5" t="inlineStr">
@@ -3988,7 +3988,7 @@
         </is>
       </c>
       <c r="J46" s="6" t="n">
-        <v>1050000</v>
+        <v>1509200</v>
       </c>
       <c r="K46" s="5" t="inlineStr">
         <is>
@@ -3997,22 +3997,22 @@
       </c>
       <c r="L46" s="5" t="inlineStr">
         <is>
-          <t>Choctawhatchee Bay / bayou waterfront</t>
+          <t>Ole River (Ono Island)</t>
         </is>
       </c>
       <c r="M46" s="5" t="inlineStr">
         <is>
-          <t>122S24125000010040</t>
+          <t>63-08-33-0-000-001.077</t>
         </is>
       </c>
       <c r="N46" s="5" t="inlineStr">
         <is>
-          <t>225 Yacht Club Dr NE, Fort Walton Beach, FL 32548</t>
+          <t>32301 RIVER RD, ORANGE BEACH, AL 36561-5737</t>
         </is>
       </c>
       <c r="O46" s="5" t="inlineStr">
         <is>
-          <t>Score 70: $1.05M value (+30), bay/bayou frontage (+15), owner-occupied (+10), medium-confidence phone (+15). Phone is owner's construction business line at this address. In direct landfall corridor per NHC Oct 7 advisory.</t>
+          <t>Score 70: $1.51M county assessed value (+30); Ole River (Ono Island) frontage (+15); owner-occupied (+10); medium-confidence phone (+15). Owner-occupied Ono Island riverfront; $1.5M assessed. In direct landfall corridor per NHC Oct 7 advisory - Tropical Storm Isaias landfall expected near AL/FL border Friday night.</t>
         </is>
       </c>
     </row>
@@ -4037,22 +4037,22 @@
       </c>
       <c r="E47" s="5" t="inlineStr">
         <is>
-          <t>Peter Clarke</t>
+          <t>Timothy E Ray</t>
         </is>
       </c>
       <c r="F47" s="5" t="inlineStr">
         <is>
-          <t>369 Gulfview Ln</t>
+          <t>225 Yacht Club Dr NE</t>
         </is>
       </c>
       <c r="G47" s="5" t="inlineStr">
         <is>
-          <t>Perdido Key</t>
+          <t>Fort Walton Beach</t>
         </is>
       </c>
       <c r="H47" s="5" t="inlineStr">
         <is>
-          <t>850-492-8436</t>
+          <t>850-796-2843</t>
         </is>
       </c>
       <c r="I47" s="5" t="inlineStr">
@@ -4061,7 +4061,7 @@
         </is>
       </c>
       <c r="J47" s="6" t="n">
-        <v>729000</v>
+        <v>1050000</v>
       </c>
       <c r="K47" s="5" t="inlineStr">
         <is>
@@ -4070,22 +4070,22 @@
       </c>
       <c r="L47" s="5" t="inlineStr">
         <is>
-          <t>Direct Gulf of Mexico frontage</t>
+          <t>Choctawhatchee Bay / bayou waterfront</t>
         </is>
       </c>
       <c r="M47" s="5" t="inlineStr">
         <is>
-          <t>064S320405018001</t>
+          <t>122S24125000010040</t>
         </is>
       </c>
       <c r="N47" s="5" t="inlineStr">
         <is>
-          <t>369 Gulfview Ln, Pensacola, FL 32507</t>
+          <t>225 Yacht Club Dr NE, Fort Walton Beach, FL 32548</t>
         </is>
       </c>
       <c r="O47" s="5" t="inlineStr">
         <is>
-          <t>Score 70: $729K value (+20), direct Gulf frontage (+25), owner-occupied (+10), medium-confidence phone (+15). In direct landfall corridor per NHC Oct 7 advisory. NOTE: Perdido Key obit for Peter Clarke Mar 2026 - verify occupancy.</t>
+          <t>Score 70: $1.05M value (+30), bay/bayou frontage (+15), owner-occupied (+10), medium-confidence phone (+15). Phone is owner's construction business line at this address. In direct landfall corridor per NHC Oct 7 advisory.</t>
         </is>
       </c>
     </row>
@@ -4095,7 +4095,7 @@
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>TIER 1 - CALL FIRST</t>
+          <t>TIER 3 - NEW NUMBER (unverified)</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
@@ -4110,33 +4110,31 @@
       </c>
       <c r="E48" s="5" t="inlineStr">
         <is>
-          <t>Chris Walter</t>
+          <t>Peter Clarke</t>
         </is>
       </c>
       <c r="F48" s="5" t="inlineStr">
         <is>
-          <t>5113 Soundside Dr</t>
+          <t>369 Gulfview Ln</t>
         </is>
       </c>
       <c r="G48" s="5" t="inlineStr">
         <is>
-          <t>Gulf Breeze</t>
+          <t>Perdido Key</t>
         </is>
       </c>
       <c r="H48" s="5" t="inlineStr">
         <is>
-          <t>8509344348</t>
+          <t>850-492-8436</t>
         </is>
       </c>
       <c r="I48" s="5" t="inlineStr">
         <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="J48" s="6" t="inlineStr">
-        <is>
-          <t>605000 (2009 sale; tax value 193965)</t>
-        </is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J48" s="6" t="n">
+        <v>729000</v>
       </c>
       <c r="K48" s="5" t="inlineStr">
         <is>
@@ -4145,22 +4143,22 @@
       </c>
       <c r="L48" s="5" t="inlineStr">
         <is>
-          <t>Santa Rosa Sound</t>
+          <t>Direct Gulf of Mexico frontage</t>
         </is>
       </c>
       <c r="M48" s="5" t="inlineStr">
         <is>
-          <t>252S282680000000250</t>
+          <t>064S320405018001</t>
         </is>
       </c>
       <c r="N48" s="5" t="inlineStr">
         <is>
-          <t>5113 Soundside Dr Gulf Breeze FL 32563</t>
+          <t>369 Gulfview Ln, Pensacola, FL 32507</t>
         </is>
       </c>
       <c r="O48" s="5" t="inlineStr">
         <is>
-          <t>Score 85: direct Santa Rosa Sound waterfront (+25), $605K last sale (+20), owner-occupied (+10), high-confidence phone (+30). 2bd/2.5ba 2,600sf on 0.94ac; works in residential construction. In direct landfall corridor per NHC 1pm Oct 7 advisory - landfall expected near AL/FL border Friday night.</t>
+          <t>Score 70: $729K value (+20), direct Gulf frontage (+25), owner-occupied (+10), medium-confidence phone (+15). In direct landfall corridor per NHC Oct 7 advisory. NOTE: Perdido Key obit for Peter Clarke Mar 2026 - verify occupancy.</t>
         </is>
       </c>
     </row>
@@ -4175,7 +4173,7 @@
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>85</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
@@ -4185,22 +4183,22 @@
       </c>
       <c r="E49" s="5" t="inlineStr">
         <is>
-          <t>Kha &amp; Albright Denise Phan</t>
+          <t>Chris Walter</t>
         </is>
       </c>
       <c r="F49" s="5" t="inlineStr">
         <is>
-          <t>83 WOODWARD ST</t>
+          <t>5113 Soundside Dr</t>
         </is>
       </c>
       <c r="G49" s="5" t="inlineStr">
         <is>
-          <t>DESTIN</t>
+          <t>Gulf Breeze</t>
         </is>
       </c>
       <c r="H49" s="5" t="inlineStr">
         <is>
-          <t>319-350-3994</t>
+          <t>8509344348</t>
         </is>
       </c>
       <c r="I49" s="5" t="inlineStr">
@@ -4208,32 +4206,34 @@
           <t>high</t>
         </is>
       </c>
-      <c r="J49" s="6" t="n">
-        <v>4603865</v>
+      <c r="J49" s="6" t="inlineStr">
+        <is>
+          <t>605000 (2009 sale; tax value 193965)</t>
+        </is>
       </c>
       <c r="K49" s="5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="L49" s="5" t="inlineStr">
         <is>
-          <t>Hutchinson Courts</t>
+          <t>Santa Rosa Sound</t>
         </is>
       </c>
       <c r="M49" s="5" t="inlineStr">
         <is>
-          <t>00-2S-22-5446-0000-0020</t>
+          <t>252S282680000000250</t>
         </is>
       </c>
       <c r="N49" s="5" t="inlineStr">
         <is>
-          <t>2006 ASPEN RIDGE SE, CEDAR RAPIDS, IA 52403</t>
+          <t>5113 Soundside Dr Gulf Breeze FL 32563</t>
         </is>
       </c>
       <c r="O49" s="5" t="inlineStr">
         <is>
-          <t>Ranked #62 of 69. Chosen from Okaloosa County Property Appraiser GIS (single-family use code 0100, assessed $4,603,865). Score 25 = $3M+ value (+25). Hutchinson Courts. Second/vacation home (out-of-area mailing address) - absentee owner; storm damage still needs a local cleanup crew fast. In direct Isaias landfall corridor per NHC 1pm Oct 7 advisory (AL/FL border, landfall Fri night). No phone found in free sources.</t>
+          <t>Score 85: direct Santa Rosa Sound waterfront (+25), $605K last sale (+20), owner-occupied (+10), high-confidence phone (+30). 2bd/2.5ba 2,600sf on 0.94ac; works in residential construction. In direct landfall corridor per NHC 1pm Oct 7 advisory - landfall expected near AL/FL border Friday night.</t>
         </is>
       </c>
     </row>
@@ -4258,22 +4258,22 @@
       </c>
       <c r="E50" s="5" t="inlineStr">
         <is>
-          <t>John Gary Hall</t>
+          <t>Kha &amp; Albright Denise Phan</t>
         </is>
       </c>
       <c r="F50" s="5" t="inlineStr">
         <is>
-          <t>29879 Saint John Dr</t>
+          <t>83 WOODWARD ST</t>
         </is>
       </c>
       <c r="G50" s="5" t="inlineStr">
         <is>
-          <t>Orange Beach</t>
+          <t>DESTIN</t>
         </is>
       </c>
       <c r="H50" s="5" t="inlineStr">
         <is>
-          <t>3347942678</t>
+          <t>319-350-3994</t>
         </is>
       </c>
       <c r="I50" s="5" t="inlineStr">
@@ -4282,7 +4282,7 @@
         </is>
       </c>
       <c r="J50" s="6" t="n">
-        <v>4589000</v>
+        <v>4603865</v>
       </c>
       <c r="K50" s="5" t="inlineStr">
         <is>
@@ -4291,22 +4291,22 @@
       </c>
       <c r="L50" s="5" t="inlineStr">
         <is>
-          <t>Bayou St. John</t>
+          <t>Hutchinson Courts</t>
         </is>
       </c>
       <c r="M50" s="5" t="inlineStr">
         <is>
-          <t>65-01-01-0-000-001.113</t>
+          <t>00-2S-22-5446-0000-0020</t>
         </is>
       </c>
       <c r="N50" s="5" t="inlineStr">
         <is>
-          <t>2810 FORTNER ST BLDG J, DOTHAN, AL 36301</t>
+          <t>2006 ASPEN RIDGE SE, CEDAR RAPIDS, IA 52403</t>
         </is>
       </c>
       <c r="O50" s="5" t="inlineStr">
         <is>
-          <t>Score 75: $4.59M county assessed value (+30); Bayou St. John frontage (+15); high-confidence phone (+30). Absentee owner (Dothan AL contractor); $4.6M bayou-front estate, highest assessed value on list. In direct landfall corridor per NHC Oct 7 advisory - Tropical Storm Isaias landfall expected near AL/FL border Friday night.</t>
+          <t>Ranked #62 of 69. Chosen from Okaloosa County Property Appraiser GIS (single-family use code 0100, assessed $4,603,865). Score 25 = $3M+ value (+25). Hutchinson Courts. Second/vacation home (out-of-area mailing address) - absentee owner; storm damage still needs a local cleanup crew fast. In direct Isaias landfall corridor per NHC 1pm Oct 7 advisory (AL/FL border, landfall Fri night). No phone found in free sources.</t>
         </is>
       </c>
     </row>
@@ -4331,22 +4331,22 @@
       </c>
       <c r="E51" s="5" t="inlineStr">
         <is>
-          <t>Andrew Vallianatos</t>
+          <t>John Gary Hall</t>
         </is>
       </c>
       <c r="F51" s="5" t="inlineStr">
         <is>
-          <t>602 LAGOON DR</t>
+          <t>29879 Saint John Dr</t>
         </is>
       </c>
       <c r="G51" s="5" t="inlineStr">
         <is>
-          <t>DESTIN</t>
+          <t>Orange Beach</t>
         </is>
       </c>
       <c r="H51" s="5" t="inlineStr">
         <is>
-          <t>850-650-3124</t>
+          <t>3347942678</t>
         </is>
       </c>
       <c r="I51" s="5" t="inlineStr">
@@ -4355,31 +4355,31 @@
         </is>
       </c>
       <c r="J51" s="6" t="n">
-        <v>4131281</v>
+        <v>4589000</v>
       </c>
       <c r="K51" s="5" t="inlineStr">
         <is>
-          <t>likely</t>
+          <t>no</t>
         </is>
       </c>
       <c r="L51" s="5" t="inlineStr">
         <is>
-          <t>Holiday Isle - lagoon</t>
+          <t>Bayou St. John</t>
         </is>
       </c>
       <c r="M51" s="5" t="inlineStr">
         <is>
-          <t>00-2S-24-2186-000E-0830</t>
+          <t>65-01-01-0-000-001.113</t>
         </is>
       </c>
       <c r="N51" s="5" t="inlineStr">
         <is>
-          <t>400 MATTIE M KELLY BLVD #12, DESTIN, FL 32541</t>
+          <t>2810 FORTNER ST BLDG J, DOTHAN, AL 36301</t>
         </is>
       </c>
       <c r="O51" s="5" t="inlineStr">
         <is>
-          <t>Ranked #14 of 69. Chosen from Okaloosa County Property Appraiser GIS (single-family use code 0100, assessed $4,131,281). Score 65 = $3M+ value (+25); bay/lagoon waterfront (+15); owner-occupied (+10); phone found via people-search (high confidence) (+15). Holiday Isle - lagoon. Likely owner-occupied. In direct Isaias landfall corridor per NHC 1pm Oct 7 advisory (AL/FL border, landfall Fri night). Phone from free people-search aggregators - dial to verify before counting as qualified.</t>
+          <t>Score 75: $4.59M county assessed value (+30); Bayou St. John frontage (+15); high-confidence phone (+30). Absentee owner (Dothan AL contractor); $4.6M bayou-front estate, highest assessed value on list. In direct landfall corridor per NHC Oct 7 advisory - Tropical Storm Isaias landfall expected near AL/FL border Friday night.</t>
         </is>
       </c>
     </row>
@@ -4404,12 +4404,12 @@
       </c>
       <c r="E52" s="5" t="inlineStr">
         <is>
-          <t>Robert E Jr Living Trust Shaw</t>
+          <t>Family Trust Travis</t>
         </is>
       </c>
       <c r="F52" s="5" t="inlineStr">
         <is>
-          <t>2982 SCENIC HIGHWAY 98</t>
+          <t>4760 OCEAN BLVD</t>
         </is>
       </c>
       <c r="G52" s="5" t="inlineStr">
@@ -4419,7 +4419,7 @@
       </c>
       <c r="H52" s="5" t="inlineStr">
         <is>
-          <t>706-275-1911</t>
+          <t>410-284-2472</t>
         </is>
       </c>
       <c r="I52" s="5" t="inlineStr">
@@ -4428,7 +4428,7 @@
         </is>
       </c>
       <c r="J52" s="6" t="n">
-        <v>3727623</v>
+        <v>4423168</v>
       </c>
       <c r="K52" s="5" t="inlineStr">
         <is>
@@ -4437,22 +4437,22 @@
       </c>
       <c r="L52" s="5" t="inlineStr">
         <is>
-          <t>Shores of Crystal Beach - Gulf front</t>
+          <t>Destiny by the Sea - direct Gulf front</t>
         </is>
       </c>
       <c r="M52" s="5" t="inlineStr">
         <is>
-          <t>00-2S-22-0584-0000-0090</t>
+          <t>00-2S-22-0075-0000-0170</t>
         </is>
       </c>
       <c r="N52" s="5" t="inlineStr">
         <is>
-          <t>PO BOX 1739, DALTON, GA 30722</t>
+          <t>310 LEISURE ACRES, BUCHANAN, TN 38222</t>
         </is>
       </c>
       <c r="O52" s="5" t="inlineStr">
         <is>
-          <t>Ranked #17 of 69. Chosen from Okaloosa County Property Appraiser GIS (single-family use code 0100, assessed $3,727,623). Score 65 = $3M+ value (+25); direct Gulf frontage (+25); phone found via people-search (medium confidence) (+15). Shores of Crystal Beach - Gulf front. Second/vacation home (out-of-area mailing address) - absentee owner; storm damage still needs a local cleanup crew fast. In direct Isaias landfall corridor per NHC 1pm Oct 7 advisory (AL/FL border, landfall Fri night). Phone from free people-search aggregators - dial to verify before counting as qualified.</t>
+          <t>Ranked #34 of 69. Chosen from Okaloosa County Property Appraiser GIS (single-family use code 0100, assessed $4,423,168). Score 50 = $3M+ value (+25); direct Gulf frontage (+25). Destiny by the Sea - direct Gulf front. Second/vacation home (out-of-area mailing address) - absentee owner; storm damage still needs a local cleanup crew fast. In direct Isaias landfall corridor per NHC 1pm Oct 7 advisory (AL/FL border, landfall Fri night). No phone found in free sources. Phone via BeenVerified.</t>
         </is>
       </c>
     </row>
@@ -4462,7 +4462,7 @@
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>TIER 3 - NEW NUMBER (unverified)</t>
+          <t>TIER 1 - CALL FIRST</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
@@ -4477,55 +4477,55 @@
       </c>
       <c r="E53" s="5" t="inlineStr">
         <is>
-          <t>Mark F Loriz</t>
+          <t>Andrew Vallianatos</t>
         </is>
       </c>
       <c r="F53" s="5" t="inlineStr">
         <is>
-          <t>2631 Bayou Blvd, Pensacola, FL 32503</t>
+          <t>602 LAGOON DR</t>
         </is>
       </c>
       <c r="G53" s="5" t="inlineStr">
         <is>
-          <t>Pensacola</t>
+          <t>DESTIN</t>
         </is>
       </c>
       <c r="H53" s="5" t="inlineStr">
         <is>
-          <t>(850) 477-7042</t>
+          <t>850-650-3124</t>
         </is>
       </c>
       <c r="I53" s="5" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="J53" s="6" t="n">
-        <v>1100000</v>
+        <v>4131281</v>
       </c>
       <c r="K53" s="5" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>likely</t>
         </is>
       </c>
       <c r="L53" s="5" t="inlineStr">
         <is>
-          <t>Bayou Texar</t>
+          <t>Holiday Isle - lagoon</t>
         </is>
       </c>
       <c r="M53" s="5" t="inlineStr">
         <is>
-          <t>331S300902000000</t>
+          <t>00-2S-24-2186-000E-0830</t>
         </is>
       </c>
       <c r="N53" s="5" t="inlineStr">
         <is>
-          <t>2631 Bayou Blvd, Pensacola, FL 32503</t>
+          <t>400 MATTIE M KELLY BLVD #12, DESTIN, FL 32541</t>
         </is>
       </c>
       <c r="O53" s="5" t="inlineStr">
         <is>
-          <t>Score 80: $1.1M last sale (2004) (+30), direct Bayou Texar frontage — 150 ft waterfront (+25), owner-occupied (+10), low-confidence phone (+15, office line). 6,740 sf, 5bd/7ba on 1.1 acres — max tree/debris exposure. In direct landfall corridor per NHC 1pm Oct 7 advisory — landfall expected near AL/FL border Friday night.</t>
+          <t>Ranked #14 of 69. Chosen from Okaloosa County Property Appraiser GIS (single-family use code 0100, assessed $4,131,281). Score 65 = $3M+ value (+25); bay/lagoon waterfront (+15); owner-occupied (+10); phone found via people-search (high confidence) (+15). Holiday Isle - lagoon. Likely owner-occupied. In direct Isaias landfall corridor per NHC 1pm Oct 7 advisory (AL/FL border, landfall Fri night). Phone from free people-search aggregators - dial to verify before counting as qualified.</t>
         </is>
       </c>
     </row>
@@ -4540,7 +4540,7 @@
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>80</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
@@ -4550,12 +4550,12 @@
       </c>
       <c r="E54" s="5" t="inlineStr">
         <is>
-          <t>Bill J Ii &amp; Mary O Smith</t>
+          <t>Robert E Jr Living Trust Shaw</t>
         </is>
       </c>
       <c r="F54" s="5" t="inlineStr">
         <is>
-          <t>793 BAYOU DR</t>
+          <t>2982 SCENIC HIGHWAY 98</t>
         </is>
       </c>
       <c r="G54" s="5" t="inlineStr">
@@ -4565,7 +4565,7 @@
       </c>
       <c r="H54" s="5" t="inlineStr">
         <is>
-          <t>256-734-4473</t>
+          <t>706-275-1911</t>
         </is>
       </c>
       <c r="I54" s="5" t="inlineStr">
@@ -4574,7 +4574,7 @@
         </is>
       </c>
       <c r="J54" s="6" t="n">
-        <v>6192452</v>
+        <v>3727623</v>
       </c>
       <c r="K54" s="5" t="inlineStr">
         <is>
@@ -4583,22 +4583,22 @@
       </c>
       <c r="L54" s="5" t="inlineStr">
         <is>
-          <t>Joes Bayou waterfront</t>
+          <t>Shores of Crystal Beach - Gulf front</t>
         </is>
       </c>
       <c r="M54" s="5" t="inlineStr">
         <is>
-          <t>00-2S-22-1320-0000-01A0</t>
+          <t>00-2S-22-0584-0000-0090</t>
         </is>
       </c>
       <c r="N54" s="5" t="inlineStr">
         <is>
-          <t>1357 ASHFORD AVE STE 2 PMB 45, SAN JUAN, PR 00907</t>
+          <t>PO BOX 1739, DALTON, GA 30722</t>
         </is>
       </c>
       <c r="O54" s="5" t="inlineStr">
         <is>
-          <t>Ranked #45 of 69. Chosen from Okaloosa County Property Appraiser GIS (single-family use code 0100, assessed $6,192,452). Score 45 = $5M+ value (+30); bayou waterfront (+15). Joes Bayou waterfront. Second/vacation home (out-of-area mailing address) - absentee owner; storm damage still needs a local cleanup crew fast. In direct Isaias landfall corridor per NHC 1pm Oct 7 advisory (AL/FL border, landfall Fri night). No phone found in free sources.</t>
+          <t>Ranked #17 of 69. Chosen from Okaloosa County Property Appraiser GIS (single-family use code 0100, assessed $3,727,623). Score 65 = $3M+ value (+25); direct Gulf frontage (+25); phone found via people-search (medium confidence) (+15). Shores of Crystal Beach - Gulf front. Second/vacation home (out-of-area mailing address) - absentee owner; storm damage still needs a local cleanup crew fast. In direct Isaias landfall corridor per NHC 1pm Oct 7 advisory (AL/FL border, landfall Fri night). Phone from free people-search aggregators - dial to verify before counting as qualified.</t>
         </is>
       </c>
     </row>
@@ -4613,7 +4613,7 @@
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>80</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
@@ -4623,55 +4623,55 @@
       </c>
       <c r="E55" s="5" t="inlineStr">
         <is>
-          <t>Sue C Dodge</t>
+          <t>Ty A &amp; Kimberly C Pennington</t>
         </is>
       </c>
       <c r="F55" s="5" t="inlineStr">
         <is>
-          <t>7533 Gulf Blvd</t>
+          <t>13 POQUITO RD</t>
         </is>
       </c>
       <c r="G55" s="5" t="inlineStr">
         <is>
-          <t>Navarre Beach</t>
+          <t>SHALIMAR</t>
         </is>
       </c>
       <c r="H55" s="5" t="inlineStr">
         <is>
-          <t>(773) 305-0707</t>
+          <t>770-971-1085</t>
         </is>
       </c>
       <c r="I55" s="5" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>low</t>
         </is>
       </c>
       <c r="J55" s="6" t="n">
-        <v>2154050</v>
+        <v>1898688</v>
       </c>
       <c r="K55" s="5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="L55" s="5" t="inlineStr">
         <is>
-          <t>Gulf of Mexico</t>
+          <t>Bayou Poquito waterfront</t>
         </is>
       </c>
       <c r="M55" s="5" t="inlineStr">
         <is>
-          <t>28-2S-26-9180-04900-0070</t>
+          <t>31-1S-23-0120-0016-0050</t>
         </is>
       </c>
       <c r="N55" s="5" t="inlineStr">
         <is>
-          <t>7533 Gulf Blvd, Navarre Beach, FL 32566</t>
+          <t>13 POQUITO RD, SHALIMAR, FL 32579</t>
         </is>
       </c>
       <c r="O55" s="5" t="inlineStr">
         <is>
-          <t>Score 70: $2.15M just value (+30), direct Gulf frontage (+25), medium-confidence phone (+15). Vacation rental ('Dodge Dunes') - absentee owner needs post-storm cleanup. In direct landfall corridor per NHC 1pm Oct 7 advisory - landfall expected near AL/FL border Friday night.</t>
+          <t>Ranked #50 of 69. Chosen from Okaloosa County Property Appraiser GIS (single-family use code 0100, assessed $1,898,688). Score 40 = $1.5M+ value (+15); bayou waterfront (+15); owner-occupied (+10). Bayou Poquito waterfront. Owner-occupied (mailing address matches property). In direct Isaias landfall corridor per NHC 1pm Oct 7 advisory (AL/FL border, landfall Fri night). No phone found in free sources. Phone via veripages + realtyhop.</t>
         </is>
       </c>
     </row>
@@ -4681,12 +4681,12 @@
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>TIER 1 - CALL FIRST</t>
+          <t>TIER 3 - NEW NUMBER (unverified)</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>80</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
@@ -4696,55 +4696,55 @@
       </c>
       <c r="E56" s="5" t="inlineStr">
         <is>
-          <t>Charles A Childress</t>
+          <t>Mark F Loriz</t>
         </is>
       </c>
       <c r="F56" s="5" t="inlineStr">
         <is>
-          <t>29024 Ono Blvd</t>
+          <t>2631 Bayou Blvd, Pensacola, FL 32503</t>
         </is>
       </c>
       <c r="G56" s="5" t="inlineStr">
         <is>
-          <t>Orange Beach</t>
+          <t>Pensacola</t>
         </is>
       </c>
       <c r="H56" s="5" t="inlineStr">
         <is>
-          <t>2519477385</t>
+          <t>(850) 477-7042</t>
         </is>
       </c>
       <c r="I56" s="5" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>low</t>
         </is>
       </c>
       <c r="J56" s="6" t="n">
-        <v>2089600</v>
+        <v>1100000</v>
       </c>
       <c r="K56" s="5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="L56" s="5" t="inlineStr">
         <is>
-          <t>Ole River (Ono Island)</t>
+          <t>Bayou Texar</t>
         </is>
       </c>
       <c r="M56" s="5" t="inlineStr">
         <is>
-          <t>65-01-01-0-000-003.000</t>
+          <t>331S300902000000</t>
         </is>
       </c>
       <c r="N56" s="5" t="inlineStr">
         <is>
-          <t>PO BOX 435, ROBERTSDALE, AL 36567-0435</t>
+          <t>2631 Bayou Blvd, Pensacola, FL 32503</t>
         </is>
       </c>
       <c r="O56" s="5" t="inlineStr">
         <is>
-          <t>Score 75: $2.09M county assessed value (+30); Ole River (Ono Island) frontage (+15); high-confidence phone (+30). Absentee owner (Robertsdale; owns Farm Fresh Meats); $2.1M Ono Island waterfront. In direct landfall corridor per NHC Oct 7 advisory - Tropical Storm Isaias landfall expected near AL/FL border Friday night.</t>
+          <t>Score 80: $1.1M last sale (2004) (+30), direct Bayou Texar frontage — 150 ft waterfront (+25), owner-occupied (+10), low-confidence phone (+15, office line). 6,740 sf, 5bd/7ba on 1.1 acres — max tree/debris exposure. In direct landfall corridor per NHC 1pm Oct 7 advisory — landfall expected near AL/FL border Friday night.</t>
         </is>
       </c>
     </row>
@@ -4754,7 +4754,7 @@
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>TIER 1 - CALL FIRST</t>
+          <t>TIER 3 - NEW NUMBER (unverified)</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
@@ -4769,31 +4769,31 @@
       </c>
       <c r="E57" s="5" t="inlineStr">
         <is>
-          <t>La Bretonne Paula De</t>
+          <t>Bill J Ii &amp; Mary O Smith</t>
         </is>
       </c>
       <c r="F57" s="5" t="inlineStr">
         <is>
-          <t>35 BAYSHORE DR</t>
+          <t>793 BAYOU DR</t>
         </is>
       </c>
       <c r="G57" s="5" t="inlineStr">
         <is>
-          <t>SHALIMAR</t>
+          <t>DESTIN</t>
         </is>
       </c>
       <c r="H57" s="5" t="inlineStr">
         <is>
-          <t>850-651-4902</t>
+          <t>256-734-4473</t>
         </is>
       </c>
       <c r="I57" s="5" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="J57" s="6" t="n">
-        <v>1604523</v>
+        <v>6192452</v>
       </c>
       <c r="K57" s="5" t="inlineStr">
         <is>
@@ -4802,22 +4802,22 @@
       </c>
       <c r="L57" s="5" t="inlineStr">
         <is>
-          <t>Jonita Estates - bay</t>
+          <t>Joes Bayou waterfront</t>
         </is>
       </c>
       <c r="M57" s="5" t="inlineStr">
         <is>
-          <t>09-2S-23-1340-0001-0180</t>
+          <t>00-2S-22-1320-0000-01A0</t>
         </is>
       </c>
       <c r="N57" s="5" t="inlineStr">
         <is>
-          <t>11365 HIGHLAND RD, BATON ROUGE, LA 70810</t>
+          <t>1357 ASHFORD AVE STE 2 PMB 45, SAN JUAN, PR 00907</t>
         </is>
       </c>
       <c r="O57" s="5" t="inlineStr">
         <is>
-          <t>Ranked #21 of 69. Chosen from Okaloosa County Property Appraiser GIS (single-family use code 0100, assessed $1,604,523). Score 45 = $1.5M+ value (+15); bay/lagoon waterfront (+15); phone found via people-search (high confidence) (+15). Jonita Estates - bay. Second/vacation home (out-of-area mailing address) - absentee owner; storm damage still needs a local cleanup crew fast. In direct Isaias landfall corridor per NHC 1pm Oct 7 advisory (AL/FL border, landfall Fri night). Phone from free people-search aggregators - dial to verify before counting as qualified.</t>
+          <t>Ranked #45 of 69. Chosen from Okaloosa County Property Appraiser GIS (single-family use code 0100, assessed $6,192,452). Score 45 = $5M+ value (+30); bayou waterfront (+15). Joes Bayou waterfront. Second/vacation home (out-of-area mailing address) - absentee owner; storm damage still needs a local cleanup crew fast. In direct Isaias landfall corridor per NHC 1pm Oct 7 advisory (AL/FL border, landfall Fri night). No phone found in free sources.</t>
         </is>
       </c>
     </row>
@@ -4827,7 +4827,7 @@
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>TIER 1 - CALL FIRST</t>
+          <t>TIER 3 - NEW NUMBER (unverified)</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
@@ -4842,55 +4842,55 @@
       </c>
       <c r="E58" s="5" t="inlineStr">
         <is>
-          <t>Estela M Harrison</t>
+          <t>Sue C Dodge</t>
         </is>
       </c>
       <c r="F58" s="5" t="inlineStr">
         <is>
-          <t>70 MARLBOROUGH RD</t>
+          <t>7533 Gulf Blvd</t>
         </is>
       </c>
       <c r="G58" s="5" t="inlineStr">
         <is>
-          <t>SHALIMAR</t>
+          <t>Navarre Beach</t>
         </is>
       </c>
       <c r="H58" s="5" t="inlineStr">
         <is>
-          <t>850-651-4777</t>
+          <t>(773) 305-0707</t>
         </is>
       </c>
       <c r="I58" s="5" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="J58" s="6" t="n">
-        <v>1582500</v>
+        <v>2154050</v>
       </c>
       <c r="K58" s="5" t="inlineStr">
         <is>
-          <t>likely</t>
+          <t>no</t>
         </is>
       </c>
       <c r="L58" s="5" t="inlineStr">
         <is>
-          <t>Leyenda S/D</t>
+          <t>Gulf of Mexico</t>
         </is>
       </c>
       <c r="M58" s="5" t="inlineStr">
         <is>
-          <t>31-1S-23-1470-0002-0030</t>
+          <t>28-2S-26-9180-04900-0070</t>
         </is>
       </c>
       <c r="N58" s="5" t="inlineStr">
         <is>
-          <t>PO BOX 754, SHALIMAR, FL 32579</t>
+          <t>7533 Gulf Blvd, Navarre Beach, FL 32566</t>
         </is>
       </c>
       <c r="O58" s="5" t="inlineStr">
         <is>
-          <t>Ranked #27 of 69. Chosen from Okaloosa County Property Appraiser GIS (single-family use code 0100, assessed $1,582,500). Score 40 = $1.5M+ value (+15); owner-occupied (+10); phone found via people-search (high confidence) (+15). Leyenda S/D. Likely owner-occupied. In direct Isaias landfall corridor per NHC 1pm Oct 7 advisory (AL/FL border, landfall Fri night). Phone from free people-search aggregators - dial to verify before counting as qualified.</t>
+          <t>Score 70: $2.15M just value (+30), direct Gulf frontage (+25), medium-confidence phone (+15). Vacation rental ('Dodge Dunes') - absentee owner needs post-storm cleanup. In direct landfall corridor per NHC 1pm Oct 7 advisory - landfall expected near AL/FL border Friday night.</t>
         </is>
       </c>
     </row>
@@ -4900,7 +4900,7 @@
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>TIER 3 - NEW NUMBER (unverified)</t>
+          <t>TIER 1 - CALL FIRST</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
@@ -4915,31 +4915,31 @@
       </c>
       <c r="E59" s="5" t="inlineStr">
         <is>
-          <t>Melissa M Cole</t>
+          <t>Charles A Childress</t>
         </is>
       </c>
       <c r="F59" s="5" t="inlineStr">
         <is>
-          <t>718 SAILFISH DR</t>
+          <t>29024 Ono Blvd</t>
         </is>
       </c>
       <c r="G59" s="5" t="inlineStr">
         <is>
-          <t>FORT WALTON BEACH</t>
+          <t>Orange Beach</t>
         </is>
       </c>
       <c r="H59" s="5" t="inlineStr">
         <is>
-          <t>678-890-2868</t>
+          <t>2519477385</t>
         </is>
       </c>
       <c r="I59" s="5" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="J59" s="6" t="n">
-        <v>1532383</v>
+        <v>2089600</v>
       </c>
       <c r="K59" s="5" t="inlineStr">
         <is>
@@ -4948,22 +4948,22 @@
       </c>
       <c r="L59" s="5" t="inlineStr">
         <is>
-          <t>Santa Rosa Island (Okaloosa Island) - near Gulf</t>
+          <t>Ole River (Ono Island)</t>
         </is>
       </c>
       <c r="M59" s="5" t="inlineStr">
         <is>
-          <t>00-2S-24-2185-0007-0395</t>
+          <t>65-01-01-0-000-003.000</t>
         </is>
       </c>
       <c r="N59" s="5" t="inlineStr">
         <is>
-          <t>2250 LOVVORN RD, CARROLLTON, GA 30117</t>
+          <t>PO BOX 435, ROBERTSDALE, AL 36567-0435</t>
         </is>
       </c>
       <c r="O59" s="5" t="inlineStr">
         <is>
-          <t>Ranked #68 of 69. Chosen from Okaloosa County Property Appraiser GIS (single-family use code 0100, assessed $1,532,383). Score 15 = $1.5M+ value (+15). Santa Rosa Island (Okaloosa Island) - near Gulf. Second/vacation home (out-of-area mailing address) - absentee owner; storm damage still needs a local cleanup crew fast. In direct Isaias landfall corridor per NHC 1pm Oct 7 advisory (AL/FL border, landfall Fri night). No phone found in free sources.</t>
+          <t>Score 75: $2.09M county assessed value (+30); Ole River (Ono Island) frontage (+15); high-confidence phone (+30). Absentee owner (Robertsdale; owns Farm Fresh Meats); $2.1M Ono Island waterfront. In direct landfall corridor per NHC Oct 7 advisory - Tropical Storm Isaias landfall expected near AL/FL border Friday night.</t>
         </is>
       </c>
     </row>
@@ -4988,22 +4988,22 @@
       </c>
       <c r="E60" s="5" t="inlineStr">
         <is>
-          <t>Richard &amp; Helen Schneider</t>
+          <t>La Bretonne Paula De</t>
         </is>
       </c>
       <c r="F60" s="5" t="inlineStr">
         <is>
-          <t>1431 WESTERN LAKE DR</t>
+          <t>35 BAYSHORE DR</t>
         </is>
       </c>
       <c r="G60" s="5" t="inlineStr">
         <is>
-          <t>Santa Rosa Beach</t>
+          <t>SHALIMAR</t>
         </is>
       </c>
       <c r="H60" s="5" t="inlineStr">
         <is>
-          <t>4042649770</t>
+          <t>850-651-4902</t>
         </is>
       </c>
       <c r="I60" s="5" t="inlineStr">
@@ -5012,7 +5012,7 @@
         </is>
       </c>
       <c r="J60" s="6" t="n">
-        <v>1073506</v>
+        <v>1604523</v>
       </c>
       <c r="K60" s="5" t="inlineStr">
         <is>
@@ -5021,22 +5021,22 @@
       </c>
       <c r="L60" s="5" t="inlineStr">
         <is>
-          <t>Western Lake</t>
+          <t>Jonita Estates - bay</t>
         </is>
       </c>
       <c r="M60" s="5" t="inlineStr">
         <is>
-          <t>15-3S-19-25412-000-0290</t>
+          <t>09-2S-23-1340-0001-0180</t>
         </is>
       </c>
       <c r="N60" s="5" t="inlineStr">
         <is>
-          <t>1014 Brookhaven Ln NE, Atlanta, GA 30319</t>
+          <t>11365 HIGHLAND RD, BATON ROUGE, LA 70810</t>
         </is>
       </c>
       <c r="O60" s="5" t="inlineStr">
         <is>
-          <t>Score 60: $1.07M value (+30), high-confidence phone (+30). Western Lake waterfront; absentee owner (Atlanta). In eastern damage corridor per NHC Oct 7 advisory.</t>
+          <t>Ranked #21 of 69. Chosen from Okaloosa County Property Appraiser GIS (single-family use code 0100, assessed $1,604,523). Score 45 = $1.5M+ value (+15); bay/lagoon waterfront (+15); phone found via people-search (high confidence) (+15). Jonita Estates - bay. Second/vacation home (out-of-area mailing address) - absentee owner; storm damage still needs a local cleanup crew fast. In direct Isaias landfall corridor per NHC 1pm Oct 7 advisory (AL/FL border, landfall Fri night). Phone from free people-search aggregators - dial to verify before counting as qualified.</t>
         </is>
       </c>
     </row>
@@ -5061,22 +5061,22 @@
       </c>
       <c r="E61" s="5" t="inlineStr">
         <is>
-          <t>Jeffrey A Sesol</t>
+          <t>Estela M Harrison</t>
         </is>
       </c>
       <c r="F61" s="5" t="inlineStr">
         <is>
-          <t>1752 Villa Vizcaya Dr</t>
+          <t>70 MARLBOROUGH RD</t>
         </is>
       </c>
       <c r="G61" s="5" t="inlineStr">
         <is>
-          <t>Navarre</t>
+          <t>SHALIMAR</t>
         </is>
       </c>
       <c r="H61" s="5" t="inlineStr">
         <is>
-          <t>(708) 267-3408</t>
+          <t>850-651-4777</t>
         </is>
       </c>
       <c r="I61" s="5" t="inlineStr">
@@ -5085,31 +5085,31 @@
         </is>
       </c>
       <c r="J61" s="6" t="n">
-        <v>374238</v>
+        <v>1582500</v>
       </c>
       <c r="K61" s="5" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>likely</t>
         </is>
       </c>
       <c r="L61" s="5" t="inlineStr">
         <is>
-          <t>Santa Rosa Sound</t>
+          <t>Leyenda S/D</t>
         </is>
       </c>
       <c r="M61" s="5" t="inlineStr">
         <is>
-          <t>24-2S-27-5578-00D00-0050</t>
+          <t>31-1S-23-1470-0002-0030</t>
         </is>
       </c>
       <c r="N61" s="5" t="inlineStr">
         <is>
-          <t>1752 Villa Vizcaya Dr, Navarre, FL 32566</t>
+          <t>PO BOX 754, SHALIMAR, FL 32579</t>
         </is>
       </c>
       <c r="O61" s="5" t="inlineStr">
         <is>
-          <t>Score 60: high-confidence phone (+30), $374K assessed value (+10), owner-occupied (+10), HOA community (+10). In direct landfall corridor per NHC 1pm Oct 7 advisory - landfall expected near AL/FL border Friday night.</t>
+          <t>Ranked #27 of 69. Chosen from Okaloosa County Property Appraiser GIS (single-family use code 0100, assessed $1,582,500). Score 40 = $1.5M+ value (+15); owner-occupied (+10); phone found via people-search (high confidence) (+15). Leyenda S/D. Likely owner-occupied. In direct Isaias landfall corridor per NHC 1pm Oct 7 advisory (AL/FL border, landfall Fri night). Phone from free people-search aggregators - dial to verify before counting as qualified.</t>
         </is>
       </c>
     </row>
@@ -5119,7 +5119,7 @@
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>TIER 1 - CALL FIRST</t>
+          <t>TIER 3 - NEW NUMBER (unverified)</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
@@ -5134,51 +5134,55 @@
       </c>
       <c r="E62" s="5" t="inlineStr">
         <is>
-          <t>Joanne Gilmore</t>
+          <t>Melissa M Cole</t>
         </is>
       </c>
       <c r="F62" s="5" t="inlineStr">
         <is>
-          <t>3610 Bayou Blvd, Pensacola, FL 32503</t>
+          <t>718 SAILFISH DR</t>
         </is>
       </c>
       <c r="G62" s="5" t="inlineStr">
         <is>
-          <t>Pensacola</t>
+          <t>FORT WALTON BEACH</t>
         </is>
       </c>
       <c r="H62" s="5" t="inlineStr">
         <is>
-          <t>(850) 433-0886</t>
+          <t>678-890-2868</t>
         </is>
       </c>
       <c r="I62" s="5" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="J62" s="6" t="n">
-        <v>351254</v>
+        <v>1532383</v>
       </c>
       <c r="K62" s="5" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="L62" s="5" t="inlineStr">
         <is>
-          <t>Bayou Texar</t>
-        </is>
-      </c>
-      <c r="M62" s="5" t="inlineStr"/>
+          <t>Santa Rosa Island (Okaloosa Island) - near Gulf</t>
+        </is>
+      </c>
+      <c r="M62" s="5" t="inlineStr">
+        <is>
+          <t>00-2S-24-2185-0007-0395</t>
+        </is>
+      </c>
       <c r="N62" s="5" t="inlineStr">
         <is>
-          <t>3610 Bayou Blvd, Pensacola, FL 32503</t>
+          <t>2250 LOVVORN RD, CARROLLTON, GA 30117</t>
         </is>
       </c>
       <c r="O62" s="5" t="inlineStr">
         <is>
-          <t>Score 65: high-confidence phone — two sources agree (+30), ~$351K est. value (+10), Bayou Texar bayou-adjacent (+15), owner-occupied (+10). 1,820 sf ranch, 1955. In direct landfall corridor per NHC 1pm Oct 7 advisory — landfall expected near AL/FL border Friday night.</t>
+          <t>Ranked #68 of 69. Chosen from Okaloosa County Property Appraiser GIS (single-family use code 0100, assessed $1,532,383). Score 15 = $1.5M+ value (+15). Santa Rosa Island (Okaloosa Island) - near Gulf. Second/vacation home (out-of-area mailing address) - absentee owner; storm damage still needs a local cleanup crew fast. In direct Isaias landfall corridor per NHC 1pm Oct 7 advisory (AL/FL border, landfall Fri night). No phone found in free sources.</t>
         </is>
       </c>
     </row>
@@ -5188,7 +5192,7 @@
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>TIER 3 - NEW NUMBER (unverified)</t>
+          <t>TIER 1 - CALL FIRST</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
@@ -5203,55 +5207,55 @@
       </c>
       <c r="E63" s="5" t="inlineStr">
         <is>
-          <t>Christopher Carbone</t>
+          <t>Richard &amp; Helen Schneider</t>
         </is>
       </c>
       <c r="F63" s="5" t="inlineStr">
         <is>
-          <t>310 Gulfview Ln</t>
+          <t>1431 WESTERN LAKE DR</t>
         </is>
       </c>
       <c r="G63" s="5" t="inlineStr">
         <is>
-          <t>Perdido Key</t>
+          <t>Santa Rosa Beach</t>
         </is>
       </c>
       <c r="H63" s="5" t="inlineStr">
         <is>
-          <t>706-257-6601</t>
+          <t>4042649770</t>
         </is>
       </c>
       <c r="I63" s="5" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="J63" s="6" t="n">
-        <v>343000</v>
+        <v>1073506</v>
       </c>
       <c r="K63" s="5" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="L63" s="5" t="inlineStr">
         <is>
-          <t>Direct Gulf of Mexico frontage</t>
+          <t>Western Lake</t>
         </is>
       </c>
       <c r="M63" s="5" t="inlineStr">
         <is>
-          <t>064S320405002002</t>
+          <t>15-3S-19-25412-000-0290</t>
         </is>
       </c>
       <c r="N63" s="5" t="inlineStr">
         <is>
-          <t>310 Gulfview Ln, Pensacola, FL 32507</t>
+          <t>1014 Brookhaven Ln NE, Atlanta, GA 30319</t>
         </is>
       </c>
       <c r="O63" s="5" t="inlineStr">
         <is>
-          <t>Score 60: $343K value (+10), direct Gulf frontage (+25), owner-occupied (+10), medium-confidence phone (+15). In direct landfall corridor per NHC Oct 7 advisory.</t>
+          <t>Score 60: $1.07M value (+30), high-confidence phone (+30). Western Lake waterfront; absentee owner (Atlanta). In eastern damage corridor per NHC Oct 7 advisory.</t>
         </is>
       </c>
     </row>
@@ -5261,12 +5265,12 @@
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>TIER 3 - NEW NUMBER (unverified)</t>
+          <t>TIER 1 - CALL FIRST</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>75</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
@@ -5276,55 +5280,55 @@
       </c>
       <c r="E64" s="5" t="inlineStr">
         <is>
-          <t>Laura P &amp; Keith Howard</t>
+          <t>Jeffrey A Sesol</t>
         </is>
       </c>
       <c r="F64" s="5" t="inlineStr">
         <is>
-          <t>727 BAYOU DR</t>
+          <t>1752 Villa Vizcaya Dr</t>
         </is>
       </c>
       <c r="G64" s="5" t="inlineStr">
         <is>
-          <t>DESTIN</t>
+          <t>Navarre</t>
         </is>
       </c>
       <c r="H64" s="5" t="inlineStr">
         <is>
-          <t>850-837-8861</t>
+          <t>(708) 267-3408</t>
         </is>
       </c>
       <c r="I64" s="5" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="J64" s="6" t="n">
-        <v>4672061</v>
+        <v>374238</v>
       </c>
       <c r="K64" s="5" t="inlineStr">
         <is>
-          <t>likely</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="L64" s="5" t="inlineStr">
         <is>
-          <t>Joes Bayou waterfront</t>
+          <t>Santa Rosa Sound</t>
         </is>
       </c>
       <c r="M64" s="5" t="inlineStr">
         <is>
-          <t>00-2S-22-1320-0025-0000</t>
+          <t>24-2S-27-5578-00D00-0050</t>
         </is>
       </c>
       <c r="N64" s="5" t="inlineStr">
         <is>
-          <t>PO BOX 5919, DESTIN, FL 32540</t>
+          <t>1752 Villa Vizcaya Dr, Navarre, FL 32566</t>
         </is>
       </c>
       <c r="O64" s="5" t="inlineStr">
         <is>
-          <t>Ranked #32 of 69. Chosen from Okaloosa County Property Appraiser GIS (single-family use code 0100, assessed $4,672,061). Score 50 = $3M+ value (+25); bayou waterfront (+15); owner-occupied (+10). Joes Bayou waterfront. Likely owner-occupied. In direct Isaias landfall corridor per NHC 1pm Oct 7 advisory (AL/FL border, landfall Fri night). No phone found in free sources.</t>
+          <t>Score 60: high-confidence phone (+30), $374K assessed value (+10), owner-occupied (+10), HOA community (+10). In direct landfall corridor per NHC 1pm Oct 7 advisory - landfall expected near AL/FL border Friday night.</t>
         </is>
       </c>
     </row>
@@ -5334,12 +5338,12 @@
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>TIER 3 - NEW NUMBER (unverified)</t>
+          <t>TIER 1 - CALL FIRST</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>75</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
@@ -5349,55 +5353,51 @@
       </c>
       <c r="E65" s="5" t="inlineStr">
         <is>
-          <t>Edward D A &amp; Michelle L Sommer</t>
+          <t>Joanne Gilmore</t>
         </is>
       </c>
       <c r="F65" s="5" t="inlineStr">
         <is>
-          <t>82 HUTCHINSON ST</t>
+          <t>3610 Bayou Blvd, Pensacola, FL 32503</t>
         </is>
       </c>
       <c r="G65" s="5" t="inlineStr">
         <is>
-          <t>DESTIN</t>
+          <t>Pensacola</t>
         </is>
       </c>
       <c r="H65" s="5" t="inlineStr">
         <is>
-          <t>951-288-3783</t>
+          <t>(850) 433-0886</t>
         </is>
       </c>
       <c r="I65" s="5" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="J65" s="6" t="n">
-        <v>4436239</v>
+        <v>351254</v>
       </c>
       <c r="K65" s="5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="L65" s="5" t="inlineStr">
         <is>
-          <t>Hutchinson Courts</t>
-        </is>
-      </c>
-      <c r="M65" s="5" t="inlineStr">
-        <is>
-          <t>00-2S-22-5445-0000-0030</t>
-        </is>
-      </c>
+          <t>Bayou Texar</t>
+        </is>
+      </c>
+      <c r="M65" s="5" t="inlineStr"/>
       <c r="N65" s="5" t="inlineStr">
         <is>
-          <t>5340 MUIRFIELD CT, DUBLIN, OH 43017</t>
+          <t>3610 Bayou Blvd, Pensacola, FL 32503</t>
         </is>
       </c>
       <c r="O65" s="5" t="inlineStr">
         <is>
-          <t>Ranked #22 of 69. Chosen from Okaloosa County Property Appraiser GIS (single-family use code 0100, assessed $4,436,239). Score 40 = $3M+ value (+25); phone found via people-search (medium confidence) (+15). Hutchinson Courts. Second/vacation home (out-of-area mailing address) - absentee owner; storm damage still needs a local cleanup crew fast. In direct Isaias landfall corridor per NHC 1pm Oct 7 advisory (AL/FL border, landfall Fri night). Phone from free people-search aggregators - dial to verify before counting as qualified.</t>
+          <t>Score 65: high-confidence phone — two sources agree (+30), ~$351K est. value (+10), Bayou Texar bayou-adjacent (+15), owner-occupied (+10). 1,820 sf ranch, 1955. In direct landfall corridor per NHC 1pm Oct 7 advisory — landfall expected near AL/FL border Friday night.</t>
         </is>
       </c>
     </row>
@@ -5412,7 +5412,7 @@
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>75</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
@@ -5422,22 +5422,22 @@
       </c>
       <c r="E66" s="5" t="inlineStr">
         <is>
-          <t>Keith A &amp; Sheila Craft</t>
+          <t>Christopher Carbone</t>
         </is>
       </c>
       <c r="F66" s="5" t="inlineStr">
         <is>
-          <t>3973 INDIAN TRL</t>
+          <t>310 Gulfview Ln</t>
         </is>
       </c>
       <c r="G66" s="5" t="inlineStr">
         <is>
-          <t>DESTIN</t>
+          <t>Perdido Key</t>
         </is>
       </c>
       <c r="H66" s="5" t="inlineStr">
         <is>
-          <t>214-387-9833</t>
+          <t>706-257-6601</t>
         </is>
       </c>
       <c r="I66" s="5" t="inlineStr">
@@ -5446,31 +5446,31 @@
         </is>
       </c>
       <c r="J66" s="6" t="n">
-        <v>4086761</v>
+        <v>343000</v>
       </c>
       <c r="K66" s="5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="L66" s="5" t="inlineStr">
         <is>
-          <t>Indian Trail - near bay</t>
+          <t>Direct Gulf of Mexico frontage</t>
         </is>
       </c>
       <c r="M66" s="5" t="inlineStr">
         <is>
-          <t>00-2S-22-0000-0044-0170</t>
+          <t>064S320405002002</t>
         </is>
       </c>
       <c r="N66" s="5" t="inlineStr">
         <is>
-          <t>3245 MAIN ST SUITE 235 #180, FRISCO, TX 75034</t>
+          <t>310 Gulfview Ln, Pensacola, FL 32507</t>
         </is>
       </c>
       <c r="O66" s="5" t="inlineStr">
         <is>
-          <t>Ranked #48 of 69. Chosen from Okaloosa County Property Appraiser GIS (single-family use code 0100, assessed $4,086,761). Score 40 = $3M+ value (+25); bay/lagoon waterfront (+15). Indian Trail - near bay. Second/vacation home (out-of-area mailing address) - absentee owner; storm damage still needs a local cleanup crew fast. In direct Isaias landfall corridor per NHC 1pm Oct 7 advisory (AL/FL border, landfall Fri night). No phone found in free sources.</t>
+          <t>Score 60: $343K value (+10), direct Gulf frontage (+25), owner-occupied (+10), medium-confidence phone (+15). In direct landfall corridor per NHC Oct 7 advisory.</t>
         </is>
       </c>
     </row>
@@ -5495,22 +5495,22 @@
       </c>
       <c r="E67" s="5" t="inlineStr">
         <is>
-          <t>Robert E Allende</t>
+          <t>Laura P &amp; Keith Howard</t>
         </is>
       </c>
       <c r="F67" s="5" t="inlineStr">
         <is>
-          <t>28220 Burkart Dr</t>
+          <t>727 BAYOU DR</t>
         </is>
       </c>
       <c r="G67" s="5" t="inlineStr">
         <is>
-          <t>Orange Beach</t>
+          <t>DESTIN</t>
         </is>
       </c>
       <c r="H67" s="5" t="inlineStr">
         <is>
-          <t>5044275615</t>
+          <t>850-837-8861</t>
         </is>
       </c>
       <c r="I67" s="5" t="inlineStr">
@@ -5519,31 +5519,31 @@
         </is>
       </c>
       <c r="J67" s="6" t="n">
-        <v>3063700</v>
+        <v>4672061</v>
       </c>
       <c r="K67" s="5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>likely</t>
         </is>
       </c>
       <c r="L67" s="5" t="inlineStr">
         <is>
-          <t>Terry Cove / Ole River</t>
+          <t>Joes Bayou waterfront</t>
         </is>
       </c>
       <c r="M67" s="5" t="inlineStr">
         <is>
-          <t>65-02-12-0-000-216.000</t>
+          <t>00-2S-22-1320-0025-0000</t>
         </is>
       </c>
       <c r="N67" s="5" t="inlineStr">
         <is>
-          <t>4399 WILLIAM SILVERS PKWY, ORANGE BEACH, AL 36561-4336</t>
+          <t>PO BOX 5919, DESTIN, FL 32540</t>
         </is>
       </c>
       <c r="O67" s="5" t="inlineStr">
         <is>
-          <t>Score 60: $3.06M county assessed value (+30); Terry Cove / Ole River frontage (+15); medium-confidence phone (+15). Burkart Estates waterfront w/ deeded boat-ramp interest; owner mailing in Orange Beach; $3.06M assessed. In direct landfall corridor per NHC Oct 7 advisory - Tropical Storm Isaias landfall expected near AL/FL border Friday night.</t>
+          <t>Ranked #32 of 69. Chosen from Okaloosa County Property Appraiser GIS (single-family use code 0100, assessed $4,672,061). Score 50 = $3M+ value (+25); bayou waterfront (+15); owner-occupied (+10). Joes Bayou waterfront. Likely owner-occupied. In direct Isaias landfall corridor per NHC 1pm Oct 7 advisory (AL/FL border, landfall Fri night). No phone found in free sources.</t>
         </is>
       </c>
     </row>
@@ -5568,51 +5568,55 @@
       </c>
       <c r="E68" s="5" t="inlineStr">
         <is>
-          <t>Nancy Dunlap</t>
+          <t>Edward D A &amp; Michelle L Sommer</t>
         </is>
       </c>
       <c r="F68" s="5" t="inlineStr">
         <is>
-          <t>1302 Panferio Dr</t>
+          <t>82 HUTCHINSON ST</t>
         </is>
       </c>
       <c r="G68" s="5" t="inlineStr">
         <is>
-          <t>Pensacola Beach</t>
+          <t>DESTIN</t>
         </is>
       </c>
       <c r="H68" s="5" t="inlineStr">
         <is>
-          <t>(407) 282-4585</t>
+          <t>951-288-3783</t>
         </is>
       </c>
       <c r="I68" s="5" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="J68" s="6" t="n">
-        <v>710000</v>
+        <v>4436239</v>
       </c>
       <c r="K68" s="5" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="L68" s="5" t="inlineStr">
         <is>
-          <t>Santa Rosa Sound</t>
+          <t>Hutchinson Courts</t>
         </is>
       </c>
       <c r="M68" s="5" t="inlineStr">
         <is>
-          <t>28-2S-26-2150-070-049</t>
-        </is>
-      </c>
-      <c r="N68" s="5" t="inlineStr"/>
+          <t>00-2S-22-5445-0000-0030</t>
+        </is>
+      </c>
+      <c r="N68" s="5" t="inlineStr">
+        <is>
+          <t>5340 MUIRFIELD CT, DUBLIN, OH 43017</t>
+        </is>
+      </c>
       <c r="O68" s="5" t="inlineStr">
         <is>
-          <t>Score 75: direct Santa Rosa Sound frontage (+25), $710K 2023 sale value (+25), owner-occupied homestead (+10), low-confidence phone (+15). 1968 cottage — wind-vulnerable roof. In direct landfall corridor per NHC 1pm Oct 7 advisory — landfall expected near AL/FL border Friday night.</t>
+          <t>Ranked #22 of 69. Chosen from Okaloosa County Property Appraiser GIS (single-family use code 0100, assessed $4,436,239). Score 40 = $3M+ value (+25); phone found via people-search (medium confidence) (+15). Hutchinson Courts. Second/vacation home (out-of-area mailing address) - absentee owner; storm damage still needs a local cleanup crew fast. In direct Isaias landfall corridor per NHC 1pm Oct 7 advisory (AL/FL border, landfall Fri night). Phone from free people-search aggregators - dial to verify before counting as qualified.</t>
         </is>
       </c>
     </row>
@@ -5627,7 +5631,7 @@
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>70</t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr">
@@ -5637,22 +5641,22 @@
       </c>
       <c r="E69" s="5" t="inlineStr">
         <is>
-          <t>Aaron W Moody And Amy F Moody</t>
+          <t>Keith A &amp; Sheila Craft</t>
         </is>
       </c>
       <c r="F69" s="5" t="inlineStr">
         <is>
-          <t>27535 Beach Blvd E</t>
+          <t>3973 INDIAN TRL</t>
         </is>
       </c>
       <c r="G69" s="5" t="inlineStr">
         <is>
-          <t>Orange Beach</t>
+          <t>DESTIN</t>
         </is>
       </c>
       <c r="H69" s="5" t="inlineStr">
         <is>
-          <t>9047829831</t>
+          <t>214-387-9833</t>
         </is>
       </c>
       <c r="I69" s="5" t="inlineStr">
@@ -5661,7 +5665,7 @@
         </is>
       </c>
       <c r="J69" s="6" t="n">
-        <v>2807000</v>
+        <v>4086761</v>
       </c>
       <c r="K69" s="5" t="inlineStr">
         <is>
@@ -5670,22 +5674,22 @@
       </c>
       <c r="L69" s="5" t="inlineStr">
         <is>
-          <t>Bay La Launch</t>
+          <t>Indian Trail - near bay</t>
         </is>
       </c>
       <c r="M69" s="5" t="inlineStr">
         <is>
-          <t>62-07-36-0-002-012.000</t>
+          <t>00-2S-22-0000-0044-0170</t>
         </is>
       </c>
       <c r="N69" s="5" t="inlineStr">
         <is>
-          <t>470 GILHAM RD, ROANOKE, AL 36274-5614</t>
+          <t>3245 MAIN ST SUITE 235 #180, FRISCO, TX 75034</t>
         </is>
       </c>
       <c r="O69" s="5" t="inlineStr">
         <is>
-          <t>Score 60: $2.81M county assessed value (+30); Bay La Launch frontage (+15); medium-confidence phone (+15). Absentee owners (Roanoke AL); $2.8M waterfront estate. In direct landfall corridor per NHC Oct 7 advisory - Tropical Storm Isaias landfall expected near AL/FL border Friday night.</t>
+          <t>Ranked #48 of 69. Chosen from Okaloosa County Property Appraiser GIS (single-family use code 0100, assessed $4,086,761). Score 40 = $3M+ value (+25); bay/lagoon waterfront (+15). Indian Trail - near bay. Second/vacation home (out-of-area mailing address) - absentee owner; storm damage still needs a local cleanup crew fast. In direct Isaias landfall corridor per NHC 1pm Oct 7 advisory (AL/FL border, landfall Fri night). No phone found in free sources.</t>
         </is>
       </c>
     </row>
@@ -5700,7 +5704,7 @@
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>70</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
@@ -5710,22 +5714,22 @@
       </c>
       <c r="E70" s="5" t="inlineStr">
         <is>
-          <t>Robert J Trust Norton</t>
+          <t>Robert E Allende</t>
         </is>
       </c>
       <c r="F70" s="5" t="inlineStr">
         <is>
-          <t>83 POQUITO RD</t>
+          <t>28220 Burkart Dr</t>
         </is>
       </c>
       <c r="G70" s="5" t="inlineStr">
         <is>
-          <t>SHALIMAR</t>
+          <t>Orange Beach</t>
         </is>
       </c>
       <c r="H70" s="5" t="inlineStr">
         <is>
-          <t>951-656-2238</t>
+          <t>5044275615</t>
         </is>
       </c>
       <c r="I70" s="5" t="inlineStr">
@@ -5734,7 +5738,7 @@
         </is>
       </c>
       <c r="J70" s="6" t="n">
-        <v>2080818</v>
+        <v>3063700</v>
       </c>
       <c r="K70" s="5" t="inlineStr">
         <is>
@@ -5743,22 +5747,22 @@
       </c>
       <c r="L70" s="5" t="inlineStr">
         <is>
-          <t>Bayou Poquito waterfront</t>
+          <t>Terry Cove / Ole River</t>
         </is>
       </c>
       <c r="M70" s="5" t="inlineStr">
         <is>
-          <t>31-1S-23-0120-0016-0420</t>
+          <t>65-02-12-0-000-216.000</t>
         </is>
       </c>
       <c r="N70" s="5" t="inlineStr">
         <is>
-          <t>6477 BOX SPRINGS BLVD, RIVERSIDE, CA 92507</t>
+          <t>4399 WILLIAM SILVERS PKWY, ORANGE BEACH, AL 36561-4336</t>
         </is>
       </c>
       <c r="O70" s="5" t="inlineStr">
         <is>
-          <t>Trustee: Robert J. Norton. $2.1M assessed Bayou Poquito waterfront; absentee CA property investor; needs local storm response crew Ranked #59 of 69. Chosen from Okaloosa County Property Appraiser GIS (single-family use code 0100, assessed $2,080,818). Score 35 = $2M+ value (+20); bayou waterfront (+15). Bayou Poquito waterfront. Second/vacation home (out-of-area mailing address) - absentee owner; storm damage still needs a local cleanup crew fast. In direct Isaias landfall corridor per NHC 1pm Oct 7 advisory (AL/FL border, landfall Fri night). No phone found in free sources.</t>
+          <t>Score 60: $3.06M county assessed value (+30); Terry Cove / Ole River frontage (+15); medium-confidence phone (+15). Burkart Estates waterfront w/ deeded boat-ramp interest; owner mailing in Orange Beach; $3.06M assessed. In direct landfall corridor per NHC Oct 7 advisory - Tropical Storm Isaias landfall expected near AL/FL border Friday night.</t>
         </is>
       </c>
     </row>
@@ -5773,7 +5777,7 @@
       </c>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>70</t>
         </is>
       </c>
       <c r="D71" s="5" t="inlineStr">
@@ -5783,55 +5787,51 @@
       </c>
       <c r="E71" s="5" t="inlineStr">
         <is>
-          <t>John A Mantle And Pamela M Mantle</t>
+          <t>Nancy Dunlap</t>
         </is>
       </c>
       <c r="F71" s="5" t="inlineStr">
         <is>
-          <t>28575 Perdido Pass Dr</t>
+          <t>1302 Panferio Dr</t>
         </is>
       </c>
       <c r="G71" s="5" t="inlineStr">
         <is>
-          <t>Orange Beach</t>
+          <t>Pensacola Beach</t>
         </is>
       </c>
       <c r="H71" s="5" t="inlineStr">
         <is>
-          <t>2055567870</t>
+          <t>(407) 282-4585</t>
         </is>
       </c>
       <c r="I71" s="5" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>low</t>
         </is>
       </c>
       <c r="J71" s="6" t="n">
-        <v>1864900</v>
+        <v>710000</v>
       </c>
       <c r="K71" s="5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="L71" s="5" t="inlineStr">
         <is>
-          <t>Perdido Pass (Ono Island)</t>
+          <t>Santa Rosa Sound</t>
         </is>
       </c>
       <c r="M71" s="5" t="inlineStr">
         <is>
-          <t>65-01-11-0-000-030.043</t>
-        </is>
-      </c>
-      <c r="N71" s="5" t="inlineStr">
-        <is>
-          <t>214 THE HIGHLANDS, TUSCALOOSA, AL 35404</t>
-        </is>
-      </c>
+          <t>28-2S-26-2150-070-049</t>
+        </is>
+      </c>
+      <c r="N71" s="5" t="inlineStr"/>
       <c r="O71" s="5" t="inlineStr">
         <is>
-          <t>Score 60: $1.86M county assessed value (+30); Perdido Pass (Ono Island) frontage (+15); medium-confidence phone (+15). Absentee owners (Tuscaloosa); $1.86M Perdido Pass waterfront. Phone listed under co-owner Pamela Mantle. In direct landfall corridor per NHC Oct 7 advisory - Tropical Storm Isaias landfall expected near AL/FL border Friday night.</t>
+          <t>Score 75: direct Santa Rosa Sound frontage (+25), $710K 2023 sale value (+25), owner-occupied homestead (+10), low-confidence phone (+15). 1968 cottage — wind-vulnerable roof. In direct landfall corridor per NHC 1pm Oct 7 advisory — landfall expected near AL/FL border Friday night.</t>
         </is>
       </c>
     </row>
@@ -5856,22 +5856,22 @@
       </c>
       <c r="E72" s="5" t="inlineStr">
         <is>
-          <t>Dennis P &amp; Gabriele Terens</t>
+          <t>Aaron W Moody And Amy F Moody</t>
         </is>
       </c>
       <c r="F72" s="5" t="inlineStr">
         <is>
-          <t>144 Monahan Dr</t>
+          <t>27535 Beach Blvd E</t>
         </is>
       </c>
       <c r="G72" s="5" t="inlineStr">
         <is>
-          <t>Fort Walton Beach</t>
+          <t>Orange Beach</t>
         </is>
       </c>
       <c r="H72" s="5" t="inlineStr">
         <is>
-          <t>978-772-7247</t>
+          <t>9047829831</t>
         </is>
       </c>
       <c r="I72" s="5" t="inlineStr">
@@ -5880,31 +5880,31 @@
         </is>
       </c>
       <c r="J72" s="6" t="n">
-        <v>1600000</v>
+        <v>2807000</v>
       </c>
       <c r="K72" s="5" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>no</t>
         </is>
       </c>
       <c r="L72" s="5" t="inlineStr">
         <is>
-          <t>Cinco Bayou waterfront</t>
+          <t>Bay La Launch</t>
         </is>
       </c>
       <c r="M72" s="5" t="inlineStr">
         <is>
-          <t>122S24021000030160</t>
+          <t>62-07-36-0-002-012.000</t>
         </is>
       </c>
       <c r="N72" s="5" t="inlineStr">
         <is>
-          <t>144 Monahan Dr, Fort Walton Beach, FL 32547</t>
+          <t>470 GILHAM RD, ROANOKE, AL 36274-5614</t>
         </is>
       </c>
       <c r="O72" s="5" t="inlineStr">
         <is>
-          <t>Score 60: $1.6M active listing (+30), bayou frontage (+15), medium-confidence phone (+15). 1947 Bella Vista waterfront estate. In direct landfall corridor per NHC Oct 7 advisory.</t>
+          <t>Score 60: $2.81M county assessed value (+30); Bay La Launch frontage (+15); medium-confidence phone (+15). Absentee owners (Roanoke AL); $2.8M waterfront estate. In direct landfall corridor per NHC Oct 7 advisory - Tropical Storm Isaias landfall expected near AL/FL border Friday night.</t>
         </is>
       </c>
     </row>
@@ -5929,22 +5929,22 @@
       </c>
       <c r="E73" s="5" t="inlineStr">
         <is>
-          <t>Robert B Swift</t>
+          <t>Robert J Trust Norton</t>
         </is>
       </c>
       <c r="F73" s="5" t="inlineStr">
         <is>
-          <t>3361 Edgewater Dr</t>
+          <t>83 POQUITO RD</t>
         </is>
       </c>
       <c r="G73" s="5" t="inlineStr">
         <is>
-          <t>Gulf Breeze</t>
+          <t>SHALIMAR</t>
         </is>
       </c>
       <c r="H73" s="5" t="inlineStr">
         <is>
-          <t>8509345757</t>
+          <t>951-656-2238</t>
         </is>
       </c>
       <c r="I73" s="5" t="inlineStr">
@@ -5953,31 +5953,31 @@
         </is>
       </c>
       <c r="J73" s="6" t="n">
-        <v>1469314</v>
+        <v>2080818</v>
       </c>
       <c r="K73" s="5" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>no</t>
         </is>
       </c>
       <c r="L73" s="5" t="inlineStr">
         <is>
-          <t>Santa Rosa Sound</t>
+          <t>Bayou Poquito waterfront</t>
         </is>
       </c>
       <c r="M73" s="5" t="inlineStr">
         <is>
-          <t>32-2S-28-4760-00500-0030</t>
+          <t>31-1S-23-0120-0016-0420</t>
         </is>
       </c>
       <c r="N73" s="5" t="inlineStr">
         <is>
-          <t>3361 Edgewater Dr, Gulf Breeze, FL 32563</t>
+          <t>6477 BOX SPRINGS BLVD, RIVERSIDE, CA 92507</t>
         </is>
       </c>
       <c r="O73" s="5" t="inlineStr">
         <is>
-          <t>Score 70: direct Santa Rosa Sound waterfront (+25), $1.47M assessed value (+30), medium-confidence phone (+15). 5bd/5ba 3,472 sqft on 0.37 acre, bought Sep 2016; currently listed for sale — motivated owner. In direct landfall corridor per NHC 1pm Oct 7 advisory — landfall expected near AL/FL border Friday night.</t>
+          <t>Trustee: Robert J. Norton. $2.1M assessed Bayou Poquito waterfront; absentee CA property investor; needs local storm response crew Ranked #59 of 69. Chosen from Okaloosa County Property Appraiser GIS (single-family use code 0100, assessed $2,080,818). Score 35 = $2M+ value (+20); bayou waterfront (+15). Bayou Poquito waterfront. Second/vacation home (out-of-area mailing address) - absentee owner; storm damage still needs a local cleanup crew fast. In direct Isaias landfall corridor per NHC 1pm Oct 7 advisory (AL/FL border, landfall Fri night). No phone found in free sources.</t>
         </is>
       </c>
     </row>
@@ -6002,12 +6002,12 @@
       </c>
       <c r="E74" s="5" t="inlineStr">
         <is>
-          <t>Henry M Kwong And Catherine O Kwong</t>
+          <t>John A Mantle And Pamela M Mantle</t>
         </is>
       </c>
       <c r="F74" s="5" t="inlineStr">
         <is>
-          <t>29149 Ono Blvd</t>
+          <t>28575 Perdido Pass Dr</t>
         </is>
       </c>
       <c r="G74" s="5" t="inlineStr">
@@ -6017,7 +6017,7 @@
       </c>
       <c r="H74" s="5" t="inlineStr">
         <is>
-          <t>3373654200</t>
+          <t>2055567870</t>
         </is>
       </c>
       <c r="I74" s="5" t="inlineStr">
@@ -6026,7 +6026,7 @@
         </is>
       </c>
       <c r="J74" s="6" t="n">
-        <v>1404600</v>
+        <v>1864900</v>
       </c>
       <c r="K74" s="5" t="inlineStr">
         <is>
@@ -6035,22 +6035,22 @@
       </c>
       <c r="L74" s="5" t="inlineStr">
         <is>
-          <t>Ole River (Ono Island)</t>
+          <t>Perdido Pass (Ono Island)</t>
         </is>
       </c>
       <c r="M74" s="5" t="inlineStr">
         <is>
-          <t>65-01-01-0-000-001.071</t>
+          <t>65-01-11-0-000-030.043</t>
         </is>
       </c>
       <c r="N74" s="5" t="inlineStr">
         <is>
-          <t>209 INTERLAKEN DR, NEW IBERIA, LA 70563-1233</t>
+          <t>214 THE HIGHLANDS, TUSCALOOSA, AL 35404</t>
         </is>
       </c>
       <c r="O74" s="5" t="inlineStr">
         <is>
-          <t>Score 60: $1.40M county assessed value (+30); Ole River (Ono Island) frontage (+15); medium-confidence phone (+15). Absentee owners (New Iberia LA); $1.4M Ono Island waterfront. In direct landfall corridor per NHC Oct 7 advisory - Tropical Storm Isaias landfall expected near AL/FL border Friday night.</t>
+          <t>Score 60: $1.86M county assessed value (+30); Perdido Pass (Ono Island) frontage (+15); medium-confidence phone (+15). Absentee owners (Tuscaloosa); $1.86M Perdido Pass waterfront. Phone listed under co-owner Pamela Mantle. In direct landfall corridor per NHC Oct 7 advisory - Tropical Storm Isaias landfall expected near AL/FL border Friday night.</t>
         </is>
       </c>
     </row>
@@ -6075,22 +6075,22 @@
       </c>
       <c r="E75" s="5" t="inlineStr">
         <is>
-          <t>Steven J Savard</t>
+          <t>Dennis P &amp; Gabriele Terens</t>
         </is>
       </c>
       <c r="F75" s="5" t="inlineStr">
         <is>
-          <t>1215 Panferio Dr</t>
+          <t>144 Monahan Dr</t>
         </is>
       </c>
       <c r="G75" s="5" t="inlineStr">
         <is>
-          <t>Pensacola Beach</t>
+          <t>Fort Walton Beach</t>
         </is>
       </c>
       <c r="H75" s="5" t="inlineStr">
         <is>
-          <t>(253) 318-5026</t>
+          <t>978-772-7247</t>
         </is>
       </c>
       <c r="I75" s="5" t="inlineStr">
@@ -6099,7 +6099,7 @@
         </is>
       </c>
       <c r="J75" s="6" t="n">
-        <v>1262247</v>
+        <v>1600000</v>
       </c>
       <c r="K75" s="5" t="inlineStr">
         <is>
@@ -6108,22 +6108,22 @@
       </c>
       <c r="L75" s="5" t="inlineStr">
         <is>
-          <t>Santa Rosa Sound</t>
+          <t>Cinco Bayou waterfront</t>
         </is>
       </c>
       <c r="M75" s="5" t="inlineStr">
         <is>
-          <t>282S262150001051</t>
+          <t>122S24021000030160</t>
         </is>
       </c>
       <c r="N75" s="5" t="inlineStr">
         <is>
-          <t>387 Echo Cir Fort Walton Beach FL 32548</t>
+          <t>144 Monahan Dr, Fort Walton Beach, FL 32547</t>
         </is>
       </c>
       <c r="O75" s="5" t="inlineStr">
         <is>
-          <t>Score 70: direct Santa Rosa Sound frontage (+25), $1.26M assessed value (+30), medium-confidence phone (+15). Sound-side dock permitted 2020. In direct landfall corridor per NHC 1pm Oct 7 advisory — landfall expected near AL/FL border Friday night.</t>
+          <t>Score 60: $1.6M active listing (+30), bayou frontage (+15), medium-confidence phone (+15). 1947 Bella Vista waterfront estate. In direct landfall corridor per NHC Oct 7 advisory.</t>
         </is>
       </c>
     </row>
@@ -6148,12 +6148,12 @@
       </c>
       <c r="E76" s="5" t="inlineStr">
         <is>
-          <t>Robert Michael Scileppi (Scileppi Revocable Trust)</t>
+          <t>Robert B Swift</t>
         </is>
       </c>
       <c r="F76" s="5" t="inlineStr">
         <is>
-          <t>1139 Seabreeze Ln</t>
+          <t>3361 Edgewater Dr</t>
         </is>
       </c>
       <c r="G76" s="5" t="inlineStr">
@@ -6163,7 +6163,7 @@
       </c>
       <c r="H76" s="5" t="inlineStr">
         <is>
-          <t>850-285-0234</t>
+          <t>8509345757</t>
         </is>
       </c>
       <c r="I76" s="5" t="inlineStr">
@@ -6172,7 +6172,7 @@
         </is>
       </c>
       <c r="J76" s="6" t="n">
-        <v>1150000</v>
+        <v>1469314</v>
       </c>
       <c r="K76" s="5" t="inlineStr">
         <is>
@@ -6181,22 +6181,22 @@
       </c>
       <c r="L76" s="5" t="inlineStr">
         <is>
-          <t>Santa Rosa Sound (canal)</t>
+          <t>Santa Rosa Sound</t>
         </is>
       </c>
       <c r="M76" s="5" t="inlineStr">
         <is>
-          <t>32-2S-28-4730-00000-1560</t>
+          <t>32-2S-28-4760-00500-0030</t>
         </is>
       </c>
       <c r="N76" s="5" t="inlineStr">
         <is>
-          <t>1139 Seabreeze Ln, Gulf Breeze, FL 32563</t>
+          <t>3361 Edgewater Dr, Gulf Breeze, FL 32563</t>
         </is>
       </c>
       <c r="O76" s="5" t="inlineStr">
         <is>
-          <t>Score 55: $1.15M assessed value (+30), canal waterfront (+15), Santa Rosa Shores HOA community (+10). Bought Feb 2025; county canal assessments confirm canal frontage; 3bd/3ba (1980). In direct landfall corridor per NHC 1pm Oct 7 advisory — landfall expected near AL/FL border Friday night.</t>
+          <t>Score 70: direct Santa Rosa Sound waterfront (+25), $1.47M assessed value (+30), medium-confidence phone (+15). 5bd/5ba 3,472 sqft on 0.37 acre, bought Sep 2016; currently listed for sale — motivated owner. In direct landfall corridor per NHC 1pm Oct 7 advisory — landfall expected near AL/FL border Friday night.</t>
         </is>
       </c>
     </row>
@@ -6221,22 +6221,22 @@
       </c>
       <c r="E77" s="5" t="inlineStr">
         <is>
-          <t>James W Gilmore</t>
+          <t>Henry M Kwong And Catherine O Kwong</t>
         </is>
       </c>
       <c r="F77" s="5" t="inlineStr">
         <is>
-          <t>4409 Soundside Dr</t>
+          <t>29149 Ono Blvd</t>
         </is>
       </c>
       <c r="G77" s="5" t="inlineStr">
         <is>
-          <t>Gulf Breeze</t>
+          <t>Orange Beach</t>
         </is>
       </c>
       <c r="H77" s="5" t="inlineStr">
         <is>
-          <t>3863281975</t>
+          <t>3373654200</t>
         </is>
       </c>
       <c r="I77" s="5" t="inlineStr">
@@ -6244,34 +6244,32 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="J77" s="6" t="inlineStr">
-        <is>
-          <t>344200 (home value est; 2017 sale 400000)</t>
-        </is>
+      <c r="J77" s="6" t="n">
+        <v>1404600</v>
       </c>
       <c r="K77" s="5" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="L77" s="5" t="inlineStr">
         <is>
-          <t>Santa Rosa Sound</t>
+          <t>Ole River (Ono Island)</t>
         </is>
       </c>
       <c r="M77" s="5" t="inlineStr">
         <is>
-          <t>342S28515000H000030</t>
+          <t>65-01-01-0-000-001.071</t>
         </is>
       </c>
       <c r="N77" s="5" t="inlineStr">
         <is>
-          <t>4409 Soundside Dr Gulf Breeze FL 32563</t>
+          <t>209 INTERLAKEN DR, NEW IBERIA, LA 70563-1233</t>
         </is>
       </c>
       <c r="O77" s="5" t="inlineStr">
         <is>
-          <t>Score 60: direct Santa Rosa Sound waterfront (+25), ~$344K home value (+10), owner-occupied (+10), medium-confidence phone (+15). Older records show Bicker family; most recent data lists Gilmore. 3bd/2ba 2,236sf on 0.76ac. In direct landfall corridor per NHC 1pm Oct 7 advisory - landfall expected near AL/FL border Friday night.</t>
+          <t>Score 60: $1.40M county assessed value (+30); Ole River (Ono Island) frontage (+15); medium-confidence phone (+15). Absentee owners (New Iberia LA); $1.4M Ono Island waterfront. In direct landfall corridor per NHC Oct 7 advisory - Tropical Storm Isaias landfall expected near AL/FL border Friday night.</t>
         </is>
       </c>
     </row>
@@ -6296,22 +6294,22 @@
       </c>
       <c r="E78" s="5" t="inlineStr">
         <is>
-          <t>William E Graves</t>
+          <t>Steven J Savard</t>
         </is>
       </c>
       <c r="F78" s="5" t="inlineStr">
         <is>
-          <t>3426 Chantarene Dr, Pensacola, FL 32507</t>
+          <t>1215 Panferio Dr</t>
         </is>
       </c>
       <c r="G78" s="5" t="inlineStr">
         <is>
-          <t>Pensacola</t>
+          <t>Pensacola Beach</t>
         </is>
       </c>
       <c r="H78" s="5" t="inlineStr">
         <is>
-          <t>(850) 501-6286</t>
+          <t>(253) 318-5026</t>
         </is>
       </c>
       <c r="I78" s="5" t="inlineStr">
@@ -6320,31 +6318,31 @@
         </is>
       </c>
       <c r="J78" s="6" t="n">
-        <v>317500</v>
+        <v>1262247</v>
       </c>
       <c r="K78" s="5" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="L78" s="5" t="inlineStr">
         <is>
-          <t>Pensacola Bay (deeded access)</t>
+          <t>Santa Rosa Sound</t>
         </is>
       </c>
       <c r="M78" s="5" t="inlineStr">
         <is>
-          <t>50-2S-30-5082-004-008</t>
+          <t>282S262150001051</t>
         </is>
       </c>
       <c r="N78" s="5" t="inlineStr">
         <is>
-          <t>3426 Chantarene Dr, Pensacola, FL 32507</t>
+          <t>387 Echo Cir Fort Walton Beach FL 32548</t>
         </is>
       </c>
       <c r="O78" s="5" t="inlineStr">
         <is>
-          <t>Score 60: $317.5K last sale (2007) (+10), Pensacola Bay deeded waterfront access (+15), owner-occupied (+10), HOA community (+10), medium-confidence phone (+15). 1992-built home. In direct landfall corridor per NHC 1pm Oct 7 advisory — landfall expected near AL/FL border Friday night.</t>
+          <t>Score 70: direct Santa Rosa Sound frontage (+25), $1.26M assessed value (+30), medium-confidence phone (+15). Sound-side dock permitted 2020. In direct landfall corridor per NHC 1pm Oct 7 advisory — landfall expected near AL/FL border Friday night.</t>
         </is>
       </c>
     </row>
@@ -6369,22 +6367,22 @@
       </c>
       <c r="E79" s="5" t="inlineStr">
         <is>
-          <t>Debra Watts</t>
+          <t>Robert Michael Scileppi (Scileppi Revocable Trust)</t>
         </is>
       </c>
       <c r="F79" s="5" t="inlineStr">
         <is>
-          <t>3421 Chantarene Dr, Pensacola, FL 32507</t>
+          <t>1139 Seabreeze Ln</t>
         </is>
       </c>
       <c r="G79" s="5" t="inlineStr">
         <is>
-          <t>Pensacola</t>
+          <t>Gulf Breeze</t>
         </is>
       </c>
       <c r="H79" s="5" t="inlineStr">
         <is>
-          <t>(850) 516-5545</t>
+          <t>850-285-0234</t>
         </is>
       </c>
       <c r="I79" s="5" t="inlineStr">
@@ -6393,31 +6391,31 @@
         </is>
       </c>
       <c r="J79" s="6" t="n">
-        <v>306600</v>
+        <v>1150000</v>
       </c>
       <c r="K79" s="5" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="L79" s="5" t="inlineStr">
         <is>
-          <t>Pensacola Bay (deeded access)</t>
+          <t>Santa Rosa Sound (canal)</t>
         </is>
       </c>
       <c r="M79" s="5" t="inlineStr">
         <is>
-          <t>50-2S-30-5082-004-007</t>
+          <t>32-2S-28-4730-00000-1560</t>
         </is>
       </c>
       <c r="N79" s="5" t="inlineStr">
         <is>
-          <t>3421 Chantarene Dr, Pensacola, FL 32507</t>
+          <t>1139 Seabreeze Ln, Gulf Breeze, FL 32563</t>
         </is>
       </c>
       <c r="O79" s="5" t="inlineStr">
         <is>
-          <t>Score 60: $306.6K last sale (2009) (+10), Pensacola Bay deeded waterfront access (+15), owner-occupied (+10), HOA community (+10), medium-confidence phone (+15). 2004-built home. In direct landfall corridor per NHC 1pm Oct 7 advisory — landfall expected near AL/FL border Friday night.</t>
+          <t>Score 55: $1.15M assessed value (+30), canal waterfront (+15), Santa Rosa Shores HOA community (+10). Bought Feb 2025; county canal assessments confirm canal frontage; 3bd/3ba (1980). In direct landfall corridor per NHC 1pm Oct 7 advisory — landfall expected near AL/FL border Friday night.</t>
         </is>
       </c>
     </row>
@@ -6427,7 +6425,7 @@
       </c>
       <c r="B80" s="5" t="inlineStr">
         <is>
-          <t>TIER 2 - CALL TODAY</t>
+          <t>TIER 3 - NEW NUMBER (unverified)</t>
         </is>
       </c>
       <c r="C80" s="5" t="inlineStr">
@@ -6442,31 +6440,33 @@
       </c>
       <c r="E80" s="5" t="inlineStr">
         <is>
-          <t>John K Kepko</t>
+          <t>James W Gilmore</t>
         </is>
       </c>
       <c r="F80" s="5" t="inlineStr">
         <is>
-          <t>1757 Villa Vizcaya Dr</t>
+          <t>4409 Soundside Dr</t>
         </is>
       </c>
       <c r="G80" s="5" t="inlineStr">
         <is>
-          <t>Navarre</t>
+          <t>Gulf Breeze</t>
         </is>
       </c>
       <c r="H80" s="5" t="inlineStr">
         <is>
-          <t>(850) 240-4157</t>
+          <t>3863281975</t>
         </is>
       </c>
       <c r="I80" s="5" t="inlineStr">
         <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="J80" s="6" t="n">
-        <v>195500</v>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J80" s="6" t="inlineStr">
+        <is>
+          <t>344200 (home value est; 2017 sale 400000)</t>
+        </is>
       </c>
       <c r="K80" s="5" t="inlineStr">
         <is>
@@ -6480,17 +6480,17 @@
       </c>
       <c r="M80" s="5" t="inlineStr">
         <is>
-          <t>24-2S-27-5578-00A00-0070</t>
+          <t>342S28515000H000030</t>
         </is>
       </c>
       <c r="N80" s="5" t="inlineStr">
         <is>
-          <t>1757 Villa Vizcaya Dr, Navarre, FL 32566</t>
+          <t>4409 Soundside Dr Gulf Breeze FL 32563</t>
         </is>
       </c>
       <c r="O80" s="5" t="inlineStr">
         <is>
-          <t>Score 50: high-confidence phone (+30), owner-occupied (+10), HOA community (+10). Home-based business owner. In direct landfall corridor per NHC 1pm Oct 7 advisory - landfall expected near AL/FL border Friday night.</t>
+          <t>Score 60: direct Santa Rosa Sound waterfront (+25), ~$344K home value (+10), owner-occupied (+10), medium-confidence phone (+15). Older records show Bicker family; most recent data lists Gilmore. 3bd/2ba 2,236sf on 0.76ac. In direct landfall corridor per NHC 1pm Oct 7 advisory - landfall expected near AL/FL border Friday night.</t>
         </is>
       </c>
     </row>
@@ -6500,7 +6500,7 @@
       </c>
       <c r="B81" s="5" t="inlineStr">
         <is>
-          <t>TIER 2 - CALL TODAY</t>
+          <t>TIER 3 - NEW NUMBER (unverified)</t>
         </is>
       </c>
       <c r="C81" s="5" t="inlineStr">
@@ -6515,30 +6515,32 @@
       </c>
       <c r="E81" s="5" t="inlineStr">
         <is>
-          <t>Herbert D Ludwig</t>
+          <t>William E Graves</t>
         </is>
       </c>
       <c r="F81" s="5" t="inlineStr">
         <is>
-          <t>4407 Soundside Dr</t>
+          <t>3426 Chantarene Dr, Pensacola, FL 32507</t>
         </is>
       </c>
       <c r="G81" s="5" t="inlineStr">
         <is>
-          <t>Gulf Breeze</t>
+          <t>Pensacola</t>
         </is>
       </c>
       <c r="H81" s="5" t="inlineStr">
         <is>
-          <t>8509161129</t>
+          <t>(850) 501-6286</t>
         </is>
       </c>
       <c r="I81" s="5" t="inlineStr">
         <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="J81" s="6" t="inlineStr"/>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J81" s="6" t="n">
+        <v>317500</v>
+      </c>
       <c r="K81" s="5" t="inlineStr">
         <is>
           <t>yes</t>
@@ -6546,18 +6548,22 @@
       </c>
       <c r="L81" s="5" t="inlineStr">
         <is>
-          <t>Santa Rosa Sound</t>
-        </is>
-      </c>
-      <c r="M81" s="5" t="inlineStr"/>
+          <t>Pensacola Bay (deeded access)</t>
+        </is>
+      </c>
+      <c r="M81" s="5" t="inlineStr">
+        <is>
+          <t>50-2S-30-5082-004-008</t>
+        </is>
+      </c>
       <c r="N81" s="5" t="inlineStr">
         <is>
-          <t>4407 Soundside Dr Gulf Breeze FL 32563</t>
+          <t>3426 Chantarene Dr, Pensacola, FL 32507</t>
         </is>
       </c>
       <c r="O81" s="5" t="inlineStr">
         <is>
-          <t>Score 65: direct Santa Rosa Sound waterfront (+25), owner-occupied (+10), high-confidence phone (+30). Value not verified in public records; older owner (age ~88). In direct landfall corridor per NHC 1pm Oct 7 advisory - landfall expected near AL/FL border Friday night.</t>
+          <t>Score 60: $317.5K last sale (2007) (+10), Pensacola Bay deeded waterfront access (+15), owner-occupied (+10), HOA community (+10), medium-confidence phone (+15). 1992-built home. In direct landfall corridor per NHC 1pm Oct 7 advisory — landfall expected near AL/FL border Friday night.</t>
         </is>
       </c>
     </row>
@@ -6567,7 +6573,7 @@
       </c>
       <c r="B82" s="5" t="inlineStr">
         <is>
-          <t>TIER 2 - CALL TODAY</t>
+          <t>TIER 3 - NEW NUMBER (unverified)</t>
         </is>
       </c>
       <c r="C82" s="5" t="inlineStr">
@@ -6582,30 +6588,32 @@
       </c>
       <c r="E82" s="5" t="inlineStr">
         <is>
-          <t>Phillip Sandfort</t>
+          <t>Debra Watts</t>
         </is>
       </c>
       <c r="F82" s="5" t="inlineStr">
         <is>
-          <t>4623 Soundside Dr</t>
+          <t>3421 Chantarene Dr, Pensacola, FL 32507</t>
         </is>
       </c>
       <c r="G82" s="5" t="inlineStr">
         <is>
-          <t>Gulf Breeze</t>
+          <t>Pensacola</t>
         </is>
       </c>
       <c r="H82" s="5" t="inlineStr">
         <is>
-          <t>8509322098</t>
+          <t>(850) 516-5545</t>
         </is>
       </c>
       <c r="I82" s="5" t="inlineStr">
         <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="J82" s="6" t="inlineStr"/>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J82" s="6" t="n">
+        <v>306600</v>
+      </c>
       <c r="K82" s="5" t="inlineStr">
         <is>
           <t>yes</t>
@@ -6613,22 +6621,22 @@
       </c>
       <c r="L82" s="5" t="inlineStr">
         <is>
-          <t>Santa Rosa Sound</t>
+          <t>Pensacola Bay (deeded access)</t>
         </is>
       </c>
       <c r="M82" s="5" t="inlineStr">
         <is>
-          <t>34-2S-28-5180-00000-1450</t>
+          <t>50-2S-30-5082-004-007</t>
         </is>
       </c>
       <c r="N82" s="5" t="inlineStr">
         <is>
-          <t>4623 Soundside Dr Gulf Breeze FL 32563</t>
+          <t>3421 Chantarene Dr, Pensacola, FL 32507</t>
         </is>
       </c>
       <c r="O82" s="5" t="inlineStr">
         <is>
-          <t>Score 65: direct Santa Rosa Sound waterfront (+25), owner-occupied (+10), high-confidence phone (+30). 3bd/2.5ba 2,268sf on 0.4ac; 143ft seawall - surge damage risk. In direct landfall corridor per NHC 1pm Oct 7 advisory - landfall expected near AL/FL border Friday night.</t>
+          <t>Score 60: $306.6K last sale (2009) (+10), Pensacola Bay deeded waterfront access (+15), owner-occupied (+10), HOA community (+10), medium-confidence phone (+15). 2004-built home. In direct landfall corridor per NHC 1pm Oct 7 advisory — landfall expected near AL/FL border Friday night.</t>
         </is>
       </c>
     </row>
@@ -6653,22 +6661,22 @@
       </c>
       <c r="E83" s="5" t="inlineStr">
         <is>
-          <t>Martha M Reocable Szescila</t>
+          <t>John K Kepko</t>
         </is>
       </c>
       <c r="F83" s="5" t="inlineStr">
         <is>
-          <t>408 Kelly Plantation Dr Unit 211, Destin, FL 32541</t>
+          <t>1757 Villa Vizcaya Dr</t>
         </is>
       </c>
       <c r="G83" s="5" t="inlineStr">
         <is>
-          <t>Destin</t>
+          <t>Navarre</t>
         </is>
       </c>
       <c r="H83" s="5" t="inlineStr">
         <is>
-          <t>(850) 424-6015</t>
+          <t>(850) 240-4157</t>
         </is>
       </c>
       <c r="I83" s="5" t="inlineStr">
@@ -6676,18 +6684,32 @@
           <t>high</t>
         </is>
       </c>
-      <c r="J83" s="6" t="inlineStr"/>
-      <c r="K83" s="5" t="inlineStr"/>
+      <c r="J83" s="6" t="n">
+        <v>195500</v>
+      </c>
+      <c r="K83" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="L83" s="5" t="inlineStr">
         <is>
-          <t>Destin</t>
-        </is>
-      </c>
-      <c r="M83" s="5" t="inlineStr"/>
-      <c r="N83" s="5" t="inlineStr"/>
+          <t>Santa Rosa Sound</t>
+        </is>
+      </c>
+      <c r="M83" s="5" t="inlineStr">
+        <is>
+          <t>24-2S-27-5578-00A00-0070</t>
+        </is>
+      </c>
+      <c r="N83" s="5" t="inlineStr">
+        <is>
+          <t>1757 Villa Vizcaya Dr, Navarre, FL 32566</t>
+        </is>
+      </c>
       <c r="O83" s="5" t="inlineStr">
         <is>
-          <t>One Water Place condo in gated Kelly Plantation; bay/Gulf views; units ~$1M+; storm surge + wind exposure on Choctawhatchee Bay. Condo = exterior/HOA-managed cleanup potential.</t>
+          <t>Score 50: high-confidence phone (+30), owner-occupied (+10), HOA community (+10). Home-based business owner. In direct landfall corridor per NHC 1pm Oct 7 advisory - landfall expected near AL/FL border Friday night.</t>
         </is>
       </c>
     </row>
@@ -6697,12 +6719,12 @@
       </c>
       <c r="B84" s="5" t="inlineStr">
         <is>
-          <t>TIER 3 - NEW NUMBER (unverified)</t>
+          <t>TIER 2 - CALL TODAY</t>
         </is>
       </c>
       <c r="C84" s="5" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>65</t>
         </is>
       </c>
       <c r="D84" s="5" t="inlineStr">
@@ -6712,12 +6734,12 @@
       </c>
       <c r="E84" s="5" t="inlineStr">
         <is>
-          <t>William Brogdon</t>
+          <t>Herbert D Ludwig</t>
         </is>
       </c>
       <c r="F84" s="5" t="inlineStr">
         <is>
-          <t>3716 Tiger Point Blvd</t>
+          <t>4407 Soundside Dr</t>
         </is>
       </c>
       <c r="G84" s="5" t="inlineStr">
@@ -6727,17 +6749,15 @@
       </c>
       <c r="H84" s="5" t="inlineStr">
         <is>
-          <t>8507914339</t>
+          <t>8509161129</t>
         </is>
       </c>
       <c r="I84" s="5" t="inlineStr">
         <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="J84" s="6" t="n">
-        <v>582000</v>
-      </c>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="J84" s="6" t="inlineStr"/>
       <c r="K84" s="5" t="inlineStr">
         <is>
           <t>yes</t>
@@ -6745,22 +6765,18 @@
       </c>
       <c r="L84" s="5" t="inlineStr">
         <is>
-          <t>Gulf Breeze</t>
-        </is>
-      </c>
-      <c r="M84" s="5" t="inlineStr">
-        <is>
-          <t>29-2S-28-5440-00A00-0300</t>
-        </is>
-      </c>
+          <t>Santa Rosa Sound</t>
+        </is>
+      </c>
+      <c r="M84" s="5" t="inlineStr"/>
       <c r="N84" s="5" t="inlineStr">
         <is>
-          <t>3716 Tiger Point Blvd, Gulf Breeze, FL 32563</t>
+          <t>4407 Soundside Dr Gulf Breeze FL 32563</t>
         </is>
       </c>
       <c r="O84" s="5" t="inlineStr">
         <is>
-          <t>Score 55: $582K assessed value (+20), owner-occupied (+10), medium-confidence phone (+15), Tiger Point HOA community (+10). 3bd/2ba 2,402 sqft (1993), owned since 2015. In direct landfall corridor per NHC 1pm Oct 7 advisory — landfall expected near AL/FL border Friday night.</t>
+          <t>Score 65: direct Santa Rosa Sound waterfront (+25), owner-occupied (+10), high-confidence phone (+30). Value not verified in public records; older owner (age ~88). In direct landfall corridor per NHC 1pm Oct 7 advisory - landfall expected near AL/FL border Friday night.</t>
         </is>
       </c>
     </row>
@@ -6770,12 +6786,12 @@
       </c>
       <c r="B85" s="5" t="inlineStr">
         <is>
-          <t>TIER 3 - NEW NUMBER (unverified)</t>
+          <t>TIER 2 - CALL TODAY</t>
         </is>
       </c>
       <c r="C85" s="5" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>65</t>
         </is>
       </c>
       <c r="D85" s="5" t="inlineStr">
@@ -6785,55 +6801,53 @@
       </c>
       <c r="E85" s="5" t="inlineStr">
         <is>
-          <t>Frances Sanders Rev Trs Miller</t>
+          <t>Phillip Sandfort</t>
         </is>
       </c>
       <c r="F85" s="5" t="inlineStr">
         <is>
-          <t>57 W WATERCOLOR BLVD</t>
+          <t>4623 Soundside Dr</t>
         </is>
       </c>
       <c r="G85" s="5" t="inlineStr">
         <is>
-          <t>Santa Rosa Beach</t>
+          <t>Gulf Breeze</t>
         </is>
       </c>
       <c r="H85" s="5" t="inlineStr">
         <is>
-          <t>8164447372</t>
+          <t>8509322098</t>
         </is>
       </c>
       <c r="I85" s="5" t="inlineStr">
         <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="J85" s="6" t="n">
-        <v>3850000</v>
-      </c>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="J85" s="6" t="inlineStr"/>
       <c r="K85" s="5" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="L85" s="5" t="inlineStr">
         <is>
-          <t>Santa Rosa Beach</t>
+          <t>Santa Rosa Sound</t>
         </is>
       </c>
       <c r="M85" s="5" t="inlineStr">
         <is>
-          <t>15-3S-19-25410-000-0010</t>
+          <t>34-2S-28-5180-00000-1450</t>
         </is>
       </c>
       <c r="N85" s="5" t="inlineStr">
         <is>
-          <t>57 W WATERCOLOR BLVD, Santa Rosa Beach, FL 32459</t>
+          <t>4623 Soundside Dr Gulf Breeze FL 32563</t>
         </is>
       </c>
       <c r="O85" s="5" t="inlineStr">
         <is>
-          <t>Score 45: $3.85M value (+30), medium-confidence phone (+15). WaterColor Santa Rosa Beach. In eastern damage corridor per NHC Oct 7 advisory.</t>
+          <t>Score 65: direct Santa Rosa Sound waterfront (+25), owner-occupied (+10), high-confidence phone (+30). 3bd/2.5ba 2,268sf on 0.4ac; 143ft seawall - surge damage risk. In direct landfall corridor per NHC 1pm Oct 7 advisory - landfall expected near AL/FL border Friday night.</t>
         </is>
       </c>
     </row>
@@ -6843,12 +6857,12 @@
       </c>
       <c r="B86" s="5" t="inlineStr">
         <is>
-          <t>TIER 3 - NEW NUMBER (unverified)</t>
+          <t>TIER 2 - CALL TODAY</t>
         </is>
       </c>
       <c r="C86" s="5" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>65</t>
         </is>
       </c>
       <c r="D86" s="5" t="inlineStr">
@@ -6858,55 +6872,41 @@
       </c>
       <c r="E86" s="5" t="inlineStr">
         <is>
-          <t>Daryl Francis Musso</t>
+          <t>Martha M Reocable Szescila</t>
         </is>
       </c>
       <c r="F86" s="5" t="inlineStr">
         <is>
-          <t>3344 Edgewater Dr</t>
+          <t>408 Kelly Plantation Dr Unit 211, Destin, FL 32541</t>
         </is>
       </c>
       <c r="G86" s="5" t="inlineStr">
         <is>
-          <t>Gulf Breeze</t>
+          <t>Destin</t>
         </is>
       </c>
       <c r="H86" s="5" t="inlineStr">
         <is>
-          <t>2257699420</t>
+          <t>(850) 424-6015</t>
         </is>
       </c>
       <c r="I86" s="5" t="inlineStr">
         <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="J86" s="6" t="n">
-        <v>713500</v>
-      </c>
-      <c r="K86" s="5" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="J86" s="6" t="inlineStr"/>
+      <c r="K86" s="5" t="inlineStr"/>
       <c r="L86" s="5" t="inlineStr">
         <is>
-          <t>Santa Rosa Sound (view)</t>
-        </is>
-      </c>
-      <c r="M86" s="5" t="inlineStr">
-        <is>
-          <t>322S284760004000080</t>
-        </is>
-      </c>
-      <c r="N86" s="5" t="inlineStr">
-        <is>
-          <t>3344 Edgewater Dr, Gulf Breeze, FL 32563</t>
-        </is>
-      </c>
+          <t>Destin</t>
+        </is>
+      </c>
+      <c r="M86" s="5" t="inlineStr"/>
+      <c r="N86" s="5" t="inlineStr"/>
       <c r="O86" s="5" t="inlineStr">
         <is>
-          <t>Score 35: $713.5K sale value (+20), medium-confidence phone (+15). 4bd/2.5ba 2,854 sqft (2006) on concrete pilings w/ pool and whole-house generator; water view of Sound; bought Jan 2026. In direct landfall corridor per NHC 1pm Oct 7 advisory — landfall expected near AL/FL border Friday night.</t>
+          <t>One Water Place condo in gated Kelly Plantation; bay/Gulf views; units ~$1M+; storm surge + wind exposure on Choctawhatchee Bay. Condo = exterior/HOA-managed cleanup potential.</t>
         </is>
       </c>
     </row>
@@ -6921,7 +6921,7 @@
       </c>
       <c r="C87" s="5" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>60</t>
         </is>
       </c>
       <c r="D87" s="5" t="inlineStr">
@@ -6931,12 +6931,12 @@
       </c>
       <c r="E87" s="5" t="inlineStr">
         <is>
-          <t>Jessica D Cousins</t>
+          <t>William Brogdon</t>
         </is>
       </c>
       <c r="F87" s="5" t="inlineStr">
         <is>
-          <t>412 Shoreline Dr</t>
+          <t>3716 Tiger Point Blvd</t>
         </is>
       </c>
       <c r="G87" s="5" t="inlineStr">
@@ -6946,7 +6946,7 @@
       </c>
       <c r="H87" s="5" t="inlineStr">
         <is>
-          <t>8509161613</t>
+          <t>8507914339</t>
         </is>
       </c>
       <c r="I87" s="5" t="inlineStr">
@@ -6955,31 +6955,31 @@
         </is>
       </c>
       <c r="J87" s="6" t="n">
-        <v>500000</v>
+        <v>582000</v>
       </c>
       <c r="K87" s="5" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="L87" s="5" t="inlineStr">
         <is>
-          <t>Santa Rosa Sound</t>
+          <t>Gulf Breeze</t>
         </is>
       </c>
       <c r="M87" s="5" t="inlineStr">
         <is>
-          <t>063S290540058000060</t>
+          <t>29-2S-28-5440-00A00-0300</t>
         </is>
       </c>
       <c r="N87" s="5" t="inlineStr">
         <is>
-          <t>412 Shoreline Dr, Gulf Breeze, FL 32561</t>
+          <t>3716 Tiger Point Blvd, Gulf Breeze, FL 32563</t>
         </is>
       </c>
       <c r="O87" s="5" t="inlineStr">
         <is>
-          <t>Score 60: direct Santa Rosa Sound waterfront (+25), $500K listing value (+20), medium-confidence phone (+15). 3bd/2ba 1,584 sqft (1976), sound-front lot. In direct landfall corridor per NHC 1pm Oct 7 advisory — landfall expected near AL/FL border Friday night.</t>
+          <t>Score 55: $582K assessed value (+20), owner-occupied (+10), medium-confidence phone (+15), Tiger Point HOA community (+10). 3bd/2ba 2,402 sqft (1993), owned since 2015. In direct landfall corridor per NHC 1pm Oct 7 advisory — landfall expected near AL/FL border Friday night.</t>
         </is>
       </c>
     </row>
@@ -6989,7 +6989,7 @@
       </c>
       <c r="B88" s="5" t="inlineStr">
         <is>
-          <t>TIER 2 - CALL TODAY</t>
+          <t>TIER 3 - NEW NUMBER (unverified)</t>
         </is>
       </c>
       <c r="C88" s="5" t="inlineStr">
@@ -7004,41 +7004,55 @@
       </c>
       <c r="E88" s="5" t="inlineStr">
         <is>
-          <t>Sonya C Johnson</t>
+          <t>Frances Sanders Rev Trs Miller</t>
         </is>
       </c>
       <c r="F88" s="5" t="inlineStr">
         <is>
-          <t>7649 Gulf Blvd, Navarre, FL 32566</t>
+          <t>57 W WATERCOLOR BLVD</t>
         </is>
       </c>
       <c r="G88" s="5" t="inlineStr">
         <is>
-          <t>Navarre</t>
+          <t>Santa Rosa Beach</t>
         </is>
       </c>
       <c r="H88" s="5" t="inlineStr">
         <is>
-          <t>(850) 396-5396</t>
+          <t>8164447372</t>
         </is>
       </c>
       <c r="I88" s="5" t="inlineStr">
         <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="J88" s="6" t="inlineStr"/>
-      <c r="K88" s="5" t="inlineStr"/>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J88" s="6" t="n">
+        <v>3850000</v>
+      </c>
+      <c r="K88" s="5" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="L88" s="5" t="inlineStr">
         <is>
-          <t>Navarre</t>
-        </is>
-      </c>
-      <c r="M88" s="5" t="inlineStr"/>
-      <c r="N88" s="5" t="inlineStr"/>
+          <t>Santa Rosa Beach</t>
+        </is>
+      </c>
+      <c r="M88" s="5" t="inlineStr">
+        <is>
+          <t>15-3S-19-25410-000-0010</t>
+        </is>
+      </c>
+      <c r="N88" s="5" t="inlineStr">
+        <is>
+          <t>57 W WATERCOLOR BLVD, Santa Rosa Beach, FL 32459</t>
+        </is>
+      </c>
       <c r="O88" s="5" t="inlineStr">
         <is>
-          <t>TOP LEAD: $2.4M assessed Gulf-front estate (3,825 sqft, built 2006) on Navarre Beach; DIRECT Gulf exposure — first to take surge/wind; 5-7 ft surge forecast for this exact stretch; owner-occupied; massive cleanup spend likely.</t>
+          <t>Score 45: $3.85M value (+30), medium-confidence phone (+15). WaterColor Santa Rosa Beach. In eastern damage corridor per NHC Oct 7 advisory.</t>
         </is>
       </c>
     </row>
@@ -7053,7 +7067,7 @@
       </c>
       <c r="C89" s="5" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>55</t>
         </is>
       </c>
       <c r="D89" s="5" t="inlineStr">
@@ -7063,12 +7077,12 @@
       </c>
       <c r="E89" s="5" t="inlineStr">
         <is>
-          <t>Matthew Mammen</t>
+          <t>Daryl Francis Musso</t>
         </is>
       </c>
       <c r="F89" s="5" t="inlineStr">
         <is>
-          <t>3623 Tiger Point Blvd</t>
+          <t>3344 Edgewater Dr</t>
         </is>
       </c>
       <c r="G89" s="5" t="inlineStr">
@@ -7078,7 +7092,7 @@
       </c>
       <c r="H89" s="5" t="inlineStr">
         <is>
-          <t>3865328484</t>
+          <t>2257699420</t>
         </is>
       </c>
       <c r="I89" s="5" t="inlineStr">
@@ -7087,31 +7101,31 @@
         </is>
       </c>
       <c r="J89" s="6" t="n">
-        <v>426000</v>
+        <v>713500</v>
       </c>
       <c r="K89" s="5" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="L89" s="5" t="inlineStr">
         <is>
-          <t>Gulf Breeze</t>
+          <t>Santa Rosa Sound (view)</t>
         </is>
       </c>
       <c r="M89" s="5" t="inlineStr">
         <is>
-          <t>29-2S-28-5440-00F00-0330</t>
+          <t>322S284760004000080</t>
         </is>
       </c>
       <c r="N89" s="5" t="inlineStr">
         <is>
-          <t>3623 Tiger Point Blvd, Gulf Breeze, FL 32563</t>
+          <t>3344 Edgewater Dr, Gulf Breeze, FL 32563</t>
         </is>
       </c>
       <c r="O89" s="5" t="inlineStr">
         <is>
-          <t>Score 45: $426K assessed value (+10), owner-occupied (+10), medium-confidence phone (+15), Tiger Point HOA community (+10). 3bd/2ba 2,186 sqft (1984), bought May 2026. In direct landfall corridor per NHC 1pm Oct 7 advisory — landfall expected near AL/FL border Friday night.</t>
+          <t>Score 35: $713.5K sale value (+20), medium-confidence phone (+15). 4bd/2.5ba 2,854 sqft (2006) on concrete pilings w/ pool and whole-house generator; water view of Sound; bought Jan 2026. In direct landfall corridor per NHC 1pm Oct 7 advisory — landfall expected near AL/FL border Friday night.</t>
         </is>
       </c>
     </row>
@@ -7126,7 +7140,7 @@
       </c>
       <c r="C90" s="5" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>55</t>
         </is>
       </c>
       <c r="D90" s="5" t="inlineStr">
@@ -7136,22 +7150,22 @@
       </c>
       <c r="E90" s="5" t="inlineStr">
         <is>
-          <t>Chareese Donnel Hastings</t>
+          <t>Jessica D Cousins</t>
         </is>
       </c>
       <c r="F90" s="5" t="inlineStr">
         <is>
-          <t>7474 Soundshore Dr</t>
+          <t>412 Shoreline Dr</t>
         </is>
       </c>
       <c r="G90" s="5" t="inlineStr">
         <is>
-          <t>Navarre</t>
+          <t>Gulf Breeze</t>
         </is>
       </c>
       <c r="H90" s="5" t="inlineStr">
         <is>
-          <t>(614) 403-6595</t>
+          <t>8509161613</t>
         </is>
       </c>
       <c r="I90" s="5" t="inlineStr">
@@ -7160,7 +7174,7 @@
         </is>
       </c>
       <c r="J90" s="6" t="n">
-        <v>493373</v>
+        <v>500000</v>
       </c>
       <c r="K90" s="5" t="inlineStr">
         <is>
@@ -7174,17 +7188,17 @@
       </c>
       <c r="M90" s="5" t="inlineStr">
         <is>
-          <t>24-2S-27-5578-00D00-0010</t>
+          <t>063S290540058000060</t>
         </is>
       </c>
       <c r="N90" s="5" t="inlineStr">
         <is>
-          <t>7474 Soundshore Dr, Navarre, FL 32566</t>
+          <t>412 Shoreline Dr, Gulf Breeze, FL 32561</t>
         </is>
       </c>
       <c r="O90" s="5" t="inlineStr">
         <is>
-          <t>Score 60: direct Santa Rosa Sound waterfront (+25), $493K assessed value (+10), medium-confidence phone (+15), HOA community (+10). Sound-side home off Hwy 98 with pool. In direct landfall corridor per NHC 1pm Oct 7 advisory - landfall expected near AL/FL border Friday night.</t>
+          <t>Score 60: direct Santa Rosa Sound waterfront (+25), $500K listing value (+20), medium-confidence phone (+15). 3bd/2ba 1,584 sqft (1976), sound-front lot. In direct landfall corridor per NHC 1pm Oct 7 advisory — landfall expected near AL/FL border Friday night.</t>
         </is>
       </c>
     </row>
@@ -7194,12 +7208,12 @@
       </c>
       <c r="B91" s="5" t="inlineStr">
         <is>
-          <t>TIER 3 - NEW NUMBER (unverified)</t>
+          <t>TIER 2 - CALL TODAY</t>
         </is>
       </c>
       <c r="C91" s="5" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>55</t>
         </is>
       </c>
       <c r="D91" s="5" t="inlineStr">
@@ -7209,12 +7223,12 @@
       </c>
       <c r="E91" s="5" t="inlineStr">
         <is>
-          <t>Daniel L Lanham &amp; Debra L Lanham</t>
+          <t>Sonya C Johnson</t>
         </is>
       </c>
       <c r="F91" s="5" t="inlineStr">
         <is>
-          <t>1769 Villa Vizcaya Dr</t>
+          <t>7649 Gulf Blvd, Navarre, FL 32566</t>
         </is>
       </c>
       <c r="G91" s="5" t="inlineStr">
@@ -7224,40 +7238,26 @@
       </c>
       <c r="H91" s="5" t="inlineStr">
         <is>
-          <t>(850) 710-3778</t>
+          <t>(850) 396-5396</t>
         </is>
       </c>
       <c r="I91" s="5" t="inlineStr">
         <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="J91" s="6" t="n">
-        <v>385651</v>
-      </c>
-      <c r="K91" s="5" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="J91" s="6" t="inlineStr"/>
+      <c r="K91" s="5" t="inlineStr"/>
       <c r="L91" s="5" t="inlineStr">
         <is>
-          <t>Santa Rosa Sound</t>
-        </is>
-      </c>
-      <c r="M91" s="5" t="inlineStr">
-        <is>
-          <t>24-2S-27-5578-00A00-0050</t>
-        </is>
-      </c>
-      <c r="N91" s="5" t="inlineStr">
-        <is>
-          <t>1769 Villa Vizcaya Dr, Navarre, FL 32566</t>
-        </is>
-      </c>
+          <t>Navarre</t>
+        </is>
+      </c>
+      <c r="M91" s="5" t="inlineStr"/>
+      <c r="N91" s="5" t="inlineStr"/>
       <c r="O91" s="5" t="inlineStr">
         <is>
-          <t>Score 35: $386K assessed value (+10), medium-confidence phone (+15), HOA community (+10). Older owners (72) - likely need debris cleanup help. In direct landfall corridor per NHC 1pm Oct 7 advisory - landfall expected near AL/FL border Friday night.</t>
+          <t>TOP LEAD: $2.4M assessed Gulf-front estate (3,825 sqft, built 2006) on Navarre Beach; DIRECT Gulf exposure — first to take surge/wind; 5-7 ft surge forecast for this exact stretch; owner-occupied; massive cleanup spend likely.</t>
         </is>
       </c>
     </row>
@@ -7272,7 +7272,7 @@
       </c>
       <c r="C92" s="5" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>50</t>
         </is>
       </c>
       <c r="D92" s="5" t="inlineStr">
@@ -7282,12 +7282,12 @@
       </c>
       <c r="E92" s="5" t="inlineStr">
         <is>
-          <t>Ralph Hershey</t>
+          <t>Matthew Mammen</t>
         </is>
       </c>
       <c r="F92" s="5" t="inlineStr">
         <is>
-          <t>1428 Sound Forest Dr, Gulf Breeze, FL 32563</t>
+          <t>3623 Tiger Point Blvd</t>
         </is>
       </c>
       <c r="G92" s="5" t="inlineStr">
@@ -7297,7 +7297,7 @@
       </c>
       <c r="H92" s="5" t="inlineStr">
         <is>
-          <t>(850) 203-1274; (850) 733-9287; (573) 864-7455</t>
+          <t>3865328484</t>
         </is>
       </c>
       <c r="I92" s="5" t="inlineStr">
@@ -7305,18 +7305,32 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="J92" s="6" t="inlineStr"/>
-      <c r="K92" s="5" t="inlineStr"/>
+      <c r="J92" s="6" t="n">
+        <v>426000</v>
+      </c>
+      <c r="K92" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="L92" s="5" t="inlineStr">
         <is>
           <t>Gulf Breeze</t>
         </is>
       </c>
-      <c r="M92" s="5" t="inlineStr"/>
-      <c r="N92" s="5" t="inlineStr"/>
+      <c r="M92" s="5" t="inlineStr">
+        <is>
+          <t>29-2S-28-5440-00F00-0330</t>
+        </is>
+      </c>
+      <c r="N92" s="5" t="inlineStr">
+        <is>
+          <t>3623 Tiger Point Blvd, Gulf Breeze, FL 32563</t>
+        </is>
+      </c>
       <c r="O92" s="5" t="inlineStr">
         <is>
-          <t>Sound Forest Dr = Santa Rosa Sound waterfront, Gulf Breeze; direct sound/bay surge exposure; waterfront homes $750K+; wooded sound-side lots = tree work; in corridor.</t>
+          <t>Score 45: $426K assessed value (+10), owner-occupied (+10), medium-confidence phone (+15), Tiger Point HOA community (+10). 3bd/2ba 2,186 sqft (1984), bought May 2026. In direct landfall corridor per NHC 1pm Oct 7 advisory — landfall expected near AL/FL border Friday night.</t>
         </is>
       </c>
     </row>
@@ -7331,7 +7345,7 @@
       </c>
       <c r="C93" s="5" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>45</t>
         </is>
       </c>
       <c r="D93" s="5" t="inlineStr">
@@ -7341,30 +7355,32 @@
       </c>
       <c r="E93" s="5" t="inlineStr">
         <is>
-          <t>Karl F Stark</t>
+          <t>Chareese Donnel Hastings</t>
         </is>
       </c>
       <c r="F93" s="5" t="inlineStr">
         <is>
-          <t>4629 Soundside Dr</t>
+          <t>7474 Soundshore Dr</t>
         </is>
       </c>
       <c r="G93" s="5" t="inlineStr">
         <is>
-          <t>Gulf Breeze</t>
+          <t>Navarre</t>
         </is>
       </c>
       <c r="H93" s="5" t="inlineStr">
         <is>
-          <t>8509324739</t>
+          <t>(614) 403-6595</t>
         </is>
       </c>
       <c r="I93" s="5" t="inlineStr">
         <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="J93" s="6" t="inlineStr"/>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J93" s="6" t="n">
+        <v>493373</v>
+      </c>
       <c r="K93" s="5" t="inlineStr">
         <is>
           <t>unknown</t>
@@ -7375,15 +7391,19 @@
           <t>Santa Rosa Sound</t>
         </is>
       </c>
-      <c r="M93" s="5" t="inlineStr"/>
+      <c r="M93" s="5" t="inlineStr">
+        <is>
+          <t>24-2S-27-5578-00D00-0010</t>
+        </is>
+      </c>
       <c r="N93" s="5" t="inlineStr">
         <is>
-          <t>4629 Soundside Dr Gulf Breeze FL 32563</t>
+          <t>7474 Soundshore Dr, Navarre, FL 32566</t>
         </is>
       </c>
       <c r="O93" s="5" t="inlineStr">
         <is>
-          <t>Score 40: direct Santa Rosa Sound waterfront (+25), low-confidence phone (+15). CAUTION: Karl F. Stark of Gulf Breeze died 2008 per obituary; household may be estate/family - verify occupant. In direct landfall corridor per NHC 1pm Oct 7 advisory - landfall expected near AL/FL border Friday night.</t>
+          <t>Score 60: direct Santa Rosa Sound waterfront (+25), $493K assessed value (+10), medium-confidence phone (+15), HOA community (+10). Sound-side home off Hwy 98 with pool. In direct landfall corridor per NHC 1pm Oct 7 advisory - landfall expected near AL/FL border Friday night.</t>
         </is>
       </c>
     </row>
@@ -7393,12 +7413,12 @@
       </c>
       <c r="B94" s="5" t="inlineStr">
         <is>
-          <t>TIER 2 - CALL TODAY</t>
+          <t>TIER 3 - NEW NUMBER (unverified)</t>
         </is>
       </c>
       <c r="C94" s="5" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>45</t>
         </is>
       </c>
       <c r="D94" s="5" t="inlineStr">
@@ -7408,41 +7428,55 @@
       </c>
       <c r="E94" s="5" t="inlineStr">
         <is>
-          <t>Langley Lindsley</t>
+          <t>Daniel L Lanham &amp; Debra L Lanham</t>
         </is>
       </c>
       <c r="F94" s="5" t="inlineStr">
         <is>
-          <t>359 Kelly Plantation Dr, Destin, FL 32541</t>
+          <t>1769 Villa Vizcaya Dr</t>
         </is>
       </c>
       <c r="G94" s="5" t="inlineStr">
         <is>
-          <t>Destin</t>
+          <t>Navarre</t>
         </is>
       </c>
       <c r="H94" s="5" t="inlineStr">
         <is>
-          <t>(850) 269-1630; (850) 974-3966</t>
+          <t>(850) 710-3778</t>
         </is>
       </c>
       <c r="I94" s="5" t="inlineStr">
         <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="J94" s="6" t="inlineStr"/>
-      <c r="K94" s="5" t="inlineStr"/>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J94" s="6" t="n">
+        <v>385651</v>
+      </c>
+      <c r="K94" s="5" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="L94" s="5" t="inlineStr">
         <is>
-          <t>Destin</t>
-        </is>
-      </c>
-      <c r="M94" s="5" t="inlineStr"/>
-      <c r="N94" s="5" t="inlineStr"/>
+          <t>Santa Rosa Sound</t>
+        </is>
+      </c>
+      <c r="M94" s="5" t="inlineStr">
+        <is>
+          <t>24-2S-27-5578-00A00-0050</t>
+        </is>
+      </c>
+      <c r="N94" s="5" t="inlineStr">
+        <is>
+          <t>1769 Villa Vizcaya Dr, Navarre, FL 32566</t>
+        </is>
+      </c>
       <c r="O94" s="5" t="inlineStr">
         <is>
-          <t>Gated Kelly Plantation community on Choctawhatchee Bay; bay-front exposure; homes $800K-$1.5M+; in NHC landfall corridor (Mobile-Destin). High tree/debris potential on wooded golf lots.</t>
+          <t>Score 35: $386K assessed value (+10), medium-confidence phone (+15), HOA community (+10). Older owners (72) - likely need debris cleanup help. In direct landfall corridor per NHC 1pm Oct 7 advisory - landfall expected near AL/FL border Friday night.</t>
         </is>
       </c>
     </row>
@@ -7452,12 +7486,12 @@
       </c>
       <c r="B95" s="5" t="inlineStr">
         <is>
-          <t>TIER 2 - CALL TODAY</t>
+          <t>TIER 3 - NEW NUMBER (unverified)</t>
         </is>
       </c>
       <c r="C95" s="5" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>45</t>
         </is>
       </c>
       <c r="D95" s="5" t="inlineStr">
@@ -7467,41 +7501,41 @@
       </c>
       <c r="E95" s="5" t="inlineStr">
         <is>
-          <t>Nathan Owendoff</t>
+          <t>Ralph Hershey</t>
         </is>
       </c>
       <c r="F95" s="5" t="inlineStr">
         <is>
-          <t>667 Emerald Bay Dr, Destin, FL 32541</t>
+          <t>1428 Sound Forest Dr, Gulf Breeze, FL 32563</t>
         </is>
       </c>
       <c r="G95" s="5" t="inlineStr">
         <is>
-          <t>Destin</t>
+          <t>Gulf Breeze</t>
         </is>
       </c>
       <c r="H95" s="5" t="inlineStr">
         <is>
-          <t>(850) 598-1704; (850) 597-6836; (850) 837-4517</t>
+          <t>(850) 203-1274; (850) 733-9287; (573) 864-7455</t>
         </is>
       </c>
       <c r="I95" s="5" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="J95" s="6" t="inlineStr"/>
       <c r="K95" s="5" t="inlineStr"/>
       <c r="L95" s="5" t="inlineStr">
         <is>
-          <t>Destin</t>
+          <t>Gulf Breeze</t>
         </is>
       </c>
       <c r="M95" s="5" t="inlineStr"/>
       <c r="N95" s="5" t="inlineStr"/>
       <c r="O95" s="5" t="inlineStr">
         <is>
-          <t>Gated Emerald Bay golf community; 2,556 sqft single-family (~$700K+ current value); mature trees + hurricane winds = tree-removal work; in landfall corridor.</t>
+          <t>Sound Forest Dr = Santa Rosa Sound waterfront, Gulf Breeze; direct sound/bay surge exposure; waterfront homes $750K+; wooded sound-side lots = tree work; in corridor.</t>
         </is>
       </c>
     </row>
@@ -7511,7 +7545,7 @@
       </c>
       <c r="B96" s="5" t="inlineStr">
         <is>
-          <t>TIER 2 - CALL TODAY</t>
+          <t>TIER 3 - NEW NUMBER (unverified)</t>
         </is>
       </c>
       <c r="C96" s="5" t="inlineStr">
@@ -7526,41 +7560,49 @@
       </c>
       <c r="E96" s="5" t="inlineStr">
         <is>
-          <t>Valerie Ballard / Jerry Ballard</t>
+          <t>Karl F Stark</t>
         </is>
       </c>
       <c r="F96" s="5" t="inlineStr">
         <is>
-          <t>942 Emerald Bay Drive, Destin, FL 32541</t>
+          <t>4629 Soundside Dr</t>
         </is>
       </c>
       <c r="G96" s="5" t="inlineStr">
         <is>
-          <t>Destin</t>
+          <t>Gulf Breeze</t>
         </is>
       </c>
       <c r="H96" s="5" t="inlineStr">
         <is>
-          <t>(850) 424-6168</t>
+          <t>8509324739</t>
         </is>
       </c>
       <c r="I96" s="5" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>low</t>
         </is>
       </c>
       <c r="J96" s="6" t="inlineStr"/>
-      <c r="K96" s="5" t="inlineStr"/>
+      <c r="K96" s="5" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="L96" s="5" t="inlineStr">
         <is>
-          <t>Destin</t>
+          <t>Santa Rosa Sound</t>
         </is>
       </c>
       <c r="M96" s="5" t="inlineStr"/>
-      <c r="N96" s="5" t="inlineStr"/>
+      <c r="N96" s="5" t="inlineStr">
+        <is>
+          <t>4629 Soundside Dr Gulf Breeze FL 32563</t>
+        </is>
+      </c>
       <c r="O96" s="5" t="inlineStr">
         <is>
-          <t>Gated Emerald Bay golf community; local 850 landline tied to address; ~$700K+ home; mature landscaping + storm winds = cleanup demand; in corridor.</t>
+          <t>Score 40: direct Santa Rosa Sound waterfront (+25), low-confidence phone (+15). CAUTION: Karl F. Stark of Gulf Breeze died 2008 per obituary; household may be estate/family - verify occupant. In direct landfall corridor per NHC 1pm Oct 7 advisory - landfall expected near AL/FL border Friday night.</t>
         </is>
       </c>
     </row>
@@ -7585,12 +7627,12 @@
       </c>
       <c r="E97" s="5" t="inlineStr">
         <is>
-          <t>Chad Blankenship</t>
+          <t>Langley Lindsley</t>
         </is>
       </c>
       <c r="F97" s="5" t="inlineStr">
         <is>
-          <t>1115 Emerald Bay Drive, Destin, FL 32541</t>
+          <t>359 Kelly Plantation Dr, Destin, FL 32541</t>
         </is>
       </c>
       <c r="G97" s="5" t="inlineStr">
@@ -7600,7 +7642,7 @@
       </c>
       <c r="H97" s="5" t="inlineStr">
         <is>
-          <t>(850) 797-2132</t>
+          <t>(850) 269-1630; (850) 974-3966</t>
         </is>
       </c>
       <c r="I97" s="5" t="inlineStr">
@@ -7619,7 +7661,7 @@
       <c r="N97" s="5" t="inlineStr"/>
       <c r="O97" s="5" t="inlineStr">
         <is>
-          <t>Gated Emerald Bay golf community; local 850 number; homeowner age 40; ~$700K+ home; tree-lined golf lots = post-hurricane debris/tree removal.</t>
+          <t>Gated Kelly Plantation community on Choctawhatchee Bay; bay-front exposure; homes $800K-$1.5M+; in NHC landfall corridor (Mobile-Destin). High tree/debris potential on wooded golf lots.</t>
         </is>
       </c>
     </row>
@@ -7629,12 +7671,12 @@
       </c>
       <c r="B98" s="5" t="inlineStr">
         <is>
-          <t>TIER 3 - NEW NUMBER (unverified)</t>
+          <t>TIER 2 - CALL TODAY</t>
         </is>
       </c>
       <c r="C98" s="5" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>40</t>
         </is>
       </c>
       <c r="D98" s="5" t="inlineStr">
@@ -7644,49 +7686,41 @@
       </c>
       <c r="E98" s="5" t="inlineStr">
         <is>
-          <t>Charles E Stamitoles</t>
+          <t>Nathan Owendoff</t>
         </is>
       </c>
       <c r="F98" s="5" t="inlineStr">
         <is>
-          <t>5640 Scenic Hwy, Pensacola, FL 32504</t>
+          <t>667 Emerald Bay Dr, Destin, FL 32541</t>
         </is>
       </c>
       <c r="G98" s="5" t="inlineStr">
         <is>
-          <t>Pensacola</t>
+          <t>Destin</t>
         </is>
       </c>
       <c r="H98" s="5" t="inlineStr">
         <is>
-          <t>(850) 393-5103</t>
+          <t>(850) 598-1704; (850) 597-6836; (850) 837-4517</t>
         </is>
       </c>
       <c r="I98" s="5" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="J98" s="6" t="inlineStr"/>
-      <c r="K98" s="5" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
+      <c r="K98" s="5" t="inlineStr"/>
       <c r="L98" s="5" t="inlineStr">
         <is>
-          <t>Escambia Bay</t>
+          <t>Destin</t>
         </is>
       </c>
       <c r="M98" s="5" t="inlineStr"/>
-      <c r="N98" s="5" t="inlineStr">
-        <is>
-          <t>5640 Scenic Hwy, Pensacola, FL 32504</t>
-        </is>
-      </c>
+      <c r="N98" s="5" t="inlineStr"/>
       <c r="O98" s="5" t="inlineStr">
         <is>
-          <t>Score 40: direct Escambia Bay bluff frontage (+25), medium-confidence phone (+15). Multi-parcel Scenic Hwy owner (5600 block) — portfolio value unknown. Steep bluff lot, mature trees. In direct landfall corridor per NHC 1pm Oct 7 advisory — landfall expected near AL/FL border Friday night.</t>
+          <t>Gated Emerald Bay golf community; 2,556 sqft single-family (~$700K+ current value); mature trees + hurricane winds = tree-removal work; in landfall corridor.</t>
         </is>
       </c>
     </row>
@@ -7696,12 +7730,12 @@
       </c>
       <c r="B99" s="5" t="inlineStr">
         <is>
-          <t>TIER 3 - NEW NUMBER (unverified)</t>
+          <t>TIER 2 - CALL TODAY</t>
         </is>
       </c>
       <c r="C99" s="5" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>40</t>
         </is>
       </c>
       <c r="D99" s="5" t="inlineStr">
@@ -7711,49 +7745,41 @@
       </c>
       <c r="E99" s="5" t="inlineStr">
         <is>
-          <t>Daniel P Summers</t>
+          <t>Valerie Ballard / Jerry Ballard</t>
         </is>
       </c>
       <c r="F99" s="5" t="inlineStr">
         <is>
-          <t>3829 Scenic Hwy, Pensacola, FL 32504</t>
+          <t>942 Emerald Bay Drive, Destin, FL 32541</t>
         </is>
       </c>
       <c r="G99" s="5" t="inlineStr">
         <is>
-          <t>Pensacola</t>
+          <t>Destin</t>
         </is>
       </c>
       <c r="H99" s="5" t="inlineStr">
         <is>
-          <t>(239) 537-0914</t>
+          <t>(850) 424-6168</t>
         </is>
       </c>
       <c r="I99" s="5" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="J99" s="6" t="inlineStr"/>
-      <c r="K99" s="5" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
+      <c r="K99" s="5" t="inlineStr"/>
       <c r="L99" s="5" t="inlineStr">
         <is>
-          <t>Escambia Bay</t>
+          <t>Destin</t>
         </is>
       </c>
       <c r="M99" s="5" t="inlineStr"/>
-      <c r="N99" s="5" t="inlineStr">
-        <is>
-          <t>3829 Scenic Hwy, Pensacola, FL 32504</t>
-        </is>
-      </c>
+      <c r="N99" s="5" t="inlineStr"/>
       <c r="O99" s="5" t="inlineStr">
         <is>
-          <t>Score 40: direct Escambia Bay bluff frontage (+25), medium-confidence mobile (+15). Scenic Hwy waterfront home — assessed value not confirmed. Bluff erosion + surge exposure. In direct landfall corridor per NHC 1pm Oct 7 advisory — landfall expected near AL/FL border Friday night.</t>
+          <t>Gated Emerald Bay golf community; local 850 landline tied to address; ~$700K+ home; mature landscaping + storm winds = cleanup demand; in corridor.</t>
         </is>
       </c>
     </row>
@@ -7763,12 +7789,12 @@
       </c>
       <c r="B100" s="5" t="inlineStr">
         <is>
-          <t>TIER 3 - NEW NUMBER (unverified)</t>
+          <t>TIER 2 - CALL TODAY</t>
         </is>
       </c>
       <c r="C100" s="5" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>40</t>
         </is>
       </c>
       <c r="D100" s="5" t="inlineStr">
@@ -7778,49 +7804,41 @@
       </c>
       <c r="E100" s="5" t="inlineStr">
         <is>
-          <t>Zak Lamarche</t>
+          <t>Chad Blankenship</t>
         </is>
       </c>
       <c r="F100" s="5" t="inlineStr">
         <is>
-          <t>2299 Scenic Hwy, Pensacola, FL 32503</t>
+          <t>1115 Emerald Bay Drive, Destin, FL 32541</t>
         </is>
       </c>
       <c r="G100" s="5" t="inlineStr">
         <is>
-          <t>Pensacola</t>
+          <t>Destin</t>
         </is>
       </c>
       <c r="H100" s="5" t="inlineStr">
         <is>
-          <t>850-436-8562</t>
+          <t>(850) 797-2132</t>
         </is>
       </c>
       <c r="I100" s="5" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="J100" s="6" t="inlineStr"/>
-      <c r="K100" s="5" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
+      <c r="K100" s="5" t="inlineStr"/>
       <c r="L100" s="5" t="inlineStr">
         <is>
-          <t>Escambia Bay</t>
+          <t>Destin</t>
         </is>
       </c>
       <c r="M100" s="5" t="inlineStr"/>
-      <c r="N100" s="5" t="inlineStr">
-        <is>
-          <t>2299 Scenic Hwy, Pensacola, FL 32503</t>
-        </is>
-      </c>
+      <c r="N100" s="5" t="inlineStr"/>
       <c r="O100" s="5" t="inlineStr">
         <is>
-          <t>Score 25: direct Escambia Bay bluff frontage (+25). Resident at Scenic Hwy address — no phone found, value unconfirmed. Bluff erosion + surge exposure. In direct landfall corridor per NHC 1pm Oct 7 advisory — landfall expected near AL/FL border Friday night.</t>
+          <t>Gated Emerald Bay golf community; local 850 number; homeowner age 40; ~$700K+ home; tree-lined golf lots = post-hurricane debris/tree removal.</t>
         </is>
       </c>
     </row>
@@ -7835,7 +7853,7 @@
       </c>
       <c r="C101" s="5" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>35</t>
         </is>
       </c>
       <c r="D101" s="5" t="inlineStr">
@@ -7845,12 +7863,12 @@
       </c>
       <c r="E101" s="5" t="inlineStr">
         <is>
-          <t>Clifford B Mowe</t>
+          <t>Charles E Stamitoles</t>
         </is>
       </c>
       <c r="F101" s="5" t="inlineStr">
         <is>
-          <t>3835 Scenic Hwy, Pensacola, FL 32504</t>
+          <t>5640 Scenic Hwy, Pensacola, FL 32504</t>
         </is>
       </c>
       <c r="G101" s="5" t="inlineStr">
@@ -7860,12 +7878,12 @@
       </c>
       <c r="H101" s="5" t="inlineStr">
         <is>
-          <t>(850) 439-2940</t>
+          <t>(850) 393-5103</t>
         </is>
       </c>
       <c r="I101" s="5" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="J101" s="6" t="inlineStr"/>
@@ -7882,12 +7900,12 @@
       <c r="M101" s="5" t="inlineStr"/>
       <c r="N101" s="5" t="inlineStr">
         <is>
-          <t>3835 Scenic Hwy, Pensacola, FL 32504</t>
+          <t>5640 Scenic Hwy, Pensacola, FL 32504</t>
         </is>
       </c>
       <c r="O101" s="5" t="inlineStr">
         <is>
-          <t>Score 40: direct Escambia Bay bluff frontage (+25), low-confidence phone (+15, business line). Scenic Hwy waterfront resident. Bluff erosion + surge exposure. In direct landfall corridor per NHC 1pm Oct 7 advisory — landfall expected near AL/FL border Friday night.</t>
+          <t>Score 40: direct Escambia Bay bluff frontage (+25), medium-confidence phone (+15). Multi-parcel Scenic Hwy owner (5600 block) — portfolio value unknown. Steep bluff lot, mature trees. In direct landfall corridor per NHC 1pm Oct 7 advisory — landfall expected near AL/FL border Friday night.</t>
         </is>
       </c>
     </row>
@@ -7902,7 +7920,7 @@
       </c>
       <c r="C102" s="5" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>35</t>
         </is>
       </c>
       <c r="D102" s="5" t="inlineStr">
@@ -7912,22 +7930,22 @@
       </c>
       <c r="E102" s="5" t="inlineStr">
         <is>
-          <t>Cynthia Shatz</t>
+          <t>Daniel P Summers</t>
         </is>
       </c>
       <c r="F102" s="5" t="inlineStr">
         <is>
-          <t>1193 Emerald Bay Dr, Destin, FL 32541</t>
+          <t>3829 Scenic Hwy, Pensacola, FL 32504</t>
         </is>
       </c>
       <c r="G102" s="5" t="inlineStr">
         <is>
-          <t>Destin</t>
+          <t>Pensacola</t>
         </is>
       </c>
       <c r="H102" s="5" t="inlineStr">
         <is>
-          <t>(210) 324-9237</t>
+          <t>(239) 537-0914</t>
         </is>
       </c>
       <c r="I102" s="5" t="inlineStr">
@@ -7936,17 +7954,25 @@
         </is>
       </c>
       <c r="J102" s="6" t="inlineStr"/>
-      <c r="K102" s="5" t="inlineStr"/>
+      <c r="K102" s="5" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="L102" s="5" t="inlineStr">
         <is>
-          <t>Destin</t>
+          <t>Escambia Bay</t>
         </is>
       </c>
       <c r="M102" s="5" t="inlineStr"/>
-      <c r="N102" s="5" t="inlineStr"/>
+      <c r="N102" s="5" t="inlineStr">
+        <is>
+          <t>3829 Scenic Hwy, Pensacola, FL 32504</t>
+        </is>
+      </c>
       <c r="O102" s="5" t="inlineStr">
         <is>
-          <t>Gated Emerald Bay golf community (~$700K+ homes); TX area code suggests second home — absentee owners need post-storm property checks; wooded lots = tree work.</t>
+          <t>Score 40: direct Escambia Bay bluff frontage (+25), medium-confidence mobile (+15). Scenic Hwy waterfront home — assessed value not confirmed. Bluff erosion + surge exposure. In direct landfall corridor per NHC 1pm Oct 7 advisory — landfall expected near AL/FL border Friday night.</t>
         </is>
       </c>
     </row>
@@ -7956,12 +7982,12 @@
       </c>
       <c r="B103" s="5" t="inlineStr">
         <is>
-          <t>TIER 2 - CALL TODAY</t>
+          <t>TIER 3 - NEW NUMBER (unverified)</t>
         </is>
       </c>
       <c r="C103" s="5" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>35</t>
         </is>
       </c>
       <c r="D103" s="5" t="inlineStr">
@@ -7971,41 +7997,49 @@
       </c>
       <c r="E103" s="5" t="inlineStr">
         <is>
-          <t>William Grubbs</t>
+          <t>Zak Lamarche</t>
         </is>
       </c>
       <c r="F103" s="5" t="inlineStr">
         <is>
-          <t>5333 Soundside Drive, Gulf Breeze, FL 32563</t>
+          <t>2299 Scenic Hwy, Pensacola, FL 32503</t>
         </is>
       </c>
       <c r="G103" s="5" t="inlineStr">
         <is>
-          <t>Gulf Breeze</t>
+          <t>Pensacola</t>
         </is>
       </c>
       <c r="H103" s="5" t="inlineStr">
         <is>
-          <t>(850) 934-1883; (904) 853-6446</t>
+          <t>850-436-8562</t>
         </is>
       </c>
       <c r="I103" s="5" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="J103" s="6" t="inlineStr"/>
-      <c r="K103" s="5" t="inlineStr"/>
+      <c r="K103" s="5" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="L103" s="5" t="inlineStr">
         <is>
-          <t>Gulf Breeze</t>
+          <t>Escambia Bay</t>
         </is>
       </c>
       <c r="M103" s="5" t="inlineStr"/>
-      <c r="N103" s="5" t="inlineStr"/>
+      <c r="N103" s="5" t="inlineStr">
+        <is>
+          <t>2299 Scenic Hwy, Pensacola, FL 32503</t>
+        </is>
+      </c>
       <c r="O103" s="5" t="inlineStr">
         <is>
-          <t>Soundside Drive = direct Santa Rosa Sound waterfront; local 850 landline history; sound-front homes $750K+; surge + wind exposure; seawall/dock damage likely = cleanup work.</t>
+          <t>Score 25: direct Escambia Bay bluff frontage (+25). Resident at Scenic Hwy address — no phone found, value unconfirmed. Bluff erosion + surge exposure. In direct landfall corridor per NHC 1pm Oct 7 advisory — landfall expected near AL/FL border Friday night.</t>
         </is>
       </c>
     </row>
@@ -8015,7 +8049,7 @@
       </c>
       <c r="B104" s="5" t="inlineStr">
         <is>
-          <t>TIER 2 - CALL TODAY</t>
+          <t>TIER 3 - NEW NUMBER (unverified)</t>
         </is>
       </c>
       <c r="C104" s="5" t="inlineStr">
@@ -8030,39 +8064,51 @@
       </c>
       <c r="E104" s="5" t="inlineStr">
         <is>
-          <t>Thomas Lampone</t>
+          <t>Clifford B Mowe</t>
         </is>
       </c>
       <c r="F104" s="5" t="inlineStr">
         <is>
-          <t>104 Matamoros Dr</t>
+          <t>3835 Scenic Hwy, Pensacola, FL 32504</t>
         </is>
       </c>
       <c r="G104" s="5" t="inlineStr">
         <is>
-          <t>Gulf Breeze FL 32561</t>
+          <t>Pensacola</t>
         </is>
       </c>
       <c r="H104" s="5" t="inlineStr">
         <is>
-          <t>(850) 406-2282</t>
+          <t>(850) 439-2940</t>
         </is>
       </c>
       <c r="I104" s="5" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>low</t>
         </is>
       </c>
       <c r="J104" s="6" t="inlineStr"/>
-      <c r="K104" s="5" t="inlineStr"/>
+      <c r="K104" s="5" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="L104" s="5" t="inlineStr">
         <is>
-          <t>Gulf Breeze FL 32561</t>
+          <t>Escambia Bay</t>
         </is>
       </c>
       <c r="M104" s="5" t="inlineStr"/>
-      <c r="N104" s="5" t="inlineStr"/>
-      <c r="O104" s="5" t="inlineStr"/>
+      <c r="N104" s="5" t="inlineStr">
+        <is>
+          <t>3835 Scenic Hwy, Pensacola, FL 32504</t>
+        </is>
+      </c>
+      <c r="O104" s="5" t="inlineStr">
+        <is>
+          <t>Score 40: direct Escambia Bay bluff frontage (+25), low-confidence phone (+15, business line). Scenic Hwy waterfront resident. Bluff erosion + surge exposure. In direct landfall corridor per NHC 1pm Oct 7 advisory — landfall expected near AL/FL border Friday night.</t>
+        </is>
+      </c>
     </row>
     <row r="105" ht="60" customHeight="1">
       <c r="A105" s="5" t="n">
@@ -8075,7 +8121,7 @@
       </c>
       <c r="C105" s="5" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30</t>
         </is>
       </c>
       <c r="D105" s="5" t="inlineStr">
@@ -8085,22 +8131,22 @@
       </c>
       <c r="E105" s="5" t="inlineStr">
         <is>
-          <t>Gary Ybarzabal</t>
+          <t>Cynthia Shatz</t>
         </is>
       </c>
       <c r="F105" s="5" t="inlineStr">
         <is>
-          <t>1770 Waterford Sound Blvd, Gulf Breeze, FL 32563</t>
+          <t>1193 Emerald Bay Dr, Destin, FL 32541</t>
         </is>
       </c>
       <c r="G105" s="5" t="inlineStr">
         <is>
-          <t>Gulf Breeze</t>
+          <t>Destin</t>
         </is>
       </c>
       <c r="H105" s="5" t="inlineStr">
         <is>
-          <t>(678) 574-3163</t>
+          <t>(210) 324-9237</t>
         </is>
       </c>
       <c r="I105" s="5" t="inlineStr">
@@ -8112,14 +8158,14 @@
       <c r="K105" s="5" t="inlineStr"/>
       <c r="L105" s="5" t="inlineStr">
         <is>
-          <t>Gulf Breeze</t>
+          <t>Destin</t>
         </is>
       </c>
       <c r="M105" s="5" t="inlineStr"/>
       <c r="N105" s="5" t="inlineStr"/>
       <c r="O105" s="5" t="inlineStr">
         <is>
-          <t>Waterfront Sound Blvd community on Santa Rosa Sound; GA area code suggests second home — absentee owner needs storm check; sound-front surge exposure; $750K+ homes.</t>
+          <t>Gated Emerald Bay golf community (~$700K+ homes); TX area code suggests second home — absentee owners need post-storm property checks; wooded lots = tree work.</t>
         </is>
       </c>
     </row>
@@ -8129,12 +8175,12 @@
       </c>
       <c r="B106" s="5" t="inlineStr">
         <is>
-          <t>TIER 3 - NEW NUMBER (unverified)</t>
+          <t>TIER 2 - CALL TODAY</t>
         </is>
       </c>
       <c r="C106" s="5" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30</t>
         </is>
       </c>
       <c r="D106" s="5" t="inlineStr">
@@ -8144,222 +8190,212 @@
       </c>
       <c r="E106" s="5" t="inlineStr">
         <is>
-          <t>Paul Ferachi</t>
+          <t>William Grubbs</t>
         </is>
       </c>
       <c r="F106" s="5" t="inlineStr">
         <is>
-          <t>1774 Ensenada Siete</t>
+          <t>5333 Soundside Drive, Gulf Breeze, FL 32563</t>
         </is>
       </c>
       <c r="G106" s="5" t="inlineStr">
         <is>
-          <t>Pensacola Beach FL 32561</t>
+          <t>Gulf Breeze</t>
         </is>
       </c>
       <c r="H106" s="5" t="inlineStr">
         <is>
-          <t>(225) 755-3695; (850) 677-8396</t>
+          <t>(850) 934-1883; (904) 853-6446</t>
         </is>
       </c>
       <c r="I106" s="5" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>high</t>
         </is>
       </c>
       <c r="J106" s="6" t="inlineStr"/>
       <c r="K106" s="5" t="inlineStr"/>
       <c r="L106" s="5" t="inlineStr">
         <is>
-          <t>Pensacola Beach FL 32561</t>
+          <t>Gulf Breeze</t>
         </is>
       </c>
       <c r="M106" s="5" t="inlineStr"/>
       <c r="N106" s="5" t="inlineStr"/>
-      <c r="O106" s="5" t="inlineStr"/>
+      <c r="O106" s="5" t="inlineStr">
+        <is>
+          <t>Soundside Drive = direct Santa Rosa Sound waterfront; local 850 landline history; sound-front homes $750K+; surge + wind exposure; seawall/dock damage likely = cleanup work.</t>
+        </is>
+      </c>
     </row>
     <row r="107" ht="60" customHeight="1">
-      <c r="A107" s="7" t="n">
+      <c r="A107" s="5" t="n">
         <v>106</v>
       </c>
-      <c r="B107" s="7" t="inlineStr">
-        <is>
-          <t>TIER 4 - NEEDS PHONE</t>
-        </is>
-      </c>
-      <c r="C107" s="7" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="D107" s="7" t="inlineStr"/>
-      <c r="E107" s="7" t="inlineStr">
-        <is>
-          <t>Nicholas J &amp; Susan Z Lembo</t>
-        </is>
-      </c>
-      <c r="F107" s="7" t="inlineStr">
-        <is>
-          <t>193 PARADISE BY THE SEA BLVD</t>
-        </is>
-      </c>
-      <c r="G107" s="7" t="inlineStr">
-        <is>
-          <t>Inlet Beach</t>
-        </is>
-      </c>
-      <c r="H107" s="7" t="inlineStr"/>
-      <c r="I107" s="7" t="inlineStr"/>
-      <c r="J107" s="8" t="n">
-        <v>28307268</v>
-      </c>
-      <c r="K107" s="7" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="L107" s="7" t="inlineStr">
-        <is>
-          <t>Gulf of Mexico</t>
-        </is>
-      </c>
-      <c r="M107" s="7" t="inlineStr">
-        <is>
-          <t>35-3S-18-16020-00A-0120</t>
-        </is>
-      </c>
-      <c r="N107" s="7" t="inlineStr">
-        <is>
-          <t>193 PARADISE BY THE SEA BLVD, Inlet Beach, FL 32461</t>
-        </is>
-      </c>
-      <c r="O107" s="7" t="inlineStr">
-        <is>
-          <t>Score 65: $28.3M value (+30), direct Gulf frontage (+25), owner-occupied (+10). In eastern damage corridor per NHC Oct 7 advisory.</t>
-        </is>
-      </c>
+      <c r="B107" s="5" t="inlineStr">
+        <is>
+          <t>TIER 2 - CALL TODAY</t>
+        </is>
+      </c>
+      <c r="C107" s="5" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D107" s="5" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="E107" s="5" t="inlineStr">
+        <is>
+          <t>Thomas Lampone</t>
+        </is>
+      </c>
+      <c r="F107" s="5" t="inlineStr">
+        <is>
+          <t>104 Matamoros Dr</t>
+        </is>
+      </c>
+      <c r="G107" s="5" t="inlineStr">
+        <is>
+          <t>Gulf Breeze FL 32561</t>
+        </is>
+      </c>
+      <c r="H107" s="5" t="inlineStr">
+        <is>
+          <t>(850) 406-2282</t>
+        </is>
+      </c>
+      <c r="I107" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J107" s="6" t="inlineStr"/>
+      <c r="K107" s="5" t="inlineStr"/>
+      <c r="L107" s="5" t="inlineStr">
+        <is>
+          <t>Gulf Breeze FL 32561</t>
+        </is>
+      </c>
+      <c r="M107" s="5" t="inlineStr"/>
+      <c r="N107" s="5" t="inlineStr"/>
+      <c r="O107" s="5" t="inlineStr"/>
     </row>
     <row r="108" ht="60" customHeight="1">
-      <c r="A108" s="7" t="n">
+      <c r="A108" s="5" t="n">
         <v>107</v>
       </c>
-      <c r="B108" s="7" t="inlineStr">
-        <is>
-          <t>TIER 4 - NEEDS PHONE</t>
-        </is>
-      </c>
-      <c r="C108" s="7" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="D108" s="7" t="inlineStr"/>
-      <c r="E108" s="7" t="inlineStr">
-        <is>
-          <t>Trust Gorman</t>
-        </is>
-      </c>
-      <c r="F108" s="7" t="inlineStr">
-        <is>
-          <t>904 SANTA ROSA BLVD</t>
-        </is>
-      </c>
-      <c r="G108" s="7" t="inlineStr">
-        <is>
-          <t>FORT WALTON BEACH</t>
-        </is>
-      </c>
-      <c r="H108" s="7" t="inlineStr"/>
-      <c r="I108" s="7" t="inlineStr"/>
-      <c r="J108" s="8" t="n">
-        <v>1842653</v>
-      </c>
-      <c r="K108" s="7" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="L108" s="7" t="inlineStr">
-        <is>
-          <t>Santa Rosa Island (Okaloosa Island) - Gulf front</t>
-        </is>
-      </c>
-      <c r="M108" s="7" t="inlineStr">
-        <is>
-          <t>00-2S-24-2185-0009-0542</t>
-        </is>
-      </c>
-      <c r="N108" s="7" t="inlineStr">
-        <is>
-          <t>904 SANTA ROSA BLVD, FT WALTON BEACH, FL 32548</t>
-        </is>
-      </c>
-      <c r="O108" s="7" t="inlineStr">
-        <is>
-          <t>Ranked #43 of 69. Chosen from Okaloosa County Property Appraiser GIS (single-family use code 0100, assessed $1,842,653). Score 50 = $1.5M+ value (+15); direct Gulf frontage (+25); owner-occupied (+10). Santa Rosa Island (Okaloosa Island) - Gulf front. Owner-occupied (mailing address matches property). In direct Isaias landfall corridor per NHC 1pm Oct 7 advisory (AL/FL border, landfall Fri night). No phone found in free sources.</t>
+      <c r="B108" s="5" t="inlineStr">
+        <is>
+          <t>TIER 3 - NEW NUMBER (unverified)</t>
+        </is>
+      </c>
+      <c r="C108" s="5" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D108" s="5" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="E108" s="5" t="inlineStr">
+        <is>
+          <t>Gary Ybarzabal</t>
+        </is>
+      </c>
+      <c r="F108" s="5" t="inlineStr">
+        <is>
+          <t>1770 Waterford Sound Blvd, Gulf Breeze, FL 32563</t>
+        </is>
+      </c>
+      <c r="G108" s="5" t="inlineStr">
+        <is>
+          <t>Gulf Breeze</t>
+        </is>
+      </c>
+      <c r="H108" s="5" t="inlineStr">
+        <is>
+          <t>(678) 574-3163</t>
+        </is>
+      </c>
+      <c r="I108" s="5" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J108" s="6" t="inlineStr"/>
+      <c r="K108" s="5" t="inlineStr"/>
+      <c r="L108" s="5" t="inlineStr">
+        <is>
+          <t>Gulf Breeze</t>
+        </is>
+      </c>
+      <c r="M108" s="5" t="inlineStr"/>
+      <c r="N108" s="5" t="inlineStr"/>
+      <c r="O108" s="5" t="inlineStr">
+        <is>
+          <t>Waterfront Sound Blvd community on Santa Rosa Sound; GA area code suggests second home — absentee owner needs storm check; sound-front surge exposure; $750K+ homes.</t>
         </is>
       </c>
     </row>
     <row r="109" ht="60" customHeight="1">
-      <c r="A109" s="7" t="n">
+      <c r="A109" s="5" t="n">
         <v>108</v>
       </c>
-      <c r="B109" s="7" t="inlineStr">
-        <is>
-          <t>TIER 4 - NEEDS PHONE</t>
-        </is>
-      </c>
-      <c r="C109" s="7" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="D109" s="7" t="inlineStr"/>
-      <c r="E109" s="7" t="inlineStr">
-        <is>
-          <t>Sandra &amp; Earl Hamilton</t>
-        </is>
-      </c>
-      <c r="F109" s="7" t="inlineStr">
-        <is>
-          <t>707 SAILFISH DR</t>
-        </is>
-      </c>
-      <c r="G109" s="7" t="inlineStr">
-        <is>
-          <t>FORT WALTON BEACH</t>
-        </is>
-      </c>
-      <c r="H109" s="7" t="inlineStr"/>
-      <c r="I109" s="7" t="inlineStr"/>
-      <c r="J109" s="8" t="n">
-        <v>1684345</v>
-      </c>
-      <c r="K109" s="7" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="L109" s="7" t="inlineStr">
-        <is>
-          <t>Santa Rosa Island (Okaloosa Island) - Gulf front</t>
-        </is>
-      </c>
-      <c r="M109" s="7" t="inlineStr">
-        <is>
-          <t>00-2S-24-2185-0007-0384</t>
-        </is>
-      </c>
-      <c r="N109" s="7" t="inlineStr">
-        <is>
-          <t>707 SAILFISH DR, FT WALTON BEACH, FL 32548</t>
-        </is>
-      </c>
-      <c r="O109" s="7" t="inlineStr">
-        <is>
-          <t>Ranked #44 of 69. Chosen from Okaloosa County Property Appraiser GIS (single-family use code 0100, assessed $1,684,345). Score 50 = $1.5M+ value (+15); direct Gulf frontage (+25); owner-occupied (+10). Santa Rosa Island (Okaloosa Island) - Gulf front. Owner-occupied (mailing address matches property). In direct Isaias landfall corridor per NHC 1pm Oct 7 advisory (AL/FL border, landfall Fri night). No phone found in free sources.</t>
-        </is>
-      </c>
+      <c r="B109" s="5" t="inlineStr">
+        <is>
+          <t>TIER 3 - NEW NUMBER (unverified)</t>
+        </is>
+      </c>
+      <c r="C109" s="5" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D109" s="5" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="E109" s="5" t="inlineStr">
+        <is>
+          <t>Paul Ferachi</t>
+        </is>
+      </c>
+      <c r="F109" s="5" t="inlineStr">
+        <is>
+          <t>1774 Ensenada Siete</t>
+        </is>
+      </c>
+      <c r="G109" s="5" t="inlineStr">
+        <is>
+          <t>Pensacola Beach FL 32561</t>
+        </is>
+      </c>
+      <c r="H109" s="5" t="inlineStr">
+        <is>
+          <t>(225) 755-3695; (850) 677-8396</t>
+        </is>
+      </c>
+      <c r="I109" s="5" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J109" s="6" t="inlineStr"/>
+      <c r="K109" s="5" t="inlineStr"/>
+      <c r="L109" s="5" t="inlineStr">
+        <is>
+          <t>Pensacola Beach FL 32561</t>
+        </is>
+      </c>
+      <c r="M109" s="5" t="inlineStr"/>
+      <c r="N109" s="5" t="inlineStr"/>
+      <c r="O109" s="5" t="inlineStr"/>
     </row>
     <row r="110" ht="60" customHeight="1">
       <c r="A110" s="7" t="n">
@@ -8372,29 +8408,29 @@
       </c>
       <c r="C110" s="7" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>85</t>
         </is>
       </c>
       <c r="D110" s="7" t="inlineStr"/>
       <c r="E110" s="7" t="inlineStr">
         <is>
-          <t>Richard V Iii Trust Brown</t>
+          <t>Nicholas J &amp; Susan Z Lembo</t>
         </is>
       </c>
       <c r="F110" s="7" t="inlineStr">
         <is>
-          <t>78 HUTCHINSON ST</t>
+          <t>193 PARADISE BY THE SEA BLVD</t>
         </is>
       </c>
       <c r="G110" s="7" t="inlineStr">
         <is>
-          <t>DESTIN</t>
+          <t>Inlet Beach</t>
         </is>
       </c>
       <c r="H110" s="7" t="inlineStr"/>
       <c r="I110" s="7" t="inlineStr"/>
       <c r="J110" s="8" t="n">
-        <v>4593621</v>
+        <v>28307268</v>
       </c>
       <c r="K110" s="7" t="inlineStr">
         <is>
@@ -8403,22 +8439,22 @@
       </c>
       <c r="L110" s="7" t="inlineStr">
         <is>
-          <t>Hutchinson Courts</t>
+          <t>Gulf of Mexico</t>
         </is>
       </c>
       <c r="M110" s="7" t="inlineStr">
         <is>
-          <t>00-2S-22-5445-0000-0050</t>
+          <t>35-3S-18-16020-00A-0120</t>
         </is>
       </c>
       <c r="N110" s="7" t="inlineStr">
         <is>
-          <t>78 HUTCHINSON ST, DESTIN, FL 32541</t>
+          <t>193 PARADISE BY THE SEA BLVD, Inlet Beach, FL 32461</t>
         </is>
       </c>
       <c r="O110" s="7" t="inlineStr">
         <is>
-          <t>Ranked #57 of 69. Chosen from Okaloosa County Property Appraiser GIS (single-family use code 0100, assessed $4,593,621). Score 35 = $3M+ value (+25); owner-occupied (+10). Hutchinson Courts. Owner-occupied (mailing address matches property). In direct Isaias landfall corridor per NHC 1pm Oct 7 advisory (AL/FL border, landfall Fri night). No phone found in free sources.</t>
+          <t>Score 65: $28.3M value (+30), direct Gulf frontage (+25), owner-occupied (+10). In eastern damage corridor per NHC Oct 7 advisory.</t>
         </is>
       </c>
     </row>
@@ -8433,29 +8469,29 @@
       </c>
       <c r="C111" s="7" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>75</t>
         </is>
       </c>
       <c r="D111" s="7" t="inlineStr"/>
       <c r="E111" s="7" t="inlineStr">
         <is>
-          <t>Family Trust Wilson</t>
+          <t>Trust Gorman</t>
         </is>
       </c>
       <c r="F111" s="7" t="inlineStr">
         <is>
-          <t>528 BAYVIEW ST</t>
+          <t>904 SANTA ROSA BLVD</t>
         </is>
       </c>
       <c r="G111" s="7" t="inlineStr">
         <is>
-          <t>DESTIN</t>
+          <t>FORT WALTON BEACH</t>
         </is>
       </c>
       <c r="H111" s="7" t="inlineStr"/>
       <c r="I111" s="7" t="inlineStr"/>
       <c r="J111" s="8" t="n">
-        <v>4191571</v>
+        <v>1842653</v>
       </c>
       <c r="K111" s="7" t="inlineStr">
         <is>
@@ -8464,22 +8500,22 @@
       </c>
       <c r="L111" s="7" t="inlineStr">
         <is>
-          <t>Joes Bayou waterfront</t>
+          <t>Santa Rosa Island (Okaloosa Island) - Gulf front</t>
         </is>
       </c>
       <c r="M111" s="7" t="inlineStr">
         <is>
-          <t>00-2S-22-1320-0040-0010</t>
+          <t>00-2S-24-2185-0009-0542</t>
         </is>
       </c>
       <c r="N111" s="7" t="inlineStr">
         <is>
-          <t>524 BAYVIEW ST, DESTIN, FL 32541</t>
+          <t>904 SANTA ROSA BLVD, FT WALTON BEACH, FL 32548</t>
         </is>
       </c>
       <c r="O111" s="7" t="inlineStr">
         <is>
-          <t>Ranked #37 of 69. Chosen from Okaloosa County Property Appraiser GIS (single-family use code 0100, assessed $4,191,571). Score 50 = $3M+ value (+25); bayou waterfront (+15); owner-occupied (+10). Joes Bayou waterfront. Owner-occupied (mailing address matches property). In direct Isaias landfall corridor per NHC 1pm Oct 7 advisory (AL/FL border, landfall Fri night). No phone found in free sources.</t>
+          <t>Ranked #43 of 69. Chosen from Okaloosa County Property Appraiser GIS (single-family use code 0100, assessed $1,842,653). Score 50 = $1.5M+ value (+15); direct Gulf frontage (+25); owner-occupied (+10). Santa Rosa Island (Okaloosa Island) - Gulf front. Owner-occupied (mailing address matches property). In direct Isaias landfall corridor per NHC 1pm Oct 7 advisory (AL/FL border, landfall Fri night). No phone found in free sources.</t>
         </is>
       </c>
     </row>
@@ -8494,29 +8530,29 @@
       </c>
       <c r="C112" s="7" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>75</t>
         </is>
       </c>
       <c r="D112" s="7" t="inlineStr"/>
       <c r="E112" s="7" t="inlineStr">
         <is>
-          <t>William Neal Perkins And Karron Lee Perkins</t>
+          <t>Sandra &amp; Earl Hamilton</t>
         </is>
       </c>
       <c r="F112" s="7" t="inlineStr">
         <is>
-          <t>26594 Cotton Bayou Dr</t>
+          <t>707 SAILFISH DR</t>
         </is>
       </c>
       <c r="G112" s="7" t="inlineStr">
         <is>
-          <t>Orange Beach</t>
+          <t>FORT WALTON BEACH</t>
         </is>
       </c>
       <c r="H112" s="7" t="inlineStr"/>
       <c r="I112" s="7" t="inlineStr"/>
       <c r="J112" s="8" t="n">
-        <v>3117300</v>
+        <v>1684345</v>
       </c>
       <c r="K112" s="7" t="inlineStr">
         <is>
@@ -8525,22 +8561,22 @@
       </c>
       <c r="L112" s="7" t="inlineStr">
         <is>
-          <t>Cotton Bayou</t>
+          <t>Santa Rosa Island (Okaloosa Island) - Gulf front</t>
         </is>
       </c>
       <c r="M112" s="7" t="inlineStr">
         <is>
-          <t>65-02-09-0-001-211.000</t>
+          <t>00-2S-24-2185-0007-0384</t>
         </is>
       </c>
       <c r="N112" s="7" t="inlineStr">
         <is>
-          <t>26594 COTTON BAYOU DR, ORANGE BEACH, AL 36561-3517</t>
+          <t>707 SAILFISH DR, FT WALTON BEACH, FL 32548</t>
         </is>
       </c>
       <c r="O112" s="7" t="inlineStr">
         <is>
-          <t>Score 55: $3.12M county assessed value (+30); Cotton Bayou frontage (+15); owner-occupied (+10); no phone found in free sources (+0). Owner-occupied Cotton Bayou waterfront; $3.1M assessed. No phone found in free sources. In direct landfall corridor per NHC Oct 7 advisory - Tropical Storm Isaias landfall expected near AL/FL border Friday night.</t>
+          <t>Ranked #44 of 69. Chosen from Okaloosa County Property Appraiser GIS (single-family use code 0100, assessed $1,684,345). Score 50 = $1.5M+ value (+15); direct Gulf frontage (+25); owner-occupied (+10). Santa Rosa Island (Okaloosa Island) - Gulf front. Owner-occupied (mailing address matches property). In direct Isaias landfall corridor per NHC 1pm Oct 7 advisory (AL/FL border, landfall Fri night). No phone found in free sources.</t>
         </is>
       </c>
     </row>
@@ -8561,23 +8597,23 @@
       <c r="D113" s="7" t="inlineStr"/>
       <c r="E113" s="7" t="inlineStr">
         <is>
-          <t>Bobby Gelpi</t>
+          <t>Richard V Iii Trust Brown</t>
         </is>
       </c>
       <c r="F113" s="7" t="inlineStr">
         <is>
-          <t>222 Ariola Dr</t>
+          <t>78 HUTCHINSON ST</t>
         </is>
       </c>
       <c r="G113" s="7" t="inlineStr">
         <is>
-          <t>Pensacola Beach</t>
+          <t>DESTIN</t>
         </is>
       </c>
       <c r="H113" s="7" t="inlineStr"/>
       <c r="I113" s="7" t="inlineStr"/>
       <c r="J113" s="8" t="n">
-        <v>750000</v>
+        <v>4593621</v>
       </c>
       <c r="K113" s="7" t="inlineStr">
         <is>
@@ -8586,18 +8622,22 @@
       </c>
       <c r="L113" s="7" t="inlineStr">
         <is>
-          <t>Gulf of Mexico</t>
+          <t>Hutchinson Courts</t>
         </is>
       </c>
       <c r="M113" s="7" t="inlineStr">
         <is>
-          <t>282S261800002016</t>
-        </is>
-      </c>
-      <c r="N113" s="7" t="inlineStr"/>
+          <t>00-2S-22-5445-0000-0050</t>
+        </is>
+      </c>
+      <c r="N113" s="7" t="inlineStr">
+        <is>
+          <t>78 HUTCHINSON ST, DESTIN, FL 32541</t>
+        </is>
+      </c>
       <c r="O113" s="7" t="inlineStr">
         <is>
-          <t>Score 60: direct Gulf frontage (+25), ~$750K est. value (+25), owner-occupied (+10), no phone (+0). 2,696 sqft. In direct landfall corridor per NHC 1pm Oct 7 advisory — landfall expected near AL/FL border Friday night.</t>
+          <t>Ranked #57 of 69. Chosen from Okaloosa County Property Appraiser GIS (single-family use code 0100, assessed $4,593,621). Score 35 = $3M+ value (+25); owner-occupied (+10). Hutchinson Courts. Owner-occupied (mailing address matches property). In direct Isaias landfall corridor per NHC 1pm Oct 7 advisory (AL/FL border, landfall Fri night). No phone found in free sources.</t>
         </is>
       </c>
     </row>
@@ -8612,49 +8652,53 @@
       </c>
       <c r="C114" s="7" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>70</t>
         </is>
       </c>
       <c r="D114" s="7" t="inlineStr"/>
       <c r="E114" s="7" t="inlineStr">
         <is>
-          <t>Lela Griffin Hilton</t>
+          <t>William Neal Perkins And Karron Lee Perkins</t>
         </is>
       </c>
       <c r="F114" s="7" t="inlineStr">
         <is>
-          <t>289 PARADISE BY THE SEA BLVD</t>
+          <t>26594 Cotton Bayou Dr</t>
         </is>
       </c>
       <c r="G114" s="7" t="inlineStr">
         <is>
-          <t>Inlet Beach</t>
+          <t>Orange Beach</t>
         </is>
       </c>
       <c r="H114" s="7" t="inlineStr"/>
       <c r="I114" s="7" t="inlineStr"/>
       <c r="J114" s="8" t="n">
-        <v>23046257</v>
+        <v>3117300</v>
       </c>
       <c r="K114" s="7" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="L114" s="7" t="inlineStr">
         <is>
-          <t>Gulf of Mexico</t>
-        </is>
-      </c>
-      <c r="M114" s="7" t="inlineStr"/>
+          <t>Cotton Bayou</t>
+        </is>
+      </c>
+      <c r="M114" s="7" t="inlineStr">
+        <is>
+          <t>65-02-09-0-001-211.000</t>
+        </is>
+      </c>
       <c r="N114" s="7" t="inlineStr">
         <is>
-          <t>289 PARADISE BY THE SEA BLVD, Inlet Beach, FL 32461</t>
+          <t>26594 COTTON BAYOU DR, ORANGE BEACH, AL 36561-3517</t>
         </is>
       </c>
       <c r="O114" s="7" t="inlineStr">
         <is>
-          <t>Score 55: $23.0M value (+30), direct Gulf frontage (+25). In eastern damage corridor per NHC Oct 7 advisory.</t>
+          <t>Score 55: $3.12M county assessed value (+30); Cotton Bayou frontage (+15); owner-occupied (+10); no phone found in free sources (+0). Owner-occupied Cotton Bayou waterfront; $3.1M assessed. No phone found in free sources. In direct landfall corridor per NHC Oct 7 advisory - Tropical Storm Isaias landfall expected near AL/FL border Friday night.</t>
         </is>
       </c>
     </row>
@@ -8669,53 +8713,49 @@
       </c>
       <c r="C115" s="7" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>70</t>
         </is>
       </c>
       <c r="D115" s="7" t="inlineStr"/>
       <c r="E115" s="7" t="inlineStr">
         <is>
-          <t>J &amp; J Okaloosa Trust Lincoln</t>
+          <t>Bobby Gelpi</t>
         </is>
       </c>
       <c r="F115" s="7" t="inlineStr">
         <is>
-          <t>4772 OCEAN BLVD</t>
+          <t>222 Ariola Dr</t>
         </is>
       </c>
       <c r="G115" s="7" t="inlineStr">
         <is>
-          <t>DESTIN</t>
+          <t>Pensacola Beach</t>
         </is>
       </c>
       <c r="H115" s="7" t="inlineStr"/>
       <c r="I115" s="7" t="inlineStr"/>
       <c r="J115" s="8" t="n">
-        <v>7896714</v>
+        <v>750000</v>
       </c>
       <c r="K115" s="7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="L115" s="7" t="inlineStr">
         <is>
-          <t>Destiny by the Sea - direct Gulf front</t>
+          <t>Gulf of Mexico</t>
         </is>
       </c>
       <c r="M115" s="7" t="inlineStr">
         <is>
-          <t>00-2S-22-0075-0000-0240</t>
-        </is>
-      </c>
-      <c r="N115" s="7" t="inlineStr">
-        <is>
-          <t>PO BOX 1559, SIKESTON, MO 63801</t>
-        </is>
-      </c>
+          <t>282S261800002016</t>
+        </is>
+      </c>
+      <c r="N115" s="7" t="inlineStr"/>
       <c r="O115" s="7" t="inlineStr">
         <is>
-          <t>Ranked #30 of 69. Chosen from Okaloosa County Property Appraiser GIS (single-family use code 0100, assessed $7,896,714). Score 55 = $5M+ value (+30); direct Gulf frontage (+25). Destiny by the Sea - direct Gulf front. Second/vacation home (out-of-area mailing address) - absentee owner; storm damage still needs a local cleanup crew fast. In direct Isaias landfall corridor per NHC 1pm Oct 7 advisory (AL/FL border, landfall Fri night). No phone found in free sources.</t>
+          <t>Score 60: direct Gulf frontage (+25), ~$750K est. value (+25), owner-occupied (+10), no phone (+0). 2,696 sqft. In direct landfall corridor per NHC 1pm Oct 7 advisory — landfall expected near AL/FL border Friday night.</t>
         </is>
       </c>
     </row>
@@ -8736,47 +8776,43 @@
       <c r="D116" s="7" t="inlineStr"/>
       <c r="E116" s="7" t="inlineStr">
         <is>
-          <t>Dane R &amp; Karin Wysocki</t>
+          <t>Lela Griffin Hilton</t>
         </is>
       </c>
       <c r="F116" s="7" t="inlineStr">
         <is>
-          <t>2980 SCENIC HIGHWAY 98</t>
+          <t>289 PARADISE BY THE SEA BLVD</t>
         </is>
       </c>
       <c r="G116" s="7" t="inlineStr">
         <is>
-          <t>DESTIN</t>
+          <t>Inlet Beach</t>
         </is>
       </c>
       <c r="H116" s="7" t="inlineStr"/>
       <c r="I116" s="7" t="inlineStr"/>
       <c r="J116" s="8" t="n">
-        <v>7205772</v>
+        <v>23046257</v>
       </c>
       <c r="K116" s="7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="L116" s="7" t="inlineStr">
         <is>
-          <t>Shores of Crystal Beach - Gulf front</t>
-        </is>
-      </c>
-      <c r="M116" s="7" t="inlineStr">
-        <is>
-          <t>00-2S-22-0584-0000-0080</t>
-        </is>
-      </c>
+          <t>Gulf of Mexico</t>
+        </is>
+      </c>
+      <c r="M116" s="7" t="inlineStr"/>
       <c r="N116" s="7" t="inlineStr">
         <is>
-          <t>1338 BALLYBUNION CT SE, GRAND RAPIDE, MI 49546</t>
+          <t>289 PARADISE BY THE SEA BLVD, Inlet Beach, FL 32461</t>
         </is>
       </c>
       <c r="O116" s="7" t="inlineStr">
         <is>
-          <t>Ranked #31 of 69. Chosen from Okaloosa County Property Appraiser GIS (single-family use code 0100, assessed $7,205,772). Score 55 = $5M+ value (+30); direct Gulf frontage (+25). Shores of Crystal Beach - Gulf front. Second/vacation home (out-of-area mailing address) - absentee owner; storm damage still needs a local cleanup crew fast. In direct Isaias landfall corridor per NHC 1pm Oct 7 advisory (AL/FL border, landfall Fri night). No phone found in free sources.</t>
+          <t>Score 55: $23.0M value (+30), direct Gulf frontage (+25). In eastern damage corridor per NHC Oct 7 advisory.</t>
         </is>
       </c>
     </row>
@@ -8797,47 +8833,47 @@
       <c r="D117" s="7" t="inlineStr"/>
       <c r="E117" s="7" t="inlineStr">
         <is>
-          <t>Joseph &amp; Beverly Wallace</t>
+          <t>J &amp; J Okaloosa Trust Lincoln</t>
         </is>
       </c>
       <c r="F117" s="7" t="inlineStr">
         <is>
-          <t>249 YACHT CLUB DR NE</t>
+          <t>4772 OCEAN BLVD</t>
         </is>
       </c>
       <c r="G117" s="7" t="inlineStr">
         <is>
-          <t>FORT WALTON BEACH</t>
+          <t>DESTIN</t>
         </is>
       </c>
       <c r="H117" s="7" t="inlineStr"/>
       <c r="I117" s="7" t="inlineStr"/>
       <c r="J117" s="8" t="n">
-        <v>2828568</v>
+        <v>7896714</v>
       </c>
       <c r="K117" s="7" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="L117" s="7" t="inlineStr">
         <is>
-          <t>Hughes Estates - Choctawhatchee Bay</t>
+          <t>Destiny by the Sea - direct Gulf front</t>
         </is>
       </c>
       <c r="M117" s="7" t="inlineStr">
         <is>
-          <t>12-2S-24-1251-0002-0070</t>
+          <t>00-2S-22-0075-0000-0240</t>
         </is>
       </c>
       <c r="N117" s="7" t="inlineStr">
         <is>
-          <t>249 YACHT CLUB DR, FT WALTON BEACH, FL 32548</t>
+          <t>PO BOX 1559, SIKESTON, MO 63801</t>
         </is>
       </c>
       <c r="O117" s="7" t="inlineStr">
         <is>
-          <t>Ranked #47 of 69. Chosen from Okaloosa County Property Appraiser GIS (single-family use code 0100, assessed $2,828,568). Score 45 = $2M+ value (+20); bay/lagoon waterfront (+15); owner-occupied (+10). Hughes Estates - Choctawhatchee Bay. Owner-occupied (mailing address matches property). In direct Isaias landfall corridor per NHC 1pm Oct 7 advisory (AL/FL border, landfall Fri night). No phone found in free sources.</t>
+          <t>Ranked #30 of 69. Chosen from Okaloosa County Property Appraiser GIS (single-family use code 0100, assessed $7,896,714). Score 55 = $5M+ value (+30); direct Gulf frontage (+25). Destiny by the Sea - direct Gulf front. Second/vacation home (out-of-area mailing address) - absentee owner; storm damage still needs a local cleanup crew fast. In direct Isaias landfall corridor per NHC 1pm Oct 7 advisory (AL/FL border, landfall Fri night). No phone found in free sources.</t>
         </is>
       </c>
     </row>
@@ -8858,47 +8894,47 @@
       <c r="D118" s="7" t="inlineStr"/>
       <c r="E118" s="7" t="inlineStr">
         <is>
-          <t>Murray Paul Farmer</t>
+          <t>Dane R &amp; Karin Wysocki</t>
         </is>
       </c>
       <c r="F118" s="7" t="inlineStr">
         <is>
-          <t>29765 Saint John Dr</t>
+          <t>2980 SCENIC HIGHWAY 98</t>
         </is>
       </c>
       <c r="G118" s="7" t="inlineStr">
         <is>
-          <t>Orange Beach</t>
+          <t>DESTIN</t>
         </is>
       </c>
       <c r="H118" s="7" t="inlineStr"/>
       <c r="I118" s="7" t="inlineStr"/>
       <c r="J118" s="8" t="n">
-        <v>2794100</v>
+        <v>7205772</v>
       </c>
       <c r="K118" s="7" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="L118" s="7" t="inlineStr">
         <is>
-          <t>Bayou St. John</t>
+          <t>Shores of Crystal Beach - Gulf front</t>
         </is>
       </c>
       <c r="M118" s="7" t="inlineStr">
         <is>
-          <t>65-01-01-0-000-001.121</t>
+          <t>00-2S-22-0584-0000-0080</t>
         </is>
       </c>
       <c r="N118" s="7" t="inlineStr">
         <is>
-          <t>29765 SAINT JOHN DR, ORANGE BEACH, AL 36561-3625</t>
+          <t>1338 BALLYBUNION CT SE, GRAND RAPIDE, MI 49546</t>
         </is>
       </c>
       <c r="O118" s="7" t="inlineStr">
         <is>
-          <t>Score 55: $2.79M county assessed value (+30); Bayou St. John frontage (+15); owner-occupied (+10); no phone found in free sources (+0). Owner-occupied bayou-front estate; $2.79M assessed. No phone found in free sources. In direct landfall corridor per NHC Oct 7 advisory - Tropical Storm Isaias landfall expected near AL/FL border Friday night.</t>
+          <t>Ranked #31 of 69. Chosen from Okaloosa County Property Appraiser GIS (single-family use code 0100, assessed $7,205,772). Score 55 = $5M+ value (+30); direct Gulf frontage (+25). Shores of Crystal Beach - Gulf front. Second/vacation home (out-of-area mailing address) - absentee owner; storm damage still needs a local cleanup crew fast. In direct Isaias landfall corridor per NHC 1pm Oct 7 advisory (AL/FL border, landfall Fri night). No phone found in free sources.</t>
         </is>
       </c>
     </row>
@@ -8919,23 +8955,23 @@
       <c r="D119" s="7" t="inlineStr"/>
       <c r="E119" s="7" t="inlineStr">
         <is>
-          <t>Morgan D Kitchens And Madalyn B Kitchens</t>
+          <t>Joseph &amp; Beverly Wallace</t>
         </is>
       </c>
       <c r="F119" s="7" t="inlineStr">
         <is>
-          <t>28430 Ono Blvd</t>
+          <t>249 YACHT CLUB DR NE</t>
         </is>
       </c>
       <c r="G119" s="7" t="inlineStr">
         <is>
-          <t>Orange Beach</t>
+          <t>FORT WALTON BEACH</t>
         </is>
       </c>
       <c r="H119" s="7" t="inlineStr"/>
       <c r="I119" s="7" t="inlineStr"/>
       <c r="J119" s="8" t="n">
-        <v>2449400</v>
+        <v>2828568</v>
       </c>
       <c r="K119" s="7" t="inlineStr">
         <is>
@@ -8944,22 +8980,22 @@
       </c>
       <c r="L119" s="7" t="inlineStr">
         <is>
-          <t>Ole River (Ono Island)</t>
+          <t>Hughes Estates - Choctawhatchee Bay</t>
         </is>
       </c>
       <c r="M119" s="7" t="inlineStr">
         <is>
-          <t>65-01-11-0-000-030.016</t>
+          <t>12-2S-24-1251-0002-0070</t>
         </is>
       </c>
       <c r="N119" s="7" t="inlineStr">
         <is>
-          <t>28430 ONO BLVD, ORANGE BEACH, AL 36561-3605</t>
+          <t>249 YACHT CLUB DR, FT WALTON BEACH, FL 32548</t>
         </is>
       </c>
       <c r="O119" s="7" t="inlineStr">
         <is>
-          <t>Score 55: $2.45M county assessed value (+30); Ole River (Ono Island) frontage (+15); owner-occupied (+10); no phone found in free sources (+0). Owner-occupied Ono Island waterfront; $2.45M assessed. Only masked phones in free sources. In direct landfall corridor per NHC Oct 7 advisory - Tropical Storm Isaias landfall expected near AL/FL border Friday night.</t>
+          <t>Ranked #47 of 69. Chosen from Okaloosa County Property Appraiser GIS (single-family use code 0100, assessed $2,828,568). Score 45 = $2M+ value (+20); bay/lagoon waterfront (+15); owner-occupied (+10). Hughes Estates - Choctawhatchee Bay. Owner-occupied (mailing address matches property). In direct Isaias landfall corridor per NHC 1pm Oct 7 advisory (AL/FL border, landfall Fri night). No phone found in free sources.</t>
         </is>
       </c>
     </row>
@@ -8980,23 +9016,23 @@
       <c r="D120" s="7" t="inlineStr"/>
       <c r="E120" s="7" t="inlineStr">
         <is>
-          <t>Timothy &amp; Sharon L Smith</t>
+          <t>Murray Paul Farmer</t>
         </is>
       </c>
       <c r="F120" s="7" t="inlineStr">
         <is>
-          <t>912 SARA DR</t>
+          <t>29765 Saint John Dr</t>
         </is>
       </c>
       <c r="G120" s="7" t="inlineStr">
         <is>
-          <t>SHALIMAR</t>
+          <t>Orange Beach</t>
         </is>
       </c>
       <c r="H120" s="7" t="inlineStr"/>
       <c r="I120" s="7" t="inlineStr"/>
       <c r="J120" s="8" t="n">
-        <v>2321206</v>
+        <v>2794100</v>
       </c>
       <c r="K120" s="7" t="inlineStr">
         <is>
@@ -9005,22 +9041,22 @@
       </c>
       <c r="L120" s="7" t="inlineStr">
         <is>
-          <t>Shalimar Plantation</t>
+          <t>Bayou St. John</t>
         </is>
       </c>
       <c r="M120" s="7" t="inlineStr">
         <is>
-          <t>06-2S-23-2238-000A-0130</t>
+          <t>65-01-01-0-000-001.121</t>
         </is>
       </c>
       <c r="N120" s="7" t="inlineStr">
         <is>
-          <t>912 SARA DR, SHALIMAR, FL 32579</t>
+          <t>29765 SAINT JOHN DR, ORANGE BEACH, AL 36561-3625</t>
         </is>
       </c>
       <c r="O120" s="7" t="inlineStr">
         <is>
-          <t>Ranked #60 of 69. Chosen from Okaloosa County Property Appraiser GIS (single-family use code 0100, assessed $2,321,206). Score 30 = $2M+ value (+20); owner-occupied (+10). Shalimar Plantation. Owner-occupied (mailing address matches property). In direct Isaias landfall corridor per NHC 1pm Oct 7 advisory (AL/FL border, landfall Fri night). No phone found in free sources.</t>
+          <t>Score 55: $2.79M county assessed value (+30); Bayou St. John frontage (+15); owner-occupied (+10); no phone found in free sources (+0). Owner-occupied bayou-front estate; $2.79M assessed. No phone found in free sources. In direct landfall corridor per NHC Oct 7 advisory - Tropical Storm Isaias landfall expected near AL/FL border Friday night.</t>
         </is>
       </c>
     </row>
@@ -9041,12 +9077,12 @@
       <c r="D121" s="7" t="inlineStr"/>
       <c r="E121" s="7" t="inlineStr">
         <is>
-          <t>John Gilbert Aufdenkampe Jr And Pamela Paugh Romano</t>
+          <t>Morgan D Kitchens And Madalyn B Kitchens</t>
         </is>
       </c>
       <c r="F121" s="7" t="inlineStr">
         <is>
-          <t>29201 Ono Blvd</t>
+          <t>28430 Ono Blvd</t>
         </is>
       </c>
       <c r="G121" s="7" t="inlineStr">
@@ -9057,7 +9093,7 @@
       <c r="H121" s="7" t="inlineStr"/>
       <c r="I121" s="7" t="inlineStr"/>
       <c r="J121" s="8" t="n">
-        <v>1981900</v>
+        <v>2449400</v>
       </c>
       <c r="K121" s="7" t="inlineStr">
         <is>
@@ -9071,17 +9107,17 @@
       </c>
       <c r="M121" s="7" t="inlineStr">
         <is>
-          <t>65-01-01-0-000-001.075</t>
+          <t>65-01-11-0-000-030.016</t>
         </is>
       </c>
       <c r="N121" s="7" t="inlineStr">
         <is>
-          <t>29201 ONO BLVD, ORANGE BEACH, AL 36561-3620</t>
+          <t>28430 ONO BLVD, ORANGE BEACH, AL 36561-3605</t>
         </is>
       </c>
       <c r="O121" s="7" t="inlineStr">
         <is>
-          <t>Score 55: $1.98M county assessed value (+30); Ole River (Ono Island) frontage (+15); owner-occupied (+10); no phone found in free sources (+0). Owner-occupied Ono Island waterfront; $1.98M assessed. No phone found in free sources. In direct landfall corridor per NHC Oct 7 advisory - Tropical Storm Isaias landfall expected near AL/FL border Friday night.</t>
+          <t>Score 55: $2.45M county assessed value (+30); Ole River (Ono Island) frontage (+15); owner-occupied (+10); no phone found in free sources (+0). Owner-occupied Ono Island waterfront; $2.45M assessed. Only masked phones in free sources. In direct landfall corridor per NHC Oct 7 advisory - Tropical Storm Isaias landfall expected near AL/FL border Friday night.</t>
         </is>
       </c>
     </row>
@@ -9102,23 +9138,23 @@
       <c r="D122" s="7" t="inlineStr"/>
       <c r="E122" s="7" t="inlineStr">
         <is>
-          <t>Family Trust Gourley</t>
+          <t>Timothy &amp; Sharon L Smith</t>
         </is>
       </c>
       <c r="F122" s="7" t="inlineStr">
         <is>
-          <t>229 MOONEY RD NE</t>
+          <t>912 SARA DR</t>
         </is>
       </c>
       <c r="G122" s="7" t="inlineStr">
         <is>
-          <t>FORT WALTON BEACH</t>
+          <t>SHALIMAR</t>
         </is>
       </c>
       <c r="H122" s="7" t="inlineStr"/>
       <c r="I122" s="7" t="inlineStr"/>
       <c r="J122" s="8" t="n">
-        <v>1959871</v>
+        <v>2321206</v>
       </c>
       <c r="K122" s="7" t="inlineStr">
         <is>
@@ -9127,22 +9163,22 @@
       </c>
       <c r="L122" s="7" t="inlineStr">
         <is>
-          <t>Mooney Rd - near bay</t>
+          <t>Shalimar Plantation</t>
         </is>
       </c>
       <c r="M122" s="7" t="inlineStr">
         <is>
-          <t>36-1S-24-0000-0005-0020</t>
+          <t>06-2S-23-2238-000A-0130</t>
         </is>
       </c>
       <c r="N122" s="7" t="inlineStr">
         <is>
-          <t>229 MOONEY RD NE, FT WALTON BEACH, FL 32547</t>
+          <t>912 SARA DR, SHALIMAR, FL 32579</t>
         </is>
       </c>
       <c r="O122" s="7" t="inlineStr">
         <is>
-          <t>Ranked #49 of 69. Chosen from Okaloosa County Property Appraiser GIS (single-family use code 0100, assessed $1,959,871). Score 40 = $1.5M+ value (+15); bay/lagoon waterfront (+15); owner-occupied (+10). Mooney Rd - near bay. Owner-occupied (mailing address matches property). In direct Isaias landfall corridor per NHC 1pm Oct 7 advisory (AL/FL border, landfall Fri night). No phone found in free sources.</t>
+          <t>Ranked #60 of 69. Chosen from Okaloosa County Property Appraiser GIS (single-family use code 0100, assessed $2,321,206). Score 30 = $2M+ value (+20); owner-occupied (+10). Shalimar Plantation. Owner-occupied (mailing address matches property). In direct Isaias landfall corridor per NHC 1pm Oct 7 advisory (AL/FL border, landfall Fri night). No phone found in free sources.</t>
         </is>
       </c>
     </row>
@@ -9163,23 +9199,23 @@
       <c r="D123" s="7" t="inlineStr"/>
       <c r="E123" s="7" t="inlineStr">
         <is>
-          <t>Ty A &amp; Kimberly C Pennington</t>
+          <t>John Gilbert Aufdenkampe Jr And Pamela Paugh Romano</t>
         </is>
       </c>
       <c r="F123" s="7" t="inlineStr">
         <is>
-          <t>13 POQUITO RD</t>
+          <t>29201 Ono Blvd</t>
         </is>
       </c>
       <c r="G123" s="7" t="inlineStr">
         <is>
-          <t>SHALIMAR</t>
+          <t>Orange Beach</t>
         </is>
       </c>
       <c r="H123" s="7" t="inlineStr"/>
       <c r="I123" s="7" t="inlineStr"/>
       <c r="J123" s="8" t="n">
-        <v>1898688</v>
+        <v>1981900</v>
       </c>
       <c r="K123" s="7" t="inlineStr">
         <is>
@@ -9188,22 +9224,22 @@
       </c>
       <c r="L123" s="7" t="inlineStr">
         <is>
-          <t>Bayou Poquito waterfront</t>
+          <t>Ole River (Ono Island)</t>
         </is>
       </c>
       <c r="M123" s="7" t="inlineStr">
         <is>
-          <t>31-1S-23-0120-0016-0050</t>
+          <t>65-01-01-0-000-001.075</t>
         </is>
       </c>
       <c r="N123" s="7" t="inlineStr">
         <is>
-          <t>13 POQUITO RD, SHALIMAR, FL 32579</t>
+          <t>29201 ONO BLVD, ORANGE BEACH, AL 36561-3620</t>
         </is>
       </c>
       <c r="O123" s="7" t="inlineStr">
         <is>
-          <t>Ranked #50 of 69. Chosen from Okaloosa County Property Appraiser GIS (single-family use code 0100, assessed $1,898,688). Score 40 = $1.5M+ value (+15); bayou waterfront (+15); owner-occupied (+10). Bayou Poquito waterfront. Owner-occupied (mailing address matches property). In direct Isaias landfall corridor per NHC 1pm Oct 7 advisory (AL/FL border, landfall Fri night). No phone found in free sources.</t>
+          <t>Score 55: $1.98M county assessed value (+30); Ole River (Ono Island) frontage (+15); owner-occupied (+10); no phone found in free sources (+0). Owner-occupied Ono Island waterfront; $1.98M assessed. No phone found in free sources. In direct landfall corridor per NHC Oct 7 advisory - Tropical Storm Isaias landfall expected near AL/FL border Friday night.</t>
         </is>
       </c>
     </row>
@@ -9224,12 +9260,12 @@
       <c r="D124" s="7" t="inlineStr"/>
       <c r="E124" s="7" t="inlineStr">
         <is>
-          <t>Jason &amp; Katie Shull</t>
+          <t>Family Trust Gourley</t>
         </is>
       </c>
       <c r="F124" s="7" t="inlineStr">
         <is>
-          <t>258 BROOKS ST SE</t>
+          <t>229 MOONEY RD NE</t>
         </is>
       </c>
       <c r="G124" s="7" t="inlineStr">
@@ -9240,7 +9276,7 @@
       <c r="H124" s="7" t="inlineStr"/>
       <c r="I124" s="7" t="inlineStr"/>
       <c r="J124" s="8" t="n">
-        <v>1836860</v>
+        <v>1959871</v>
       </c>
       <c r="K124" s="7" t="inlineStr">
         <is>
@@ -9249,22 +9285,22 @@
       </c>
       <c r="L124" s="7" t="inlineStr">
         <is>
-          <t>Bay Towne View - bay</t>
+          <t>Mooney Rd - near bay</t>
         </is>
       </c>
       <c r="M124" s="7" t="inlineStr">
         <is>
-          <t>24-2S-24-0200-0000-0020</t>
+          <t>36-1S-24-0000-0005-0020</t>
         </is>
       </c>
       <c r="N124" s="7" t="inlineStr">
         <is>
-          <t>258 BROOKS ST, FT WALTON BEACH, FL 32548</t>
+          <t>229 MOONEY RD NE, FT WALTON BEACH, FL 32547</t>
         </is>
       </c>
       <c r="O124" s="7" t="inlineStr">
         <is>
-          <t>Ranked #51 of 69. Chosen from Okaloosa County Property Appraiser GIS (single-family use code 0100, assessed $1,836,860). Score 40 = $1.5M+ value (+15); bay/lagoon waterfront (+15); owner-occupied (+10). Bay Towne View - bay. Owner-occupied (mailing address matches property). In direct Isaias landfall corridor per NHC 1pm Oct 7 advisory (AL/FL border, landfall Fri night). No phone found in free sources.</t>
+          <t>Ranked #49 of 69. Chosen from Okaloosa County Property Appraiser GIS (single-family use code 0100, assessed $1,959,871). Score 40 = $1.5M+ value (+15); bay/lagoon waterfront (+15); owner-occupied (+10). Mooney Rd - near bay. Owner-occupied (mailing address matches property). In direct Isaias landfall corridor per NHC 1pm Oct 7 advisory (AL/FL border, landfall Fri night). No phone found in free sources.</t>
         </is>
       </c>
     </row>
@@ -9285,12 +9321,12 @@
       <c r="D125" s="7" t="inlineStr"/>
       <c r="E125" s="7" t="inlineStr">
         <is>
-          <t>Rev Living Trust Wampler</t>
+          <t>Jason &amp; Katie Shull</t>
         </is>
       </c>
       <c r="F125" s="7" t="inlineStr">
         <is>
-          <t>327 BEAL PKWY NW</t>
+          <t>258 BROOKS ST SE</t>
         </is>
       </c>
       <c r="G125" s="7" t="inlineStr">
@@ -9301,7 +9337,7 @@
       <c r="H125" s="7" t="inlineStr"/>
       <c r="I125" s="7" t="inlineStr"/>
       <c r="J125" s="8" t="n">
-        <v>1782993</v>
+        <v>1836860</v>
       </c>
       <c r="K125" s="7" t="inlineStr">
         <is>
@@ -9310,22 +9346,22 @@
       </c>
       <c r="L125" s="7" t="inlineStr">
         <is>
-          <t>Beal Pkwy - near bay</t>
+          <t>Bay Towne View - bay</t>
         </is>
       </c>
       <c r="M125" s="7" t="inlineStr">
         <is>
-          <t>10-2S-24-0000-0041-0000</t>
+          <t>24-2S-24-0200-0000-0020</t>
         </is>
       </c>
       <c r="N125" s="7" t="inlineStr">
         <is>
-          <t>327 BEAL PKWY NW, FT WALTON BEACH, FL 32548</t>
+          <t>258 BROOKS ST, FT WALTON BEACH, FL 32548</t>
         </is>
       </c>
       <c r="O125" s="7" t="inlineStr">
         <is>
-          <t>Ranked #53 of 69. Chosen from Okaloosa County Property Appraiser GIS (single-family use code 0100, assessed $1,782,993). Score 40 = $1.5M+ value (+15); bay/lagoon waterfront (+15); owner-occupied (+10). Beal Pkwy - near bay. Owner-occupied (mailing address matches property). In direct Isaias landfall corridor per NHC 1pm Oct 7 advisory (AL/FL border, landfall Fri night). No phone found in free sources.</t>
+          <t>Ranked #51 of 69. Chosen from Okaloosa County Property Appraiser GIS (single-family use code 0100, assessed $1,836,860). Score 40 = $1.5M+ value (+15); bay/lagoon waterfront (+15); owner-occupied (+10). Bay Towne View - bay. Owner-occupied (mailing address matches property). In direct Isaias landfall corridor per NHC 1pm Oct 7 advisory (AL/FL border, landfall Fri night). No phone found in free sources.</t>
         </is>
       </c>
     </row>
@@ -9346,23 +9382,23 @@
       <c r="D126" s="7" t="inlineStr"/>
       <c r="E126" s="7" t="inlineStr">
         <is>
-          <t>William Byron &amp; Amy W Knight</t>
+          <t>Rev Living Trust Wampler</t>
         </is>
       </c>
       <c r="F126" s="7" t="inlineStr">
         <is>
-          <t>1302 WESTERN LAKE DR</t>
+          <t>327 BEAL PKWY NW</t>
         </is>
       </c>
       <c r="G126" s="7" t="inlineStr">
         <is>
-          <t>Santa Rosa Beach</t>
+          <t>FORT WALTON BEACH</t>
         </is>
       </c>
       <c r="H126" s="7" t="inlineStr"/>
       <c r="I126" s="7" t="inlineStr"/>
       <c r="J126" s="8" t="n">
-        <v>1775000</v>
+        <v>1782993</v>
       </c>
       <c r="K126" s="7" t="inlineStr">
         <is>
@@ -9371,18 +9407,22 @@
       </c>
       <c r="L126" s="7" t="inlineStr">
         <is>
-          <t>Western Lake</t>
-        </is>
-      </c>
-      <c r="M126" s="7" t="inlineStr"/>
+          <t>Beal Pkwy - near bay</t>
+        </is>
+      </c>
+      <c r="M126" s="7" t="inlineStr">
+        <is>
+          <t>10-2S-24-0000-0041-0000</t>
+        </is>
+      </c>
       <c r="N126" s="7" t="inlineStr">
         <is>
-          <t>1302 WESTERN LAKE DR, Santa Rosa Beach, FL 32459</t>
+          <t>327 BEAL PKWY NW, FT WALTON BEACH, FL 32548</t>
         </is>
       </c>
       <c r="O126" s="7" t="inlineStr">
         <is>
-          <t>Score 40: $1.78M value (+30), owner-occupied (+10). Western Lake waterfront. In eastern damage corridor per NHC Oct 7 advisory.</t>
+          <t>Ranked #53 of 69. Chosen from Okaloosa County Property Appraiser GIS (single-family use code 0100, assessed $1,782,993). Score 40 = $1.5M+ value (+15); bay/lagoon waterfront (+15); owner-occupied (+10). Beal Pkwy - near bay. Owner-occupied (mailing address matches property). In direct Isaias landfall corridor per NHC 1pm Oct 7 advisory (AL/FL border, landfall Fri night). No phone found in free sources.</t>
         </is>
       </c>
     </row>
@@ -9403,23 +9443,23 @@
       <c r="D127" s="7" t="inlineStr"/>
       <c r="E127" s="7" t="inlineStr">
         <is>
-          <t>Shawn B &amp; Darbonnier Bri Kurtz</t>
+          <t>William Byron &amp; Amy W Knight</t>
         </is>
       </c>
       <c r="F127" s="7" t="inlineStr">
         <is>
-          <t>837 CHOCTAW LN</t>
+          <t>1302 WESTERN LAKE DR</t>
         </is>
       </c>
       <c r="G127" s="7" t="inlineStr">
         <is>
-          <t>SHALIMAR</t>
+          <t>Santa Rosa Beach</t>
         </is>
       </c>
       <c r="H127" s="7" t="inlineStr"/>
       <c r="I127" s="7" t="inlineStr"/>
       <c r="J127" s="8" t="n">
-        <v>1738593</v>
+        <v>1775000</v>
       </c>
       <c r="K127" s="7" t="inlineStr">
         <is>
@@ -9428,22 +9468,18 @@
       </c>
       <c r="L127" s="7" t="inlineStr">
         <is>
-          <t>Bluffs at Shalimar Pointe</t>
-        </is>
-      </c>
-      <c r="M127" s="7" t="inlineStr">
-        <is>
-          <t>04-2S-23-4805-0000-0050</t>
-        </is>
-      </c>
+          <t>Western Lake</t>
+        </is>
+      </c>
+      <c r="M127" s="7" t="inlineStr"/>
       <c r="N127" s="7" t="inlineStr">
         <is>
-          <t>837 CHOCTAW LN, SHALIMAR, FL 32579</t>
+          <t>1302 WESTERN LAKE DR, Santa Rosa Beach, FL 32459</t>
         </is>
       </c>
       <c r="O127" s="7" t="inlineStr">
         <is>
-          <t>Ranked #63 of 69. Chosen from Okaloosa County Property Appraiser GIS (single-family use code 0100, assessed $1,738,593). Score 25 = $1.5M+ value (+15); owner-occupied (+10). Bluffs at Shalimar Pointe. Owner-occupied (mailing address matches property). In direct Isaias landfall corridor per NHC 1pm Oct 7 advisory (AL/FL border, landfall Fri night). No phone found in free sources.</t>
+          <t>Score 40: $1.78M value (+30), owner-occupied (+10). Western Lake waterfront. In eastern damage corridor per NHC Oct 7 advisory.</t>
         </is>
       </c>
     </row>
@@ -9464,23 +9500,23 @@
       <c r="D128" s="7" t="inlineStr"/>
       <c r="E128" s="7" t="inlineStr">
         <is>
-          <t>John M Bates And Pamela Bates</t>
+          <t>Shawn B &amp; Darbonnier Bri Kurtz</t>
         </is>
       </c>
       <c r="F128" s="7" t="inlineStr">
         <is>
-          <t>30846 River Rd</t>
+          <t>837 CHOCTAW LN</t>
         </is>
       </c>
       <c r="G128" s="7" t="inlineStr">
         <is>
-          <t>Orange Beach</t>
+          <t>SHALIMAR</t>
         </is>
       </c>
       <c r="H128" s="7" t="inlineStr"/>
       <c r="I128" s="7" t="inlineStr"/>
       <c r="J128" s="8" t="n">
-        <v>1733800</v>
+        <v>1738593</v>
       </c>
       <c r="K128" s="7" t="inlineStr">
         <is>
@@ -9489,22 +9525,22 @@
       </c>
       <c r="L128" s="7" t="inlineStr">
         <is>
-          <t>Ole River (Ono Island)</t>
+          <t>Bluffs at Shalimar Pointe</t>
         </is>
       </c>
       <c r="M128" s="7" t="inlineStr">
         <is>
-          <t>64-03-06-0-000-001.020</t>
+          <t>04-2S-23-4805-0000-0050</t>
         </is>
       </c>
       <c r="N128" s="7" t="inlineStr">
         <is>
-          <t>30846 RIVER RD, ORANGE BEACH, AL 36561-5748</t>
+          <t>837 CHOCTAW LN, SHALIMAR, FL 32579</t>
         </is>
       </c>
       <c r="O128" s="7" t="inlineStr">
         <is>
-          <t>Score 55: $1.73M county assessed value (+30); Ole River (Ono Island) frontage (+15); owner-occupied (+10); no phone found in free sources (+0). Owner-occupied Ono Island riverfront; $1.73M assessed. No verifiable phone found. In direct landfall corridor per NHC Oct 7 advisory - Tropical Storm Isaias landfall expected near AL/FL border Friday night.</t>
+          <t>Ranked #63 of 69. Chosen from Okaloosa County Property Appraiser GIS (single-family use code 0100, assessed $1,738,593). Score 25 = $1.5M+ value (+15); owner-occupied (+10). Bluffs at Shalimar Pointe. Owner-occupied (mailing address matches property). In direct Isaias landfall corridor per NHC 1pm Oct 7 advisory (AL/FL border, landfall Fri night). No phone found in free sources.</t>
         </is>
       </c>
     </row>
@@ -9525,23 +9561,23 @@
       <c r="D129" s="7" t="inlineStr"/>
       <c r="E129" s="7" t="inlineStr">
         <is>
-          <t>Dennis A &amp; Jaime M Mcmanus</t>
+          <t>John M Bates And Pamela Bates</t>
         </is>
       </c>
       <c r="F129" s="7" t="inlineStr">
         <is>
-          <t>2300 WATKINS CV</t>
+          <t>30846 River Rd</t>
         </is>
       </c>
       <c r="G129" s="7" t="inlineStr">
         <is>
-          <t>FORT WALTON BEACH</t>
+          <t>Orange Beach</t>
         </is>
       </c>
       <c r="H129" s="7" t="inlineStr"/>
       <c r="I129" s="7" t="inlineStr"/>
       <c r="J129" s="8" t="n">
-        <v>1665176</v>
+        <v>1733800</v>
       </c>
       <c r="K129" s="7" t="inlineStr">
         <is>
@@ -9550,22 +9586,22 @@
       </c>
       <c r="L129" s="7" t="inlineStr">
         <is>
-          <t>Dallas Duncan</t>
+          <t>Ole River (Ono Island)</t>
         </is>
       </c>
       <c r="M129" s="7" t="inlineStr">
         <is>
-          <t>01-2S-24-0600-0000-06C1</t>
+          <t>64-03-06-0-000-001.020</t>
         </is>
       </c>
       <c r="N129" s="7" t="inlineStr">
         <is>
-          <t>2300 WATKINS COVE, FT WALTON BEACH, FL 32547</t>
+          <t>30846 RIVER RD, ORANGE BEACH, AL 36561-5748</t>
         </is>
       </c>
       <c r="O129" s="7" t="inlineStr">
         <is>
-          <t>Ranked #65 of 69. Chosen from Okaloosa County Property Appraiser GIS (single-family use code 0100, assessed $1,665,176). Score 25 = $1.5M+ value (+15); owner-occupied (+10). Dallas Duncan. Owner-occupied (mailing address matches property). In direct Isaias landfall corridor per NHC 1pm Oct 7 advisory (AL/FL border, landfall Fri night). No phone found in free sources.</t>
+          <t>Score 55: $1.73M county assessed value (+30); Ole River (Ono Island) frontage (+15); owner-occupied (+10); no phone found in free sources (+0). Owner-occupied Ono Island riverfront; $1.73M assessed. No verifiable phone found. In direct landfall corridor per NHC Oct 7 advisory - Tropical Storm Isaias landfall expected near AL/FL border Friday night.</t>
         </is>
       </c>
     </row>
@@ -9586,23 +9622,23 @@
       <c r="D130" s="7" t="inlineStr"/>
       <c r="E130" s="7" t="inlineStr">
         <is>
-          <t>F.W. &amp; Sharon Rev Trust Schinz</t>
+          <t>Dennis A &amp; Jaime M Mcmanus</t>
         </is>
       </c>
       <c r="F130" s="7" t="inlineStr">
         <is>
-          <t>275 COUNTRY CLUB RD</t>
+          <t>2300 WATKINS CV</t>
         </is>
       </c>
       <c r="G130" s="7" t="inlineStr">
         <is>
-          <t>SHALIMAR</t>
+          <t>FORT WALTON BEACH</t>
         </is>
       </c>
       <c r="H130" s="7" t="inlineStr"/>
       <c r="I130" s="7" t="inlineStr"/>
       <c r="J130" s="8" t="n">
-        <v>1601856</v>
+        <v>1665176</v>
       </c>
       <c r="K130" s="7" t="inlineStr">
         <is>
@@ -9611,22 +9647,22 @@
       </c>
       <c r="L130" s="7" t="inlineStr">
         <is>
-          <t>Shalimar golf area</t>
+          <t>Dallas Duncan</t>
         </is>
       </c>
       <c r="M130" s="7" t="inlineStr">
         <is>
-          <t>04-2S-23-0000-0010-0490</t>
+          <t>01-2S-24-0600-0000-06C1</t>
         </is>
       </c>
       <c r="N130" s="7" t="inlineStr">
         <is>
-          <t>275 COUNTRY CLUB RD, SHALIMAR, FL 32579</t>
+          <t>2300 WATKINS COVE, FT WALTON BEACH, FL 32547</t>
         </is>
       </c>
       <c r="O130" s="7" t="inlineStr">
         <is>
-          <t>Ranked #66 of 69. Chosen from Okaloosa County Property Appraiser GIS (single-family use code 0100, assessed $1,601,856). Score 25 = $1.5M+ value (+15); owner-occupied (+10). Shalimar golf area. Owner-occupied (mailing address matches property). In direct Isaias landfall corridor per NHC 1pm Oct 7 advisory (AL/FL border, landfall Fri night). No phone found in free sources.</t>
+          <t>Ranked #65 of 69. Chosen from Okaloosa County Property Appraiser GIS (single-family use code 0100, assessed $1,665,176). Score 25 = $1.5M+ value (+15); owner-occupied (+10). Dallas Duncan. Owner-occupied (mailing address matches property). In direct Isaias landfall corridor per NHC 1pm Oct 7 advisory (AL/FL border, landfall Fri night). No phone found in free sources.</t>
         </is>
       </c>
     </row>
@@ -9647,23 +9683,23 @@
       <c r="D131" s="7" t="inlineStr"/>
       <c r="E131" s="7" t="inlineStr">
         <is>
-          <t>Richard Gene Jr Trust Starr</t>
+          <t>F.W. &amp; Sharon Rev Trust Schinz</t>
         </is>
       </c>
       <c r="F131" s="7" t="inlineStr">
         <is>
-          <t>250 BROOKS ST SE</t>
+          <t>275 COUNTRY CLUB RD</t>
         </is>
       </c>
       <c r="G131" s="7" t="inlineStr">
         <is>
-          <t>FORT WALTON BEACH</t>
+          <t>SHALIMAR</t>
         </is>
       </c>
       <c r="H131" s="7" t="inlineStr"/>
       <c r="I131" s="7" t="inlineStr"/>
       <c r="J131" s="8" t="n">
-        <v>1553683</v>
+        <v>1601856</v>
       </c>
       <c r="K131" s="7" t="inlineStr">
         <is>
@@ -9672,22 +9708,22 @@
       </c>
       <c r="L131" s="7" t="inlineStr">
         <is>
-          <t>Bay Towne View - bay</t>
+          <t>Shalimar golf area</t>
         </is>
       </c>
       <c r="M131" s="7" t="inlineStr">
         <is>
-          <t>24-2S-24-0200-0000-0060</t>
+          <t>04-2S-23-0000-0010-0490</t>
         </is>
       </c>
       <c r="N131" s="7" t="inlineStr">
         <is>
-          <t>250 BROOKS ST, FT WALTON BEACH, FL 32548</t>
+          <t>275 COUNTRY CLUB RD, SHALIMAR, FL 32579</t>
         </is>
       </c>
       <c r="O131" s="7" t="inlineStr">
         <is>
-          <t>Ranked #55 of 69. Chosen from Okaloosa County Property Appraiser GIS (single-family use code 0100, assessed $1,553,683). Score 40 = $1.5M+ value (+15); bay/lagoon waterfront (+15); owner-occupied (+10). Bay Towne View - bay. Owner-occupied (mailing address matches property). In direct Isaias landfall corridor per NHC 1pm Oct 7 advisory (AL/FL border, landfall Fri night). No phone found in free sources.</t>
+          <t>Ranked #66 of 69. Chosen from Okaloosa County Property Appraiser GIS (single-family use code 0100, assessed $1,601,856). Score 25 = $1.5M+ value (+15); owner-occupied (+10). Shalimar golf area. Owner-occupied (mailing address matches property). In direct Isaias landfall corridor per NHC 1pm Oct 7 advisory (AL/FL border, landfall Fri night). No phone found in free sources.</t>
         </is>
       </c>
     </row>
@@ -9708,23 +9744,23 @@
       <c r="D132" s="7" t="inlineStr"/>
       <c r="E132" s="7" t="inlineStr">
         <is>
-          <t>Living Trust Mclaughlin</t>
+          <t>Richard Gene Jr Trust Starr</t>
         </is>
       </c>
       <c r="F132" s="7" t="inlineStr">
         <is>
-          <t>17 POQUITO RD</t>
+          <t>250 BROOKS ST SE</t>
         </is>
       </c>
       <c r="G132" s="7" t="inlineStr">
         <is>
-          <t>SHALIMAR</t>
+          <t>FORT WALTON BEACH</t>
         </is>
       </c>
       <c r="H132" s="7" t="inlineStr"/>
       <c r="I132" s="7" t="inlineStr"/>
       <c r="J132" s="8" t="n">
-        <v>1541919</v>
+        <v>1553683</v>
       </c>
       <c r="K132" s="7" t="inlineStr">
         <is>
@@ -9733,22 +9769,22 @@
       </c>
       <c r="L132" s="7" t="inlineStr">
         <is>
-          <t>Bayou Poquito waterfront</t>
+          <t>Bay Towne View - bay</t>
         </is>
       </c>
       <c r="M132" s="7" t="inlineStr">
         <is>
-          <t>31-1S-23-0120-0016-0080</t>
+          <t>24-2S-24-0200-0000-0060</t>
         </is>
       </c>
       <c r="N132" s="7" t="inlineStr">
         <is>
-          <t>17 POQUITO RD, SHALIMAR, FL 32579</t>
+          <t>250 BROOKS ST, FT WALTON BEACH, FL 32548</t>
         </is>
       </c>
       <c r="O132" s="7" t="inlineStr">
         <is>
-          <t>Ranked #56 of 69. Chosen from Okaloosa County Property Appraiser GIS (single-family use code 0100, assessed $1,541,919). Score 40 = $1.5M+ value (+15); bayou waterfront (+15); owner-occupied (+10). Bayou Poquito waterfront. Owner-occupied (mailing address matches property). In direct Isaias landfall corridor per NHC 1pm Oct 7 advisory (AL/FL border, landfall Fri night). No phone found in free sources.</t>
+          <t>Ranked #55 of 69. Chosen from Okaloosa County Property Appraiser GIS (single-family use code 0100, assessed $1,553,683). Score 40 = $1.5M+ value (+15); bay/lagoon waterfront (+15); owner-occupied (+10). Bay Towne View - bay. Owner-occupied (mailing address matches property). In direct Isaias landfall corridor per NHC 1pm Oct 7 advisory (AL/FL border, landfall Fri night). No phone found in free sources.</t>
         </is>
       </c>
     </row>
@@ -9769,23 +9805,23 @@
       <c r="D133" s="7" t="inlineStr"/>
       <c r="E133" s="7" t="inlineStr">
         <is>
-          <t>John G Wagner</t>
+          <t>Living Trust Mclaughlin</t>
         </is>
       </c>
       <c r="F133" s="7" t="inlineStr">
         <is>
-          <t>1750 E Texar Dr, Pensacola, FL 32503</t>
+          <t>17 POQUITO RD</t>
         </is>
       </c>
       <c r="G133" s="7" t="inlineStr">
         <is>
-          <t>Pensacola</t>
+          <t>SHALIMAR</t>
         </is>
       </c>
       <c r="H133" s="7" t="inlineStr"/>
       <c r="I133" s="7" t="inlineStr"/>
       <c r="J133" s="8" t="n">
-        <v>1227780</v>
+        <v>1541919</v>
       </c>
       <c r="K133" s="7" t="inlineStr">
         <is>
@@ -9794,22 +9830,22 @@
       </c>
       <c r="L133" s="7" t="inlineStr">
         <is>
-          <t>Bayou Texar</t>
+          <t>Bayou Poquito waterfront</t>
         </is>
       </c>
       <c r="M133" s="7" t="inlineStr">
         <is>
-          <t>032S302000015001</t>
+          <t>31-1S-23-0120-0016-0080</t>
         </is>
       </c>
       <c r="N133" s="7" t="inlineStr">
         <is>
-          <t>1750 Texar Dr, Pensacola, FL 32503</t>
+          <t>17 POQUITO RD, SHALIMAR, FL 32579</t>
         </is>
       </c>
       <c r="O133" s="7" t="inlineStr">
         <is>
-          <t>Score 65: $1,227,780 assessed just value (+30), direct Bayou Texar frontage (+25), owner-occupied (+10). 5,033 sf home on 1.9 acres, built 1960. No phone found. In direct landfall corridor per NHC 1pm Oct 7 advisory — landfall expected near AL/FL border Friday night.</t>
+          <t>Ranked #56 of 69. Chosen from Okaloosa County Property Appraiser GIS (single-family use code 0100, assessed $1,541,919). Score 40 = $1.5M+ value (+15); bayou waterfront (+15); owner-occupied (+10). Bayou Poquito waterfront. Owner-occupied (mailing address matches property). In direct Isaias landfall corridor per NHC 1pm Oct 7 advisory (AL/FL border, landfall Fri night). No phone found in free sources.</t>
         </is>
       </c>
     </row>
@@ -9830,25 +9866,23 @@
       <c r="D134" s="7" t="inlineStr"/>
       <c r="E134" s="7" t="inlineStr">
         <is>
-          <t>Glyn Bordelon</t>
+          <t>John G Wagner</t>
         </is>
       </c>
       <c r="F134" s="7" t="inlineStr">
         <is>
-          <t>4403 Soundside Dr</t>
+          <t>1750 E Texar Dr, Pensacola, FL 32503</t>
         </is>
       </c>
       <c r="G134" s="7" t="inlineStr">
         <is>
-          <t>Gulf Breeze</t>
+          <t>Pensacola</t>
         </is>
       </c>
       <c r="H134" s="7" t="inlineStr"/>
       <c r="I134" s="7" t="inlineStr"/>
-      <c r="J134" s="8" t="inlineStr">
-        <is>
-          <t>1185000 (2018 sale)</t>
-        </is>
+      <c r="J134" s="8" t="n">
+        <v>1227780</v>
       </c>
       <c r="K134" s="7" t="inlineStr">
         <is>
@@ -9857,22 +9891,22 @@
       </c>
       <c r="L134" s="7" t="inlineStr">
         <is>
-          <t>Santa Rosa Sound</t>
+          <t>Bayou Texar</t>
         </is>
       </c>
       <c r="M134" s="7" t="inlineStr">
         <is>
-          <t>342S280000002030000</t>
+          <t>032S302000015001</t>
         </is>
       </c>
       <c r="N134" s="7" t="inlineStr">
         <is>
-          <t>4403 Soundside Dr Gulf Breeze FL 32563</t>
+          <t>1750 Texar Dr, Pensacola, FL 32503</t>
         </is>
       </c>
       <c r="O134" s="7" t="inlineStr">
         <is>
-          <t>Score 65: direct Santa Rosa Sound waterfront (+25), $1.19M last sale (+30), owner-occupied (+10). No phone found - knock before storm. 1.09-acre 4bd/5ba 3,838sf home, mature trees. In direct landfall corridor per NHC 1pm Oct 7 advisory - landfall expected near AL/FL border Friday night.</t>
+          <t>Score 65: $1,227,780 assessed just value (+30), direct Bayou Texar frontage (+25), owner-occupied (+10). 5,033 sf home on 1.9 acres, built 1960. No phone found. In direct landfall corridor per NHC 1pm Oct 7 advisory — landfall expected near AL/FL border Friday night.</t>
         </is>
       </c>
     </row>
@@ -9893,23 +9927,25 @@
       <c r="D135" s="7" t="inlineStr"/>
       <c r="E135" s="7" t="inlineStr">
         <is>
-          <t>Robert T &amp; Reese Clairen Reese</t>
+          <t>Glyn Bordelon</t>
         </is>
       </c>
       <c r="F135" s="7" t="inlineStr">
         <is>
-          <t>353 Gulfview Ln</t>
+          <t>4403 Soundside Dr</t>
         </is>
       </c>
       <c r="G135" s="7" t="inlineStr">
         <is>
-          <t>Perdido Key</t>
+          <t>Gulf Breeze</t>
         </is>
       </c>
       <c r="H135" s="7" t="inlineStr"/>
       <c r="I135" s="7" t="inlineStr"/>
-      <c r="J135" s="8" t="n">
-        <v>643000</v>
+      <c r="J135" s="8" t="inlineStr">
+        <is>
+          <t>1185000 (2018 sale)</t>
+        </is>
       </c>
       <c r="K135" s="7" t="inlineStr">
         <is>
@@ -9918,22 +9954,22 @@
       </c>
       <c r="L135" s="7" t="inlineStr">
         <is>
-          <t>Direct Gulf of Mexico frontage</t>
+          <t>Santa Rosa Sound</t>
         </is>
       </c>
       <c r="M135" s="7" t="inlineStr">
         <is>
-          <t>064S320405014001</t>
+          <t>342S280000002030000</t>
         </is>
       </c>
       <c r="N135" s="7" t="inlineStr">
         <is>
-          <t>353 Gulfview Ln, Pensacola, FL 32507</t>
+          <t>4403 Soundside Dr Gulf Breeze FL 32563</t>
         </is>
       </c>
       <c r="O135" s="7" t="inlineStr">
         <is>
-          <t>Score 55: $643K value (+20), direct Gulf frontage (+25), owner-occupied (+10). In direct landfall corridor per NHC Oct 7 advisory.</t>
+          <t>Score 65: direct Santa Rosa Sound waterfront (+25), $1.19M last sale (+30), owner-occupied (+10). No phone found - knock before storm. 1.09-acre 4bd/5ba 3,838sf home, mature trees. In direct landfall corridor per NHC 1pm Oct 7 advisory - landfall expected near AL/FL border Friday night.</t>
         </is>
       </c>
     </row>
@@ -9954,12 +9990,12 @@
       <c r="D136" s="7" t="inlineStr"/>
       <c r="E136" s="7" t="inlineStr">
         <is>
-          <t>Terence A Mozena</t>
+          <t>Robert T &amp; Reese Clairen Reese</t>
         </is>
       </c>
       <c r="F136" s="7" t="inlineStr">
         <is>
-          <t>349 Gulfview Ln</t>
+          <t>353 Gulfview Ln</t>
         </is>
       </c>
       <c r="G136" s="7" t="inlineStr">
@@ -9970,7 +10006,7 @@
       <c r="H136" s="7" t="inlineStr"/>
       <c r="I136" s="7" t="inlineStr"/>
       <c r="J136" s="8" t="n">
-        <v>579000</v>
+        <v>643000</v>
       </c>
       <c r="K136" s="7" t="inlineStr">
         <is>
@@ -9984,17 +10020,17 @@
       </c>
       <c r="M136" s="7" t="inlineStr">
         <is>
-          <t>064S320405013001</t>
+          <t>064S320405014001</t>
         </is>
       </c>
       <c r="N136" s="7" t="inlineStr">
         <is>
-          <t>349 Gulfview Ln, Pensacola, FL 32507</t>
+          <t>353 Gulfview Ln, Pensacola, FL 32507</t>
         </is>
       </c>
       <c r="O136" s="7" t="inlineStr">
         <is>
-          <t>Score 55: $579K value (+20), direct Gulf frontage (+25), owner-occupied (+10). In direct landfall corridor per NHC Oct 7 advisory.</t>
+          <t>Score 55: $643K value (+20), direct Gulf frontage (+25), owner-occupied (+10). In direct landfall corridor per NHC Oct 7 advisory.</t>
         </is>
       </c>
     </row>
@@ -10009,53 +10045,53 @@
       </c>
       <c r="C137" s="7" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>65</t>
         </is>
       </c>
       <c r="D137" s="7" t="inlineStr"/>
       <c r="E137" s="7" t="inlineStr">
         <is>
-          <t>Spence Family Partnership P</t>
+          <t>Terence A Mozena</t>
         </is>
       </c>
       <c r="F137" s="7" t="inlineStr">
         <is>
-          <t>4764 OCEAN BLVD</t>
+          <t>349 Gulfview Ln</t>
         </is>
       </c>
       <c r="G137" s="7" t="inlineStr">
         <is>
-          <t>DESTIN</t>
+          <t>Perdido Key</t>
         </is>
       </c>
       <c r="H137" s="7" t="inlineStr"/>
       <c r="I137" s="7" t="inlineStr"/>
       <c r="J137" s="8" t="n">
-        <v>4430584</v>
+        <v>579000</v>
       </c>
       <c r="K137" s="7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="L137" s="7" t="inlineStr">
         <is>
-          <t>Destiny by the Sea - direct Gulf front</t>
+          <t>Direct Gulf of Mexico frontage</t>
         </is>
       </c>
       <c r="M137" s="7" t="inlineStr">
         <is>
-          <t>00-2S-22-0075-0000-0200</t>
+          <t>064S320405013001</t>
         </is>
       </c>
       <c r="N137" s="7" t="inlineStr">
         <is>
-          <t>180 SYCAMORE CT, LUMBERTON, TX 77657</t>
+          <t>349 Gulfview Ln, Pensacola, FL 32507</t>
         </is>
       </c>
       <c r="O137" s="7" t="inlineStr">
         <is>
-          <t>Ranked #33 of 69. Chosen from Okaloosa County Property Appraiser GIS (single-family use code 0100, assessed $4,430,584). Score 50 = $3M+ value (+25); direct Gulf frontage (+25). Destiny by the Sea - direct Gulf front. Second/vacation home (out-of-area mailing address) - absentee owner; storm damage still needs a local cleanup crew fast. In direct Isaias landfall corridor per NHC 1pm Oct 7 advisory (AL/FL border, landfall Fri night). No phone found in free sources.</t>
+          <t>Score 55: $579K value (+20), direct Gulf frontage (+25), owner-occupied (+10). In direct landfall corridor per NHC Oct 7 advisory.</t>
         </is>
       </c>
     </row>
@@ -10076,12 +10112,12 @@
       <c r="D138" s="7" t="inlineStr"/>
       <c r="E138" s="7" t="inlineStr">
         <is>
-          <t>Family Trust Travis</t>
+          <t>Spence Family Partnership P</t>
         </is>
       </c>
       <c r="F138" s="7" t="inlineStr">
         <is>
-          <t>4760 OCEAN BLVD</t>
+          <t>4764 OCEAN BLVD</t>
         </is>
       </c>
       <c r="G138" s="7" t="inlineStr">
@@ -10092,7 +10128,7 @@
       <c r="H138" s="7" t="inlineStr"/>
       <c r="I138" s="7" t="inlineStr"/>
       <c r="J138" s="8" t="n">
-        <v>4423168</v>
+        <v>4430584</v>
       </c>
       <c r="K138" s="7" t="inlineStr">
         <is>
@@ -10106,17 +10142,17 @@
       </c>
       <c r="M138" s="7" t="inlineStr">
         <is>
-          <t>00-2S-22-0075-0000-0170</t>
+          <t>00-2S-22-0075-0000-0200</t>
         </is>
       </c>
       <c r="N138" s="7" t="inlineStr">
         <is>
-          <t>310 LEISURE ACRES, BUCHANAN, TN 38222</t>
+          <t>180 SYCAMORE CT, LUMBERTON, TX 77657</t>
         </is>
       </c>
       <c r="O138" s="7" t="inlineStr">
         <is>
-          <t>Ranked #34 of 69. Chosen from Okaloosa County Property Appraiser GIS (single-family use code 0100, assessed $4,423,168). Score 50 = $3M+ value (+25); direct Gulf frontage (+25). Destiny by the Sea - direct Gulf front. Second/vacation home (out-of-area mailing address) - absentee owner; storm damage still needs a local cleanup crew fast. In direct Isaias landfall corridor per NHC 1pm Oct 7 advisory (AL/FL border, landfall Fri night). No phone found in free sources.</t>
+          <t>Ranked #33 of 69. Chosen from Okaloosa County Property Appraiser GIS (single-family use code 0100, assessed $4,430,584). Score 50 = $3M+ value (+25); direct Gulf frontage (+25). Destiny by the Sea - direct Gulf front. Second/vacation home (out-of-area mailing address) - absentee owner; storm damage still needs a local cleanup crew fast. In direct Isaias landfall corridor per NHC 1pm Oct 7 advisory (AL/FL border, landfall Fri night). No phone found in free sources.</t>
         </is>
       </c>
     </row>
